--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -60954,6 +60954,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2635">
+      <c r="A2635" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2635" t="n">
+        <v>432669</v>
+      </c>
+      <c r="C2635" t="n">
+        <v>12.3299999237061</v>
+      </c>
+      <c r="D2635" t="n">
+        <v>12.0200004577637</v>
+      </c>
+      <c r="E2635" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="F2635" t="n">
+        <v>12.1099996566772</v>
+      </c>
+      <c r="G2635" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -60977,6 +60977,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2636">
+      <c r="A2636" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2636" t="n">
+        <v>318929</v>
+      </c>
+      <c r="C2636" t="n">
+        <v>12.3500003814697</v>
+      </c>
+      <c r="D2636" t="n">
+        <v>11.9200000762939</v>
+      </c>
+      <c r="E2636" t="n">
+        <v>12.0600004196167</v>
+      </c>
+      <c r="F2636" t="n">
+        <v>12.3500003814697</v>
+      </c>
+      <c r="G2636" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -61000,6 +61000,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2637">
+      <c r="A2637" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2637" t="n">
+        <v>627522</v>
+      </c>
+      <c r="C2637" t="n">
+        <v>12.6599998474121</v>
+      </c>
+      <c r="D2637" t="n">
+        <v>12.2200002670288</v>
+      </c>
+      <c r="E2637" t="n">
+        <v>12.2600002288818</v>
+      </c>
+      <c r="F2637" t="n">
+        <v>12.6999998092651</v>
+      </c>
+      <c r="G2637" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -61008,7 +61008,7 @@
         <v>627522</v>
       </c>
       <c r="C2637" t="n">
-        <v>12.6599998474121</v>
+        <v>12.6999998092651</v>
       </c>
       <c r="D2637" t="n">
         <v>12.2200002670288</v>
@@ -61020,6 +61020,29 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G2637" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2638">
+      <c r="A2638" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2638" t="n">
+        <v>350148</v>
+      </c>
+      <c r="C2638" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="D2638" t="n">
+        <v>12.5100002288818</v>
+      </c>
+      <c r="E2638" t="n">
+        <v>12.710000038147</v>
+      </c>
+      <c r="F2638" t="n">
+        <v>12.6499996185303</v>
+      </c>
+      <c r="G2638" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -60864,19 +60864,19 @@
     </row>
     <row r="2631">
       <c r="A2631" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2631" t="n">
-        <v>284461</v>
+        <v>273630</v>
       </c>
       <c r="C2631" t="n">
-        <v>13.0600004196167</v>
+        <v>13.1000003814697</v>
       </c>
       <c r="D2631" t="n">
-        <v>12.7799997329712</v>
+        <v>12.8599996566772</v>
       </c>
       <c r="E2631" t="n">
-        <v>12.8100004196167</v>
+        <v>13.039999961853</v>
       </c>
       <c r="F2631" t="n">
         <v>12.8699998855591</v>
@@ -60887,22 +60887,22 @@
     </row>
     <row r="2632">
       <c r="A2632" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2632" t="n">
-        <v>355698</v>
+        <v>284461</v>
       </c>
       <c r="C2632" t="n">
-        <v>13</v>
+        <v>13.0600004196167</v>
       </c>
       <c r="D2632" t="n">
-        <v>12.3500003814697</v>
+        <v>12.7799997329712</v>
       </c>
       <c r="E2632" t="n">
-        <v>13</v>
+        <v>12.8100004196167</v>
       </c>
       <c r="F2632" t="n">
-        <v>12.4200000762939</v>
+        <v>12.8699998855591</v>
       </c>
       <c r="G2632" t="s">
         <v>7</v>
@@ -60910,22 +60910,22 @@
     </row>
     <row r="2633">
       <c r="A2633" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2633" t="n">
-        <v>262410</v>
+        <v>355698</v>
       </c>
       <c r="C2633" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2633" t="n">
+        <v>12.3500003814697</v>
+      </c>
+      <c r="E2633" t="n">
+        <v>13</v>
+      </c>
+      <c r="F2633" t="n">
         <v>12.4200000762939</v>
-      </c>
-      <c r="D2633" t="n">
-        <v>12.1800003051758</v>
-      </c>
-      <c r="E2633" t="n">
-        <v>12.4200000762939</v>
-      </c>
-      <c r="F2633" t="n">
-        <v>12.25</v>
       </c>
       <c r="G2633" t="s">
         <v>7</v>
@@ -60933,22 +60933,22 @@
     </row>
     <row r="2634">
       <c r="A2634" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2634" t="n">
-        <v>364198</v>
+        <v>262410</v>
       </c>
       <c r="C2634" t="n">
-        <v>12.4399995803833</v>
+        <v>12.4200000762939</v>
       </c>
       <c r="D2634" t="n">
+        <v>12.1800003051758</v>
+      </c>
+      <c r="E2634" t="n">
+        <v>12.4200000762939</v>
+      </c>
+      <c r="F2634" t="n">
         <v>12.25</v>
-      </c>
-      <c r="E2634" t="n">
-        <v>12.2700004577637</v>
-      </c>
-      <c r="F2634" t="n">
-        <v>12.4099998474121</v>
       </c>
       <c r="G2634" t="s">
         <v>7</v>
@@ -60956,22 +60956,22 @@
     </row>
     <row r="2635">
       <c r="A2635" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2635" t="n">
-        <v>432669</v>
+        <v>364198</v>
       </c>
       <c r="C2635" t="n">
-        <v>12.3299999237061</v>
+        <v>12.4399995803833</v>
       </c>
       <c r="D2635" t="n">
-        <v>12.0200004577637</v>
+        <v>12.25</v>
       </c>
       <c r="E2635" t="n">
-        <v>12.3000001907349</v>
+        <v>12.2700004577637</v>
       </c>
       <c r="F2635" t="n">
-        <v>12.1099996566772</v>
+        <v>12.4099998474121</v>
       </c>
       <c r="G2635" t="s">
         <v>7</v>
@@ -60979,22 +60979,22 @@
     </row>
     <row r="2636">
       <c r="A2636" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2636" t="n">
-        <v>318929</v>
+        <v>432669</v>
       </c>
       <c r="C2636" t="n">
-        <v>12.3500003814697</v>
+        <v>12.3299999237061</v>
       </c>
       <c r="D2636" t="n">
-        <v>11.9200000762939</v>
+        <v>12.0200004577637</v>
       </c>
       <c r="E2636" t="n">
-        <v>12.0600004196167</v>
+        <v>12.3000001907349</v>
       </c>
       <c r="F2636" t="n">
-        <v>12.3500003814697</v>
+        <v>12.1099996566772</v>
       </c>
       <c r="G2636" t="s">
         <v>7</v>
@@ -61002,22 +61002,22 @@
     </row>
     <row r="2637">
       <c r="A2637" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2637" t="n">
-        <v>627522</v>
+        <v>318929</v>
       </c>
       <c r="C2637" t="n">
-        <v>12.6999998092651</v>
+        <v>12.3500003814697</v>
       </c>
       <c r="D2637" t="n">
-        <v>12.2200002670288</v>
+        <v>11.9200000762939</v>
       </c>
       <c r="E2637" t="n">
-        <v>12.2600002288818</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="F2637" t="n">
-        <v>12.6999998092651</v>
+        <v>12.3500003814697</v>
       </c>
       <c r="G2637" t="s">
         <v>7</v>
@@ -61025,24 +61025,47 @@
     </row>
     <row r="2638">
       <c r="A2638" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2638" t="n">
-        <v>350148</v>
+        <v>627522</v>
       </c>
       <c r="C2638" t="n">
-        <v>12.75</v>
+        <v>12.6999998092651</v>
       </c>
       <c r="D2638" t="n">
-        <v>12.5100002288818</v>
+        <v>12.2200002670288</v>
       </c>
       <c r="E2638" t="n">
-        <v>12.710000038147</v>
+        <v>12.2600002288818</v>
       </c>
       <c r="F2638" t="n">
-        <v>12.6499996185303</v>
+        <v>12.6999998092651</v>
       </c>
       <c r="G2638" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2639">
+      <c r="A2639" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2639" t="n">
+        <v>650040</v>
+      </c>
+      <c r="C2639" t="n">
+        <v>12.7600002288818</v>
+      </c>
+      <c r="D2639" t="n">
+        <v>12.4799995422363</v>
+      </c>
+      <c r="E2639" t="n">
+        <v>12.5799999237061</v>
+      </c>
+      <c r="F2639" t="n">
+        <v>12.6400003433228</v>
+      </c>
+      <c r="G2639" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -525,7 +525,7 @@
         <v>3.75</v>
       </c>
       <c r="G6" t="n">
-        <v>3.01192617416382</v>
+        <v>3.0119264125824</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G12" t="n">
-        <v>3.11473345756531</v>
+        <v>3.11473321914673</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G14" t="n">
-        <v>3.07618069648743</v>
+        <v>3.07618093490601</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G17" t="n">
-        <v>3.11473345756531</v>
+        <v>3.11473321914673</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.86199998855591</v>
       </c>
       <c r="G18" t="n">
-        <v>3.101881980896</v>
+        <v>3.10188221931458</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G20" t="n">
-        <v>3.09545707702637</v>
+        <v>3.09545731544495</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G22" t="n">
-        <v>3.24163579940796</v>
+        <v>3.24163556098938</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>3.28179478645325</v>
+        <v>3.28179502487183</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G24" t="n">
-        <v>3.37335729598999</v>
+        <v>3.37335681915283</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>3.37657046318054</v>
+        <v>3.37656998634338</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G27" t="n">
-        <v>3.32355999946594</v>
+        <v>3.32356023788452</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G28" t="n">
-        <v>3.28018808364868</v>
+        <v>3.28018879890442</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G30" t="n">
-        <v>3.09224462509155</v>
+        <v>3.09224414825439</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G32" t="n">
-        <v>3.03280901908875</v>
+        <v>3.03280878067017</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G35" t="n">
-        <v>3.09224462509155</v>
+        <v>3.09224414825439</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G37" t="n">
-        <v>3.12437152862549</v>
+        <v>3.12437176704407</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.90400004386902</v>
       </c>
       <c r="G38" t="n">
-        <v>3.13561606407166</v>
+        <v>3.13561630249023</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>2.9797990322113</v>
+        <v>2.97979879379272</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G41" t="n">
-        <v>2.93964004516602</v>
+        <v>2.93964028358459</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G42" t="n">
-        <v>2.98943686485291</v>
+        <v>2.98943710327148</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G43" t="n">
-        <v>3.07296776771545</v>
+        <v>3.07296800613403</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>3.17256236076355</v>
+        <v>3.17256212234497</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G45" t="n">
-        <v>3.17577505111694</v>
+        <v>3.17577481269836</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G50" t="n">
-        <v>3.0842125415802</v>
+        <v>3.08421230316162</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>3.02798986434937</v>
+        <v>3.02798962593079</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>3.02798986434937</v>
+        <v>3.02798962593079</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.75</v>
       </c>
       <c r="G57" t="n">
-        <v>3.01192617416382</v>
+        <v>3.0119264125824</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G59" t="n">
-        <v>3.01995825767517</v>
+        <v>3.01995801925659</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G60" t="n">
-        <v>3.07618069648743</v>
+        <v>3.07618093490601</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G61" t="n">
-        <v>3.09063839912415</v>
+        <v>3.09063792228699</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.09224462509155</v>
+        <v>3.09224414825439</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.156498670578</v>
+        <v>3.15649843215942</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G66" t="n">
-        <v>3.10991406440735</v>
+        <v>3.10991430282593</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G67" t="n">
-        <v>3.05369186401367</v>
+        <v>3.05369162559509</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>3.30910277366638</v>
+        <v>3.30910301208496</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G72" t="n">
-        <v>3.44724988937378</v>
+        <v>3.44725012779236</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>3.45367550849915</v>
+        <v>3.45367527008057</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G75" t="n">
-        <v>3.43921804428101</v>
+        <v>3.43921828269958</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.25</v>
       </c>
       <c r="G76" t="n">
-        <v>3.41351652145386</v>
+        <v>3.4135160446167</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G77" t="n">
-        <v>3.29625225067139</v>
+        <v>3.29625201225281</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>4.03200006484985</v>
       </c>
       <c r="G80" t="n">
-        <v>3.23842334747314</v>
+        <v>3.23842358589172</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>3.30107116699219</v>
+        <v>3.30107140541077</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>4.12799978256226</v>
       </c>
       <c r="G82" t="n">
-        <v>3.31552815437317</v>
+        <v>3.31552791595459</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>3.31713485717773</v>
+        <v>3.31713509559631</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G84" t="n">
-        <v>3.29303932189941</v>
+        <v>3.29303956031799</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G88" t="n">
-        <v>3.37014436721802</v>
+        <v>3.37014484405518</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4.25</v>
       </c>
       <c r="G89" t="n">
-        <v>3.41351652145386</v>
+        <v>3.4135160446167</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G90" t="n">
-        <v>3.44885635375977</v>
+        <v>3.44885683059692</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G91" t="n">
-        <v>3.4086971282959</v>
+        <v>3.40869736671448</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G95" t="n">
-        <v>3.38138914108276</v>
+        <v>3.38138937950134</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G97" t="n">
-        <v>3.30910277366638</v>
+        <v>3.30910301208496</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.15399980545044</v>
       </c>
       <c r="G98" t="n">
-        <v>3.33641076087952</v>
+        <v>3.3364109992981</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G99" t="n">
-        <v>3.35247445106506</v>
+        <v>3.35247421264648</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G100" t="n">
-        <v>3.42636728286743</v>
+        <v>3.42636752128601</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G104" t="n">
-        <v>3.45367550849915</v>
+        <v>3.45367527008057</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>3.49383473396301</v>
+        <v>3.49383425712585</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G106" t="n">
-        <v>3.48259019851685</v>
+        <v>3.48258972167969</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G107" t="n">
-        <v>3.51471757888794</v>
+        <v>3.51471734046936</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G108" t="n">
-        <v>3.54041886329651</v>
+        <v>3.54041862487793</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G109" t="n">
-        <v>3.50186610221863</v>
+        <v>3.50186657905579</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.53399348258972</v>
+        <v>3.5339937210083</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G111" t="n">
-        <v>3.57415246963501</v>
+        <v>3.57415270805359</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G112" t="n">
-        <v>3.59824800491333</v>
+        <v>3.59824824333191</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G113" t="n">
-        <v>3.59824800491333</v>
+        <v>3.59824824333191</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G114" t="n">
-        <v>3.57415246963501</v>
+        <v>3.57415270805359</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.58218455314636</v>
+        <v>3.58218479156494</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.5</v>
       </c>
       <c r="G116" t="n">
-        <v>3.61431193351746</v>
+        <v>3.61431169509888</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G117" t="n">
-        <v>3.60627937316895</v>
+        <v>3.60627913475037</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>3.53399348258972</v>
+        <v>3.5339937210083</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G119" t="n">
-        <v>3.5420253276825</v>
+        <v>3.54202508926392</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.36199998855591</v>
       </c>
       <c r="G120" t="n">
-        <v>3.50347304344177</v>
+        <v>3.50347256660461</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G121" t="n">
-        <v>3.50186610221863</v>
+        <v>3.50186657905579</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.50186610221863</v>
+        <v>3.50186657905579</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G123" t="n">
-        <v>3.40709090232849</v>
+        <v>3.40709066390991</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.25</v>
       </c>
       <c r="G124" t="n">
-        <v>3.41351652145386</v>
+        <v>3.4135160446167</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G128" t="n">
-        <v>3.22878503799438</v>
+        <v>3.22878479957581</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.08400011062622</v>
       </c>
       <c r="G129" t="n">
-        <v>3.28018808364868</v>
+        <v>3.28018879890442</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G130" t="n">
-        <v>3.30107116699219</v>
+        <v>3.30107140541077</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G131" t="n">
-        <v>3.26733732223511</v>
+        <v>3.26733756065369</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.93600010871887</v>
       </c>
       <c r="G134" t="n">
-        <v>3.16131782531738</v>
+        <v>3.16131806373596</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G136" t="n">
-        <v>3.09866976737976</v>
+        <v>3.09866952896118</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>3.07618069648743</v>
+        <v>3.07618093490601</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G140" t="n">
-        <v>3.02156472206116</v>
+        <v>3.021564245224</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.84800004959106</v>
       </c>
       <c r="G141" t="n">
-        <v>3.09063839912415</v>
+        <v>3.09063792228699</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G142" t="n">
-        <v>3.02959609031677</v>
+        <v>3.02959632873535</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G146" t="n">
-        <v>3.06975531578064</v>
+        <v>3.06975507736206</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4</v>
       </c>
       <c r="G147" t="n">
-        <v>3.21272134780884</v>
+        <v>3.21272110939026</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G148" t="n">
-        <v>3.25930595397949</v>
+        <v>3.25930571556091</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.07800006866455</v>
       </c>
       <c r="G149" t="n">
-        <v>3.27536940574646</v>
+        <v>3.27536916732788</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G150" t="n">
-        <v>3.30749654769897</v>
+        <v>3.30749678611755</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.0460000038147</v>
       </c>
       <c r="G153" t="n">
-        <v>3.24966740608215</v>
+        <v>3.24966788291931</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G154" t="n">
-        <v>3.19023251533508</v>
+        <v>3.1902322769165</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.33400011062622</v>
       </c>
       <c r="G161" t="n">
-        <v>3.48098397254944</v>
+        <v>3.48098349571228</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G162" t="n">
-        <v>3.50186610221863</v>
+        <v>3.50186657905579</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G164" t="n">
-        <v>3.53238725662231</v>
+        <v>3.53238701820374</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.49383473396301</v>
+        <v>3.49383425712585</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G166" t="n">
-        <v>3.51150465011597</v>
+        <v>3.51150393486023</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G168" t="n">
-        <v>3.56772708892822</v>
+        <v>3.5677273273468</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G169" t="n">
-        <v>3.53881216049194</v>
+        <v>3.53881287574768</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G170" t="n">
-        <v>3.60306715965271</v>
+        <v>3.60306739807129</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G171" t="n">
-        <v>3.57575917243958</v>
+        <v>3.575758934021</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G172" t="n">
-        <v>3.55166339874268</v>
+        <v>3.5516631603241</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G174" t="n">
-        <v>3.68499159812927</v>
+        <v>3.68499135971069</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.55399990081787</v>
       </c>
       <c r="G176" t="n">
-        <v>3.65768337249756</v>
+        <v>3.65768361091614</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G177" t="n">
-        <v>3.71069312095642</v>
+        <v>3.71069288253784</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.61800003051758</v>
       </c>
       <c r="G178" t="n">
-        <v>3.70908665657043</v>
+        <v>3.70908713340759</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G179" t="n">
-        <v>3.72354388237</v>
+        <v>3.72354412078857</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G180" t="n">
-        <v>3.67053437232971</v>
+        <v>3.67053389549255</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G181" t="n">
-        <v>3.83759522438049</v>
+        <v>3.83759570121765</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G182" t="n">
-        <v>3.72675609588623</v>
+        <v>3.72675681114197</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.78800010681152</v>
       </c>
       <c r="G184" t="n">
-        <v>3.84562754631042</v>
+        <v>3.845627784729</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.72399997711182</v>
       </c>
       <c r="G185" t="n">
-        <v>3.79422330856323</v>
+        <v>3.79422402381897</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G186" t="n">
-        <v>3.82313847541809</v>
+        <v>3.82313871383667</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>3.85526585578918</v>
+        <v>3.85526609420776</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.75</v>
       </c>
       <c r="G188" t="n">
-        <v>3.81510710716248</v>
+        <v>3.8151068687439</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G190" t="n">
-        <v>3.87614846229553</v>
+        <v>3.87614870071411</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G191" t="n">
-        <v>3.79261755943298</v>
+        <v>3.7926173210144</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G192" t="n">
-        <v>3.89381766319275</v>
+        <v>3.89381814002991</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G193" t="n">
-        <v>3.82313847541809</v>
+        <v>3.82313871383667</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G194" t="n">
-        <v>3.72675609588623</v>
+        <v>3.72675681114197</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G195" t="n">
-        <v>3.71069312095642</v>
+        <v>3.71069288253784</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.89381766319275</v>
+        <v>3.89381814002991</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.94399976730347</v>
       </c>
       <c r="G198" t="n">
-        <v>3.97092366218567</v>
+        <v>3.97092342376709</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>3.85526585578918</v>
+        <v>3.85526609420776</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.89542531967163</v>
+        <v>3.89542484283447</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G202" t="n">
-        <v>3.80064964294434</v>
+        <v>3.80064940452576</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>3.75085234642029</v>
+        <v>3.75085186958313</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G204" t="n">
-        <v>3.84402132034302</v>
+        <v>3.84402084350586</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G205" t="n">
-        <v>3.87132906913757</v>
+        <v>3.87132883071899</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G206" t="n">
-        <v>3.95485949516296</v>
+        <v>3.95485997200012</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G207" t="n">
-        <v>3.92273211479187</v>
+        <v>3.92273283004761</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90185022354126</v>
+        <v>3.90184998512268</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G209" t="n">
-        <v>3.92273211479187</v>
+        <v>3.92273283004761</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G210" t="n">
-        <v>3.87132906913757</v>
+        <v>3.87132883071899</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.89400005340576</v>
       </c>
       <c r="G211" t="n">
-        <v>3.93076515197754</v>
+        <v>3.9307644367218</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.98377442359924</v>
+        <v>3.9837749004364</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.86600017547607</v>
       </c>
       <c r="G213" t="n">
-        <v>3.90827488899231</v>
+        <v>3.90827512741089</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G215" t="n">
-        <v>3.94361543655396</v>
+        <v>3.94361591339111</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G216" t="n">
-        <v>3.96931624412537</v>
+        <v>3.96931743621826</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5</v>
       </c>
       <c r="G217" t="n">
-        <v>4.01590204238892</v>
+        <v>4.01590156555176</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G219" t="n">
-        <v>4.08818817138672</v>
+        <v>4.08818769454956</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>4.20063304901123</v>
+        <v>4.20063400268555</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G223" t="n">
-        <v>4.25284004211426</v>
+        <v>4.25283908843994</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>4.29701519012451</v>
+        <v>4.29701471328735</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>4.90341567993164</v>
+        <v>4.9034161567688</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G231" t="n">
-        <v>4.74679517745972</v>
+        <v>4.74679565429688</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>6</v>
       </c>
       <c r="G232" t="n">
-        <v>4.81908226013184</v>
+        <v>4.81908273696899</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G233" t="n">
-        <v>4.87530517578125</v>
+        <v>4.87530469894409</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G236" t="n">
-        <v>4.94357442855835</v>
+        <v>4.94357538223267</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>6.27500009536743</v>
       </c>
       <c r="G238" t="n">
-        <v>5.03995704650879</v>
+        <v>5.03995752334595</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G239" t="n">
-        <v>5.07610034942627</v>
+        <v>5.07609987258911</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G240" t="n">
-        <v>5.19256162643433</v>
+        <v>5.19256114959717</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G242" t="n">
-        <v>5.27287864685059</v>
+        <v>5.27287912368774</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G243" t="n">
-        <v>5.36524534225464</v>
+        <v>5.36524438858032</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G244" t="n">
-        <v>5.46564245223999</v>
+        <v>5.46564197540283</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G246" t="n">
-        <v>5.45359468460083</v>
+        <v>5.45359516143799</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G247" t="n">
-        <v>5.20862483978271</v>
+        <v>5.2086238861084</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G249" t="n">
-        <v>5.44957876205444</v>
+        <v>5.44957828521729</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>5.4937539100647</v>
+        <v>5.49375343322754</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G251" t="n">
-        <v>5.50178480148315</v>
+        <v>5.50178575515747</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>5.60619878768921</v>
+        <v>5.60619831085205</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G254" t="n">
-        <v>5.69856357574463</v>
+        <v>5.6985650062561</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>5.71864366531372</v>
+        <v>5.71864414215088</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G256" t="n">
-        <v>5.74675607681274</v>
+        <v>5.74675559997559</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G257" t="n">
-        <v>5.68250131607056</v>
+        <v>5.68249988555908</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G259" t="n">
-        <v>5.38130807876587</v>
+        <v>5.38130855560303</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G260" t="n">
-        <v>5.3893404006958</v>
+        <v>5.38933992385864</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G261" t="n">
-        <v>5.36926031112671</v>
+        <v>5.36926078796387</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>5.5058012008667</v>
+        <v>5.50580072402954</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>5.4616265296936</v>
+        <v>5.46162700653076</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G265" t="n">
-        <v>5.4937539100647</v>
+        <v>5.49375343322754</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G266" t="n">
-        <v>5.54240655899048</v>
+        <v>5.54240703582764</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>5.36401176452637</v>
+        <v>5.36401128768921</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G271" t="n">
-        <v>5.60322380065918</v>
+        <v>5.60322427749634</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G272" t="n">
-        <v>5.63565921783447</v>
+        <v>5.63565826416016</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G275" t="n">
-        <v>5.70052909851074</v>
+        <v>5.7005295753479</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>5.7451286315918</v>
+        <v>5.74512815475464</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>5.79783582687378</v>
+        <v>5.79783630371094</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G278" t="n">
-        <v>5.99244785308838</v>
+        <v>5.9924488067627</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G280" t="n">
-        <v>5.73701953887939</v>
+        <v>5.73701906204224</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G281" t="n">
-        <v>5.72080135345459</v>
+        <v>5.72080183029175</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G283" t="n">
-        <v>5.63160419464111</v>
+        <v>5.63160467147827</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>5.54240655899048</v>
+        <v>5.54240703582764</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G286" t="n">
-        <v>5.55051612854004</v>
+        <v>5.55051517486572</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G288" t="n">
-        <v>5.70863914489746</v>
+        <v>5.7086386680603</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G291" t="n">
-        <v>5.66809415817261</v>
+        <v>5.66809368133545</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G292" t="n">
-        <v>5.66809415817261</v>
+        <v>5.66809368133545</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G295" t="n">
-        <v>5.72080135345459</v>
+        <v>5.72080183029175</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G296" t="n">
-        <v>5.7410740852356</v>
+        <v>5.74107360839844</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G298" t="n">
-        <v>5.58700513839722</v>
+        <v>5.58700561523438</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G299" t="n">
-        <v>5.55051612854004</v>
+        <v>5.55051517486572</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.74499988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>5.46942758560181</v>
+        <v>5.46942663192749</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G301" t="n">
-        <v>5.53024339675903</v>
+        <v>5.53024387359619</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>6.75500011444092</v>
       </c>
       <c r="G302" t="n">
-        <v>5.47753620147705</v>
+        <v>5.47753667831421</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G304" t="n">
-        <v>5.44915533065796</v>
+        <v>5.44915390014648</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G305" t="n">
-        <v>5.44915533065796</v>
+        <v>5.44915390014648</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.74499988555908</v>
       </c>
       <c r="G306" t="n">
-        <v>5.46942758560181</v>
+        <v>5.46942663192749</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G311" t="n">
-        <v>5.44915533065796</v>
+        <v>5.44915390014648</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G314" t="n">
-        <v>5.18156242370605</v>
+        <v>5.1815619468689</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>6.25</v>
       </c>
       <c r="G315" t="n">
-        <v>5.06803798675537</v>
+        <v>5.06803846359253</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G320" t="n">
-        <v>5.01127624511719</v>
+        <v>5.01127672195435</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G321" t="n">
-        <v>5.05992889404297</v>
+        <v>5.05992984771729</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G322" t="n">
-        <v>5.08020114898682</v>
+        <v>5.08020162582397</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G323" t="n">
-        <v>5.25454139709473</v>
+        <v>5.25454235076904</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>5.30319499969482</v>
+        <v>5.30319547653198</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G326" t="n">
-        <v>5.58700513839722</v>
+        <v>5.58700561523438</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>5.6478214263916</v>
+        <v>5.64782238006592</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>5.50591707229614</v>
+        <v>5.5059175491333</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>5.62755012512207</v>
+        <v>5.62754917144775</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G333" t="n">
-        <v>5.67214870452881</v>
+        <v>5.67214822769165</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G334" t="n">
-        <v>5.66403961181641</v>
+        <v>5.66404008865356</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>5.7451286315918</v>
+        <v>5.74512815475464</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G338" t="n">
-        <v>5.72080135345459</v>
+        <v>5.72080183029175</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>5.83837985992432</v>
+        <v>5.83838033676147</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G341" t="n">
-        <v>5.78972721099854</v>
+        <v>5.78972768783569</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G343" t="n">
-        <v>5.93974018096924</v>
+        <v>5.93974113464355</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>5.75729179382324</v>
+        <v>5.75729131698608</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>5.96001291275024</v>
+        <v>5.96001386642456</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G350" t="n">
-        <v>6.0005578994751</v>
+        <v>6.00055646896362</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G352" t="n">
-        <v>6.06948232650757</v>
+        <v>6.06948280334473</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>7.5</v>
       </c>
       <c r="G353" t="n">
-        <v>6.08164644241333</v>
+        <v>6.08164548873901</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G354" t="n">
-        <v>6.10191822052002</v>
+        <v>6.10191869735718</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G355" t="n">
-        <v>6.07353639602661</v>
+        <v>6.07353687286377</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>6.01272058486938</v>
+        <v>6.01272106170654</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>6.02893877029419</v>
+        <v>6.02893829345703</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G360" t="n">
-        <v>5.87487030029297</v>
+        <v>5.87486982345581</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G361" t="n">
-        <v>5.94379568099976</v>
+        <v>5.94379615783691</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G362" t="n">
-        <v>5.98839473724365</v>
+        <v>5.98839426040649</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G363" t="n">
-        <v>6.0005578994751</v>
+        <v>6.00055646896362</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G364" t="n">
-        <v>6.07759189605713</v>
+        <v>6.07759094238281</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>6.04921054840088</v>
+        <v>6.04921102523804</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G366" t="n">
-        <v>5.95190477371216</v>
+        <v>5.951904296875</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>7.375</v>
       </c>
       <c r="G369" t="n">
-        <v>5.98028564453125</v>
+        <v>5.98028612136841</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G370" t="n">
-        <v>5.80594348907471</v>
+        <v>5.80594444274902</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.83837985992432</v>
+        <v>5.83838033676147</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G377" t="n">
-        <v>5.85459804534912</v>
+        <v>5.85459852218628</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G378" t="n">
-        <v>5.70052909851074</v>
+        <v>5.7005295753479</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>5.7451286315918</v>
+        <v>5.74512815475464</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G381" t="n">
-        <v>5.89514255523682</v>
+        <v>5.8951416015625</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>5.96001291275024</v>
+        <v>5.96001386642456</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G383" t="n">
-        <v>6.11813640594482</v>
+        <v>6.11813688278198</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G384" t="n">
-        <v>6.26815032958984</v>
+        <v>6.26814985275269</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.34500026702881</v>
       </c>
       <c r="G386" t="n">
-        <v>6.766845703125</v>
+        <v>6.76684522628784</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.35499954223633</v>
       </c>
       <c r="G389" t="n">
-        <v>6.77495288848877</v>
+        <v>6.77495336532593</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G391" t="n">
-        <v>6.63304805755615</v>
+        <v>6.63304853439331</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>6.64926624298096</v>
+        <v>6.64926671981812</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>8</v>
       </c>
       <c r="G393" t="n">
-        <v>6.48708915710449</v>
+        <v>6.48708868026733</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G394" t="n">
-        <v>6.57628679275513</v>
+        <v>6.57628631591797</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G395" t="n">
-        <v>6.46276235580444</v>
+        <v>6.46276187896729</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G397" t="n">
-        <v>6.32491159439087</v>
+        <v>6.32491207122803</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G398" t="n">
-        <v>6.41005516052246</v>
+        <v>6.4100546836853</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G401" t="n">
-        <v>6.53574275970459</v>
+        <v>6.53574228286743</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>6.4141092300415</v>
+        <v>6.41410875320435</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>8.07499980926514</v>
       </c>
       <c r="G406" t="n">
-        <v>6.54790592193604</v>
+        <v>6.54790544509888</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G407" t="n">
-        <v>6.33302021026611</v>
+        <v>6.33302068710327</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G409" t="n">
-        <v>6.43843555450439</v>
+        <v>6.43843650817871</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G410" t="n">
-        <v>6.50736141204834</v>
+        <v>6.50736093521118</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G411" t="n">
-        <v>6.4141092300415</v>
+        <v>6.41410875320435</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>6.45059967041016</v>
+        <v>6.45059871673584</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8</v>
       </c>
       <c r="G414" t="n">
-        <v>6.48708915710449</v>
+        <v>6.48708868026733</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>6.43438196182251</v>
+        <v>6.43438148498535</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8</v>
       </c>
       <c r="G417" t="n">
-        <v>6.48708915710449</v>
+        <v>6.48708868026733</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>6.49114370346069</v>
+        <v>6.49114465713501</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G420" t="n">
-        <v>6.7263011932373</v>
+        <v>6.72630071640015</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G422" t="n">
-        <v>6.77900743484497</v>
+        <v>6.77900791168213</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.07499980926514</v>
       </c>
       <c r="G427" t="n">
-        <v>6.54790592193604</v>
+        <v>6.54790544509888</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>6.59250450134277</v>
+        <v>6.59250402450562</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G432" t="n">
-        <v>7.30203008651733</v>
+        <v>7.30203056335449</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G433" t="n">
-        <v>7.31419372558594</v>
+        <v>7.31419324874878</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G434" t="n">
-        <v>7.34257411956787</v>
+        <v>7.34257364273071</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G435" t="n">
-        <v>7.31419372558594</v>
+        <v>7.31419324874878</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>7.33852005004883</v>
+        <v>7.33851957321167</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>7.33041191101074</v>
+        <v>7.33041095733643</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G438" t="n">
-        <v>7.5128607749939</v>
+        <v>7.51286029815674</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>7.81288814544678</v>
+        <v>7.81288862228394</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G440" t="n">
-        <v>7.62233066558838</v>
+        <v>7.6223292350769</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>9.5</v>
       </c>
       <c r="G441" t="n">
-        <v>7.70341920852661</v>
+        <v>7.70341873168945</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.5</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70341920852661</v>
+        <v>7.70341873168945</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66692781448364</v>
+        <v>7.6669282913208</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G444" t="n">
-        <v>7.52502202987671</v>
+        <v>7.52502298355103</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G447" t="n">
-        <v>7.78450775146484</v>
+        <v>7.78450679779053</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G448" t="n">
-        <v>7.44393491744995</v>
+        <v>7.44393587112427</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G449" t="n">
-        <v>7.15201616287231</v>
+        <v>7.15201568603516</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G450" t="n">
-        <v>7.27770376205444</v>
+        <v>7.27770280838013</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G452" t="n">
-        <v>7.00605583190918</v>
+        <v>7.00605726242065</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.75</v>
       </c>
       <c r="G453" t="n">
-        <v>7.09525394439697</v>
+        <v>7.09525346755981</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G454" t="n">
-        <v>7.28175687789917</v>
+        <v>7.28175640106201</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>7.33446502685547</v>
+        <v>7.33446550369263</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G456" t="n">
-        <v>7.43582677841187</v>
+        <v>7.43582630157471</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>8.83500003814697</v>
       </c>
       <c r="G457" t="n">
-        <v>7.16417932510376</v>
+        <v>7.1641788482666</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G458" t="n">
-        <v>7.05065536499023</v>
+        <v>7.05065488815308</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G460" t="n">
-        <v>7.15201616287231</v>
+        <v>7.15201568603516</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G461" t="n">
-        <v>7.24932193756104</v>
+        <v>7.24932146072388</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G462" t="n">
-        <v>7.20877742767334</v>
+        <v>7.2087779045105</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G463" t="n">
-        <v>7.07092714309692</v>
+        <v>7.07092761993408</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G465" t="n">
-        <v>6.90469598770142</v>
+        <v>6.90469551086426</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G470" t="n">
-        <v>6.62899541854858</v>
+        <v>6.62899446487427</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>6.45059967041016</v>
+        <v>6.45059871673584</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G472" t="n">
-        <v>6.56412363052368</v>
+        <v>6.564124584198</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>7.12363576889038</v>
+        <v>7.12363433837891</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G476" t="n">
-        <v>7.06281805038452</v>
+        <v>7.06281852722168</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>8.28499984741211</v>
       </c>
       <c r="G479" t="n">
-        <v>6.71819114685059</v>
+        <v>6.71819162368774</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G480" t="n">
-        <v>6.92496776580811</v>
+        <v>6.92496824264526</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>9</v>
       </c>
       <c r="G483" t="n">
-        <v>7.29797601699829</v>
+        <v>7.29797649383545</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9</v>
       </c>
       <c r="G484" t="n">
-        <v>7.29797601699829</v>
+        <v>7.29797649383545</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G485" t="n">
-        <v>7.17634248733521</v>
+        <v>7.17634296417236</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>7.13174390792847</v>
+        <v>7.13174343109131</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>7.22905015945435</v>
+        <v>7.22904968261719</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>8.8149995803833</v>
       </c>
       <c r="G489" t="n">
-        <v>7.1479606628418</v>
+        <v>7.14796161651611</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G490" t="n">
-        <v>7.78450775146484</v>
+        <v>7.78450679779053</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G491" t="n">
-        <v>8.08453464508057</v>
+        <v>8.0845365524292</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>7.97911930084229</v>
+        <v>7.97911977767944</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G493" t="n">
-        <v>8.25482177734375</v>
+        <v>8.25482273101807</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.26293182373047</v>
+        <v>8.26293087005615</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G496" t="n">
-        <v>7.99533843994141</v>
+        <v>7.99533700942993</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>8.10075283050537</v>
+        <v>8.10075187683105</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G498" t="n">
-        <v>8.02777194976807</v>
+        <v>8.02777290344238</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>7.94668483734131</v>
+        <v>7.94668292999268</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G500" t="n">
-        <v>8.05209922790527</v>
+        <v>8.05210018157959</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>8.03588199615479</v>
+        <v>8.03588104248047</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G502" t="n">
-        <v>8.06020832061768</v>
+        <v>8.06020736694336</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G503" t="n">
-        <v>7.99939155578613</v>
+        <v>7.99939107894897</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G507" t="n">
-        <v>8.20616722106934</v>
+        <v>8.20616817474365</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G509" t="n">
-        <v>8.25482177734375</v>
+        <v>8.25482273101807</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>10.0900001525879</v>
       </c>
       <c r="G510" t="n">
-        <v>8.18184185028076</v>
+        <v>8.18184089660645</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G511" t="n">
-        <v>8.32780265808105</v>
+        <v>8.32780170440674</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G513" t="n">
-        <v>8.63593864440918</v>
+        <v>8.63593769073486</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G514" t="n">
-        <v>8.84676837921143</v>
+        <v>8.84676742553711</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G515" t="n">
-        <v>8.55484867095947</v>
+        <v>8.55484962463379</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G516" t="n">
-        <v>8.66837310791016</v>
+        <v>8.66837215423584</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G517" t="n">
-        <v>8.50619411468506</v>
+        <v>8.50619506835938</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G518" t="n">
-        <v>8.67648220062256</v>
+        <v>8.67648124694824</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G519" t="n">
-        <v>8.70891761779785</v>
+        <v>8.70891666412354</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G523" t="n">
-        <v>8.27914810180664</v>
+        <v>8.27914714813232</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G530" t="n">
-        <v>8.09916496276855</v>
+        <v>8.09916591644287</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G531" t="n">
-        <v>8.16052436828613</v>
+        <v>8.1605224609375</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G532" t="n">
-        <v>8.19733715057373</v>
+        <v>8.19733810424805</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G533" t="n">
-        <v>8.26278591156006</v>
+        <v>8.26278686523438</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G535" t="n">
-        <v>8.68819713592529</v>
+        <v>8.68819618225098</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G536" t="n">
-        <v>8.72091960906982</v>
+        <v>8.72092056274414</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G539" t="n">
-        <v>8.68819713592529</v>
+        <v>8.68819618225098</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>8.67183589935303</v>
+        <v>8.67183399200439</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G541" t="n">
-        <v>8.65547180175781</v>
+        <v>8.65547275543213</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G542" t="n">
-        <v>8.66365242004395</v>
+        <v>8.66365337371826</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G543" t="n">
-        <v>8.70455932617188</v>
+        <v>8.70455837249756</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G545" t="n">
-        <v>8.35277652740479</v>
+        <v>8.35277557373047</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>8.46730995178223</v>
+        <v>8.46731090545654</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G548" t="n">
-        <v>8.46730995178223</v>
+        <v>8.46731090545654</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G551" t="n">
-        <v>8.32005214691162</v>
+        <v>8.32005310058594</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G552" t="n">
-        <v>8.16052436828613</v>
+        <v>8.1605224609375</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>8.30368900299072</v>
+        <v>8.30368995666504</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G557" t="n">
-        <v>8.34459400177002</v>
+        <v>8.34459495544434</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G558" t="n">
-        <v>8.35277652740479</v>
+        <v>8.35277557373047</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G559" t="n">
-        <v>8.21370029449463</v>
+        <v>8.21369934082031</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>7.94372653961182</v>
+        <v>7.94372606277466</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G563" t="n">
-        <v>8.32005214691162</v>
+        <v>8.32005310058594</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G564" t="n">
-        <v>8.44276714324951</v>
+        <v>8.44276809692383</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>8.26278591156006</v>
+        <v>8.26278686523438</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G569" t="n">
-        <v>8.01735591888428</v>
+        <v>8.01735496520996</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>9.75</v>
       </c>
       <c r="G570" t="n">
-        <v>7.97645235061646</v>
+        <v>7.97645139694214</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G571" t="n">
-        <v>7.85373735427856</v>
+        <v>7.85373640060425</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G573" t="n">
-        <v>7.64921188354492</v>
+        <v>7.6492133140564</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>7.71057033538818</v>
+        <v>7.71056938171387</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G578" t="n">
-        <v>7.72284126281738</v>
+        <v>7.72284078598022</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>9.29500007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>7.60421800613403</v>
+        <v>7.60421657562256</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>7.53467893600464</v>
+        <v>7.53467845916748</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.15499973297119</v>
       </c>
       <c r="G581" t="n">
-        <v>7.48968315124512</v>
+        <v>7.48968267440796</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G582" t="n">
-        <v>7.73102140426636</v>
+        <v>7.73102188110352</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G583" t="n">
-        <v>7.58376598358154</v>
+        <v>7.5837664604187</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G584" t="n">
-        <v>7.45695924758911</v>
+        <v>7.45695972442627</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G585" t="n">
-        <v>7.43650817871094</v>
+        <v>7.43650770187378</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G586" t="n">
-        <v>7.69011735916138</v>
+        <v>7.69011640548706</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>7.49786424636841</v>
+        <v>7.49786472320557</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G589" t="n">
-        <v>7.70238828659058</v>
+        <v>7.70238733291626</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>9.35499954223633</v>
       </c>
       <c r="G590" t="n">
-        <v>7.65330171585083</v>
+        <v>7.65330362319946</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G591" t="n">
-        <v>7.48150205612183</v>
+        <v>7.48150110244751</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G592" t="n">
-        <v>7.57558441162109</v>
+        <v>7.57558393478394</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G594" t="n">
-        <v>7.55103969573975</v>
+        <v>7.5510401725769</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>8.75</v>
       </c>
       <c r="G596" t="n">
-        <v>7.15835380554199</v>
+        <v>7.15835332870483</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>7.01927757263184</v>
+        <v>7.01927709579468</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G598" t="n">
-        <v>7.0642728805542</v>
+        <v>7.06427335739136</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G599" t="n">
-        <v>7.33833456039429</v>
+        <v>7.33833503723145</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G600" t="n">
-        <v>7.52649688720703</v>
+        <v>7.52649736404419</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G601" t="n">
-        <v>7.90282201766968</v>
+        <v>7.90282344818115</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G604" t="n">
-        <v>7.94372653961182</v>
+        <v>7.94372606277466</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10</v>
       </c>
       <c r="G605" t="n">
-        <v>8.18097591400146</v>
+        <v>8.18097686767578</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G606" t="n">
-        <v>8.05826091766357</v>
+        <v>8.05826187133789</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G607" t="n">
-        <v>8.08689498901367</v>
+        <v>8.08689403533936</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G608" t="n">
-        <v>8.23006248474121</v>
+        <v>8.23006057739258</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G610" t="n">
-        <v>8.26278591156006</v>
+        <v>8.26278686523438</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G612" t="n">
-        <v>8.89272022247314</v>
+        <v>8.89271926879883</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G614" t="n">
-        <v>8.85181522369385</v>
+        <v>8.85181617736816</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G615" t="n">
-        <v>8.84363460540771</v>
+        <v>8.84363651275635</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G617" t="n">
-        <v>8.647292137146</v>
+        <v>8.64729118347168</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G620" t="n">
-        <v>8.8599967956543</v>
+        <v>8.85999584197998</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G624" t="n">
-        <v>8.4182243347168</v>
+        <v>8.41822338104248</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>7.87828016281128</v>
+        <v>7.8782787322998</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>9.60499954223633</v>
       </c>
       <c r="G628" t="n">
-        <v>7.85782766342163</v>
+        <v>7.85782623291016</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G630" t="n">
-        <v>8.19733715057373</v>
+        <v>8.19733810424805</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G631" t="n">
-        <v>7.90282201766968</v>
+        <v>7.90282344818115</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.29500007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>7.60421800613403</v>
+        <v>7.60421657562256</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G638" t="n">
-        <v>8.12370777130127</v>
+        <v>8.1237096786499</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>7.935546875</v>
+        <v>7.93554735183716</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G640" t="n">
-        <v>7.90282201766968</v>
+        <v>7.90282344818115</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G641" t="n">
-        <v>8.13597965240479</v>
+        <v>8.1359806060791</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G647" t="n">
-        <v>8.21370029449463</v>
+        <v>8.21369934082031</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G648" t="n">
-        <v>7.85373735427856</v>
+        <v>7.85373640060425</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G649" t="n">
-        <v>8.05826091766357</v>
+        <v>8.05826187133789</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G650" t="n">
-        <v>7.99281454086304</v>
+        <v>7.99281406402588</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>9.69499969482422</v>
       </c>
       <c r="G652" t="n">
-        <v>7.93145513534546</v>
+        <v>7.93145561218262</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G653" t="n">
-        <v>7.86191701889038</v>
+        <v>7.86191749572754</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G654" t="n">
-        <v>7.40787410736084</v>
+        <v>7.40787315368652</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G655" t="n">
-        <v>7.58376598358154</v>
+        <v>7.5837664604187</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G656" t="n">
-        <v>7.69011735916138</v>
+        <v>7.69011640548706</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>9.625</v>
       </c>
       <c r="G657" t="n">
-        <v>7.87418842315674</v>
+        <v>7.8741888999939</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G661" t="n">
-        <v>7.935546875</v>
+        <v>7.93554735183716</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G662" t="n">
-        <v>8.05417060852051</v>
+        <v>8.05416965484619</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>8.04599094390869</v>
+        <v>8.04598999023438</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G667" t="n">
-        <v>8.03371906280518</v>
+        <v>8.03371810913086</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G669" t="n">
-        <v>7.80465030670166</v>
+        <v>7.80465126037598</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G670" t="n">
-        <v>7.86191701889038</v>
+        <v>7.86191749572754</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>9.91499996185303</v>
       </c>
       <c r="G672" t="n">
-        <v>8.11143684387207</v>
+        <v>8.11143779754639</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G673" t="n">
-        <v>7.83328485488892</v>
+        <v>7.83328437805176</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G674" t="n">
-        <v>7.52649688720703</v>
+        <v>7.52649736404419</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G675" t="n">
-        <v>7.7514762878418</v>
+        <v>7.75147581100464</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G676" t="n">
-        <v>7.73102140426636</v>
+        <v>7.73102188110352</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>9.38500022888184</v>
       </c>
       <c r="G677" t="n">
-        <v>7.67784547805786</v>
+        <v>7.67784595489502</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G678" t="n">
-        <v>7.49377393722534</v>
+        <v>7.49377298355103</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G679" t="n">
-        <v>7.65739297866821</v>
+        <v>7.65739250183105</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>9.3100004196167</v>
       </c>
       <c r="G680" t="n">
-        <v>7.61648893356323</v>
+        <v>7.61648988723755</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>9.29500007629395</v>
       </c>
       <c r="G681" t="n">
-        <v>7.60421800613403</v>
+        <v>7.60421657562256</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>9.53999996185303</v>
       </c>
       <c r="G682" t="n">
-        <v>7.80465030670166</v>
+        <v>7.80465126037598</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G683" t="n">
-        <v>8.07462310791016</v>
+        <v>8.07462215423584</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G684" t="n">
-        <v>8.05826091766357</v>
+        <v>8.05826187133789</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>9.99499988555908</v>
       </c>
       <c r="G685" t="n">
-        <v>8.17688369750977</v>
+        <v>8.17688465118408</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G686" t="n">
-        <v>8.06644248962402</v>
+        <v>8.06644153594971</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G687" t="n">
-        <v>8.03780746459961</v>
+        <v>8.03780841827393</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G688" t="n">
-        <v>8.01735591888428</v>
+        <v>8.01735496520996</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G689" t="n">
-        <v>8.05417060852051</v>
+        <v>8.05416965484619</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>9.77000045776367</v>
       </c>
       <c r="G690" t="n">
-        <v>7.99281454086304</v>
+        <v>7.99281406402588</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G692" t="n">
-        <v>8.23006248474121</v>
+        <v>8.23006057739258</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G693" t="n">
-        <v>8.13597965240479</v>
+        <v>8.1359806060791</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>8.03780746459961</v>
+        <v>8.03780841827393</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G695" t="n">
-        <v>8.05008125305176</v>
+        <v>8.05008029937744</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G699" t="n">
-        <v>8.46730995178223</v>
+        <v>8.46731090545654</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G702" t="n">
-        <v>8.23824119567871</v>
+        <v>8.23824024200439</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G703" t="n">
-        <v>8.34459400177002</v>
+        <v>8.34459495544434</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G704" t="n">
-        <v>8.47549057006836</v>
+        <v>8.47549152374268</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G705" t="n">
-        <v>8.647292137146</v>
+        <v>8.64729118347168</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G707" t="n">
-        <v>8.32005214691162</v>
+        <v>8.32005310058594</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G709" t="n">
-        <v>8.34459400177002</v>
+        <v>8.34459495544434</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G713" t="n">
-        <v>8.68001365661621</v>
+        <v>8.68001461029053</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G715" t="n">
-        <v>8.68001365661621</v>
+        <v>8.68001461029053</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G716" t="n">
-        <v>8.647292137146</v>
+        <v>8.64729118347168</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G717" t="n">
-        <v>8.66365242004395</v>
+        <v>8.66365337371826</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>8.71273994445801</v>
+        <v>8.71273899078369</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G719" t="n">
-        <v>8.8599967956543</v>
+        <v>8.85999584197998</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G720" t="n">
-        <v>9.34267520904541</v>
+        <v>9.34267330169678</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G722" t="n">
-        <v>9.39175891876221</v>
+        <v>9.39175987243652</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G723" t="n">
-        <v>9.424485206604</v>
+        <v>9.42448425292969</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G724" t="n">
-        <v>9.37539863586426</v>
+        <v>9.37539768218994</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G725" t="n">
-        <v>9.22814083099365</v>
+        <v>9.22814178466797</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>9.12178802490234</v>
+        <v>9.12178611755371</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G727" t="n">
-        <v>9.12996864318848</v>
+        <v>9.12996768951416</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>9.12178802490234</v>
+        <v>9.12178611755371</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>9.3263111114502</v>
+        <v>9.32631301879883</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>9.3263111114502</v>
+        <v>9.32631301879883</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G732" t="n">
-        <v>9.18723487854004</v>
+        <v>9.18723583221436</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>9.3263111114502</v>
+        <v>9.32631301879883</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>8.87635803222656</v>
+        <v>8.87635898590088</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>9.12178802490234</v>
+        <v>9.12178611755371</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G741" t="n">
-        <v>8.80272960662842</v>
+        <v>8.80273056030273</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G742" t="n">
-        <v>8.97453117370605</v>
+        <v>8.97453212738037</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>8.67183589935303</v>
+        <v>8.67183399200439</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G744" t="n">
-        <v>8.84363460540771</v>
+        <v>8.84363651275635</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>11</v>
       </c>
       <c r="G745" t="n">
-        <v>8.99907302856445</v>
+        <v>8.99907398223877</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G746" t="n">
-        <v>8.90908241271973</v>
+        <v>8.90908336639404</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G747" t="n">
-        <v>8.89272022247314</v>
+        <v>8.89271926879883</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G748" t="n">
-        <v>8.8599967956543</v>
+        <v>8.85999584197998</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>8.46730995178223</v>
+        <v>8.46731090545654</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G751" t="n">
-        <v>8.49185180664062</v>
+        <v>8.49185276031494</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G752" t="n">
-        <v>8.68819713592529</v>
+        <v>8.68819618225098</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G753" t="n">
-        <v>8.68819713592529</v>
+        <v>8.68819618225098</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>8.87635803222656</v>
+        <v>8.87635898590088</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G758" t="n">
-        <v>8.90090274810791</v>
+        <v>8.90090084075928</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G761" t="n">
-        <v>8.90090274810791</v>
+        <v>8.90090084075928</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G762" t="n">
-        <v>8.94180679321289</v>
+        <v>8.94180774688721</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G763" t="n">
-        <v>8.78636837005615</v>
+        <v>8.78636741638184</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G764" t="n">
-        <v>8.75364398956299</v>
+        <v>8.75364303588867</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>8.46730995178223</v>
+        <v>8.46731090545654</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>8.46730995178223</v>
+        <v>8.46731090545654</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G768" t="n">
-        <v>8.34459400177002</v>
+        <v>8.34459495544434</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>8.34459400177002</v>
+        <v>8.34459495544434</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G770" t="n">
-        <v>8.03371906280518</v>
+        <v>8.03371810913086</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G774" t="n">
-        <v>8.66365242004395</v>
+        <v>8.66365337371826</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G775" t="n">
-        <v>8.6802978515625</v>
+        <v>8.68029880523682</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G776" t="n">
-        <v>8.4972038269043</v>
+        <v>8.49720573425293</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G777" t="n">
-        <v>8.43062591552734</v>
+        <v>8.43062496185303</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>10</v>
       </c>
       <c r="G778" t="n">
-        <v>8.32243251800537</v>
+        <v>8.32243347167969</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G779" t="n">
-        <v>8.57210731506348</v>
+        <v>8.57210636138916</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G780" t="n">
-        <v>8.4389476776123</v>
+        <v>8.43894863128662</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>8.82178020477295</v>
+        <v>8.82177925109863</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G782" t="n">
-        <v>8.57210731506348</v>
+        <v>8.57210636138916</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G783" t="n">
-        <v>8.6802978515625</v>
+        <v>8.68029880523682</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G788" t="n">
-        <v>8.4389476776123</v>
+        <v>8.43894863128662</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G792" t="n">
-        <v>8.2308874130249</v>
+        <v>8.23088645935059</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G794" t="n">
-        <v>8.2766580581665</v>
+        <v>8.27665996551514</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G795" t="n">
-        <v>8.15598583221436</v>
+        <v>8.15598392486572</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>9.75</v>
       </c>
       <c r="G796" t="n">
-        <v>8.11437129974365</v>
+        <v>8.11437320709229</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>9.84500026702881</v>
       </c>
       <c r="G797" t="n">
-        <v>8.19343566894531</v>
+        <v>8.19343662261963</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>9.90499973297119</v>
       </c>
       <c r="G798" t="n">
-        <v>8.24337005615234</v>
+        <v>8.24336910247803</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>8.18511295318604</v>
+        <v>8.18511390686035</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G802" t="n">
-        <v>8.13933849334717</v>
+        <v>8.1393404006958</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G803" t="n">
-        <v>8.12269401550293</v>
+        <v>8.12269496917725</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G804" t="n">
-        <v>8.14766216278076</v>
+        <v>8.14766120910645</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G805" t="n">
-        <v>7.91463327407837</v>
+        <v>7.914635181427</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>9.5649995803833</v>
       </c>
       <c r="G806" t="n">
-        <v>7.96040773391724</v>
+        <v>7.96040678024292</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G808" t="n">
-        <v>8.59707450866699</v>
+        <v>8.59707260131836</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>10</v>
       </c>
       <c r="G809" t="n">
-        <v>8.32243251800537</v>
+        <v>8.32243347167969</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>9.96500015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>8.29330539703369</v>
+        <v>8.29330444335938</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G812" t="n">
-        <v>8.17679119110107</v>
+        <v>8.17679214477539</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G813" t="n">
-        <v>8.30162715911865</v>
+        <v>8.30162811279297</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G814" t="n">
-        <v>8.4389476776123</v>
+        <v>8.43894863128662</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G816" t="n">
-        <v>8.37236785888672</v>
+        <v>8.37236881256104</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G818" t="n">
-        <v>8.41398048400879</v>
+        <v>8.41397953033447</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G823" t="n">
-        <v>8.37236785888672</v>
+        <v>8.37236881256104</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G824" t="n">
-        <v>8.42230224609375</v>
+        <v>8.42230319976807</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>9.75</v>
       </c>
       <c r="G827" t="n">
-        <v>8.11437129974365</v>
+        <v>8.11437320709229</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G828" t="n">
-        <v>8.21008110046387</v>
+        <v>8.21008014678955</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>9.57999992370605</v>
       </c>
       <c r="G830" t="n">
-        <v>7.97289228439331</v>
+        <v>7.97289180755615</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G831" t="n">
-        <v>7.8896656036377</v>
+        <v>7.88966655731201</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G834" t="n">
-        <v>7.98953628540039</v>
+        <v>7.98953723907471</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G835" t="n">
-        <v>7.82308721542358</v>
+        <v>7.82308673858643</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G836" t="n">
-        <v>7.76066923141479</v>
+        <v>7.76066970825195</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>7.66079902648926</v>
+        <v>7.66079998016357</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G838" t="n">
-        <v>7.68992853164673</v>
+        <v>7.68992805480957</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G839" t="n">
-        <v>7.5983829498291</v>
+        <v>7.59838199615479</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G840" t="n">
-        <v>7.59005975723267</v>
+        <v>7.59005880355835</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G843" t="n">
-        <v>8.08108329772949</v>
+        <v>8.08108234405518</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>8.08108329772949</v>
+        <v>8.08108234405518</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G846" t="n">
-        <v>7.58589792251587</v>
+        <v>7.58589887619019</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G847" t="n">
-        <v>7.81476449966431</v>
+        <v>7.81476545333862</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G848" t="n">
-        <v>7.66079902648926</v>
+        <v>7.66079998016357</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G850" t="n">
-        <v>7.58173656463623</v>
+        <v>7.58173608779907</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G851" t="n">
-        <v>7.58589792251587</v>
+        <v>7.58589887619019</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G852" t="n">
-        <v>7.5983829498291</v>
+        <v>7.59838199615479</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>7.52347898483276</v>
+        <v>7.52347993850708</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G855" t="n">
-        <v>7.57341527938843</v>
+        <v>7.57341480255127</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G856" t="n">
-        <v>8.13933849334717</v>
+        <v>8.1393404006958</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>8.17679119110107</v>
+        <v>8.17679214477539</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G858" t="n">
-        <v>8.50552654266357</v>
+        <v>8.50552749633789</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G860" t="n">
-        <v>8.2766580581665</v>
+        <v>8.27665996551514</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G861" t="n">
-        <v>8.1684684753418</v>
+        <v>8.16846752166748</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G862" t="n">
-        <v>8.28082084655762</v>
+        <v>8.2808198928833</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>9.72500038146973</v>
       </c>
       <c r="G865" t="n">
-        <v>8.09356594085693</v>
+        <v>8.09356689453125</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G866" t="n">
-        <v>8.0727596282959</v>
+        <v>8.07276058197021</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G867" t="n">
-        <v>8.31411075592041</v>
+        <v>8.31410980224609</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G868" t="n">
-        <v>8.38068962097168</v>
+        <v>8.380690574646</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G880" t="n">
-        <v>8.85507011413574</v>
+        <v>8.85506916046143</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G881" t="n">
-        <v>8.6802978515625</v>
+        <v>8.68029880523682</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G882" t="n">
-        <v>8.73023223876953</v>
+        <v>8.73023319244385</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G883" t="n">
-        <v>8.74687671661377</v>
+        <v>8.74687767028809</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G884" t="n">
-        <v>8.76352310180664</v>
+        <v>8.76352214813232</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G886" t="n">
-        <v>8.38068962097168</v>
+        <v>8.380690574646</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G888" t="n">
-        <v>8.0727596282959</v>
+        <v>8.07276058197021</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>8.04363059997559</v>
+        <v>8.04363250732422</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G893" t="n">
-        <v>8.1684684753418</v>
+        <v>8.16846752166748</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G895" t="n">
-        <v>8.31411075592041</v>
+        <v>8.31410980224609</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>10</v>
       </c>
       <c r="G897" t="n">
-        <v>8.32243251800537</v>
+        <v>8.32243347167969</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G898" t="n">
-        <v>8.3474006652832</v>
+        <v>8.34739971160889</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G899" t="n">
-        <v>8.41398048400879</v>
+        <v>8.41397953033447</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G900" t="n">
-        <v>8.60539627075195</v>
+        <v>8.60539817810059</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G901" t="n">
-        <v>8.65532970428467</v>
+        <v>8.65533065795898</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G904" t="n">
-        <v>8.38901424407959</v>
+        <v>8.38901329040527</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G905" t="n">
-        <v>8.43062591552734</v>
+        <v>8.43062496185303</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G906" t="n">
-        <v>8.53881645202637</v>
+        <v>8.53881740570068</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G907" t="n">
-        <v>8.52217102050781</v>
+        <v>8.52217197418213</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G909" t="n">
-        <v>8.6802978515625</v>
+        <v>8.68029880523682</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>8.86339092254639</v>
+        <v>8.8633918762207</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G911" t="n">
-        <v>9.12138557434082</v>
+        <v>9.12138652801514</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G912" t="n">
-        <v>9.4043493270874</v>
+        <v>9.40435028076172</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G913" t="n">
-        <v>9.30448055267334</v>
+        <v>9.30448246002197</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G914" t="n">
-        <v>9.25454521179199</v>
+        <v>9.25454616546631</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G916" t="n">
-        <v>9.25454521179199</v>
+        <v>9.25454616546631</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G917" t="n">
-        <v>9.43764114379883</v>
+        <v>9.4376392364502</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G919" t="n">
-        <v>9.4043493270874</v>
+        <v>9.40435028076172</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>9.4043493270874</v>
+        <v>9.40435028076172</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>11.25</v>
       </c>
       <c r="G921" t="n">
-        <v>9.36273670196533</v>
+        <v>9.36273765563965</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G922" t="n">
-        <v>9.46260738372803</v>
+        <v>9.46260643005371</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G924" t="n">
-        <v>9.57912158966064</v>
+        <v>9.57911968231201</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G927" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G934" t="n">
-        <v>9.84543895721436</v>
+        <v>9.84543800354004</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G935" t="n">
-        <v>9.9536304473877</v>
+        <v>9.95363140106201</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G937" t="n">
-        <v>9.83711528778076</v>
+        <v>9.83711624145508</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G940" t="n">
-        <v>9.99524211883545</v>
+        <v>9.99524307250977</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G942" t="n">
-        <v>9.97859668731689</v>
+        <v>9.97859764099121</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G943" t="n">
-        <v>10.0784673690796</v>
+        <v>10.0784664154053</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>10.0701446533203</v>
+        <v>10.0701456069946</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G947" t="n">
-        <v>9.87040519714355</v>
+        <v>9.87040710449219</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G950" t="n">
-        <v>9.77053642272949</v>
+        <v>9.77053737640381</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>9.82047271728516</v>
+        <v>9.82047176361084</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G954" t="n">
-        <v>9.46260738372803</v>
+        <v>9.46260643005371</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G955" t="n">
-        <v>9.87872886657715</v>
+        <v>9.87872791290283</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G956" t="n">
-        <v>9.82047271728516</v>
+        <v>9.82047176361084</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G961" t="n">
-        <v>9.82047271728516</v>
+        <v>9.82047176361084</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G963" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G964" t="n">
-        <v>9.4709300994873</v>
+        <v>9.47092914581299</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G965" t="n">
-        <v>9.37938213348389</v>
+        <v>9.3793830871582</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G966" t="n">
-        <v>9.4043493270874</v>
+        <v>9.40435028076172</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G967" t="n">
-        <v>9.30448055267334</v>
+        <v>9.30448246002197</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G968" t="n">
-        <v>9.12970924377441</v>
+        <v>9.12971019744873</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G969" t="n">
-        <v>8.42230224609375</v>
+        <v>8.42230319976807</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G970" t="n">
-        <v>8.0186653137207</v>
+        <v>8.01866436004639</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G971" t="n">
-        <v>8.17262935638428</v>
+        <v>8.17262840270996</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G972" t="n">
-        <v>7.87302160263062</v>
+        <v>7.87302207946777</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G973" t="n">
-        <v>7.86053800582886</v>
+        <v>7.8605375289917</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G974" t="n">
-        <v>7.56925392150879</v>
+        <v>7.56925344467163</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>7.76066923141479</v>
+        <v>7.76066970825195</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G976" t="n">
-        <v>7.46522283554077</v>
+        <v>7.46522331237793</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>8.72500038146973</v>
       </c>
       <c r="G977" t="n">
-        <v>7.26132345199585</v>
+        <v>7.26132297515869</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G978" t="n">
-        <v>7.16145324707031</v>
+        <v>7.16145372390747</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G980" t="n">
-        <v>6.59136772155762</v>
+        <v>6.59136724472046</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>7.80499982833862</v>
       </c>
       <c r="G981" t="n">
-        <v>6.49565935134888</v>
+        <v>6.49565887451172</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G984" t="n">
-        <v>4.89359045028687</v>
+        <v>4.89359140396118</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G986" t="n">
-        <v>4.93520259857178</v>
+        <v>4.93520355224609</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G988" t="n">
-        <v>5.52609586715698</v>
+        <v>5.52609539031982</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G989" t="n">
-        <v>5.49280595779419</v>
+        <v>5.49280643463135</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>6.5</v>
       </c>
       <c r="G991" t="n">
-        <v>5.40958118438721</v>
+        <v>5.40958213806152</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>5.16823148727417</v>
+        <v>5.16823053359985</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G993" t="n">
-        <v>4.89359045028687</v>
+        <v>4.89359140396118</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G999" t="n">
-        <v>5.18071508407593</v>
+        <v>5.18071460723877</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1000" t="n">
-        <v>5.31803464889526</v>
+        <v>5.31803512573242</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1002" t="n">
-        <v>5.1099739074707</v>
+        <v>5.10997438430786</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1003" t="n">
-        <v>5.1099739074707</v>
+        <v>5.10997438430786</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G1005" t="n">
-        <v>5.07252264022827</v>
+        <v>5.07252311706543</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G1006" t="n">
-        <v>5.07252264022827</v>
+        <v>5.07252311706543</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G1012" t="n">
-        <v>5.63428783416748</v>
+        <v>5.63428735733032</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>5.60099792480469</v>
+        <v>5.60099744796753</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.43454885482788</v>
+        <v>5.43454933166504</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1018" t="n">
-        <v>5.49280595779419</v>
+        <v>5.49280643463135</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.76744651794434</v>
+        <v>5.76744604110718</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G1022" t="n">
-        <v>6.02128076553345</v>
+        <v>6.02128028869629</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1025" t="n">
-        <v>5.57602977752686</v>
+        <v>5.57603025436401</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G1028" t="n">
-        <v>5.65093278884888</v>
+        <v>5.65093231201172</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G1029" t="n">
-        <v>5.56354665756226</v>
+        <v>5.5635461807251</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1030" t="n">
-        <v>5.55106258392334</v>
+        <v>5.55106353759766</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>7.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.24182510375977</v>
+        <v>6.24182462692261</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1035" t="n">
-        <v>6.17940664291382</v>
+        <v>6.17940711975098</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.6704306602478</v>
+        <v>6.67043113708496</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1038" t="n">
-        <v>6.82439565658569</v>
+        <v>6.82439517974854</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G1039" t="n">
-        <v>6.78694438934326</v>
+        <v>6.78694343566895</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1041" t="n">
-        <v>7.11984157562256</v>
+        <v>7.11984205245972</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>6.59136772155762</v>
+        <v>6.59136724472046</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G1045" t="n">
-        <v>6.58720636367798</v>
+        <v>6.58720588684082</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.4582085609436</v>
+        <v>6.45820903778076</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G1047" t="n">
-        <v>6.5955286026001</v>
+        <v>6.59552812576294</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.6080117225647</v>
+        <v>6.60801267623901</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G1049" t="n">
-        <v>6.57888412475586</v>
+        <v>6.5788836479187</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>6.52478790283203</v>
+        <v>6.52478742599487</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1051" t="n">
-        <v>6.43324041366577</v>
+        <v>6.43324136734009</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>6.49149799346924</v>
+        <v>6.4914984703064</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.21269702911377</v>
+        <v>6.21269655227661</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G1056" t="n">
-        <v>6.03792524337769</v>
+        <v>6.03792572021484</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>6.17524528503418</v>
+        <v>6.17524576187134</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.04208707809448</v>
+        <v>6.04208660125732</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>7.45499992370605</v>
       </c>
       <c r="G1061" t="n">
-        <v>6.20437383651733</v>
+        <v>6.20437431335449</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G1065" t="n">
-        <v>5.93805694580078</v>
+        <v>5.93805646896362</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.13363361358643</v>
+        <v>6.13363313674927</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>7.5</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.24182510375977</v>
+        <v>6.24182462692261</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1071" t="n">
-        <v>6.17524528503418</v>
+        <v>6.17524576187134</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1072" t="n">
-        <v>6.49149799346924</v>
+        <v>6.4914984703064</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>7.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.24182510375977</v>
+        <v>6.24182462692261</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1075" t="n">
-        <v>6.1586012840271</v>
+        <v>6.15860033035278</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.95470142364502</v>
+        <v>5.95470190048218</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>7.34499979019165</v>
       </c>
       <c r="G1078" t="n">
-        <v>6.11282682418823</v>
+        <v>6.11282777786255</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>7.25</v>
       </c>
       <c r="G1079" t="n">
-        <v>6.03376483917236</v>
+        <v>6.03376388549805</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G1081" t="n">
-        <v>5.84650993347168</v>
+        <v>5.84650945663452</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.91308927536011</v>
+        <v>5.91308975219727</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.89228296279907</v>
+        <v>5.89228343963623</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.27095365524292</v>
+        <v>6.27095413208008</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G1088" t="n">
-        <v>6.21685743331909</v>
+        <v>6.21685695648193</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1089" t="n">
-        <v>6.20853567123413</v>
+        <v>6.20853519439697</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.13363361358643</v>
+        <v>6.13363313674927</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.12531089782715</v>
+        <v>6.12531137466431</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G1093" t="n">
-        <v>6.02128076553345</v>
+        <v>6.02128028869629</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1095" t="n">
-        <v>6.04208707809448</v>
+        <v>6.04208660125732</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G1096" t="n">
-        <v>6.14611768722534</v>
+        <v>6.14611721038818</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>7.40500020980835</v>
       </c>
       <c r="G1097" t="n">
-        <v>6.16276216506958</v>
+        <v>6.16276168823242</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G1098" t="n">
-        <v>6.14611768722534</v>
+        <v>6.14611721038818</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>6.12114953994751</v>
+        <v>6.12115001678467</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G1101" t="n">
-        <v>6.27095365524292</v>
+        <v>6.27095413208008</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G1102" t="n">
-        <v>6.25847053527832</v>
+        <v>6.25847005844116</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G1103" t="n">
-        <v>6.51646566390991</v>
+        <v>6.51646518707275</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G1107" t="n">
-        <v>7.16561460494995</v>
+        <v>7.16561508178711</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.84936237335205</v>
+        <v>6.84936189651489</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>6.82439565658569</v>
+        <v>6.82439517974854</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G1112" t="n">
-        <v>6.89097452163696</v>
+        <v>6.89097499847412</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G1114" t="n">
-        <v>6.73701000213623</v>
+        <v>6.73701047897339</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G1116" t="n">
-        <v>6.32921075820923</v>
+        <v>6.32921028137207</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1117" t="n">
-        <v>6.12531089782715</v>
+        <v>6.12531137466431</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G1120" t="n">
-        <v>5.93389511108398</v>
+        <v>5.93389463424683</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>7.25</v>
       </c>
       <c r="G1124" t="n">
-        <v>6.03376483917236</v>
+        <v>6.03376388549805</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1128" t="n">
-        <v>5.84234857559204</v>
+        <v>5.8423490524292</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G1129" t="n">
-        <v>6.03792524337769</v>
+        <v>6.03792572021484</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1133" t="n">
-        <v>5.80073595046997</v>
+        <v>5.80073642730713</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1134" t="n">
-        <v>5.47616147994995</v>
+        <v>5.47616052627563</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1135" t="n">
-        <v>5.39293718338013</v>
+        <v>5.39293670654297</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>6.5</v>
       </c>
       <c r="G1136" t="n">
-        <v>5.40958118438721</v>
+        <v>5.40958213806152</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.36796951293945</v>
+        <v>5.36796998977661</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.97265386581421</v>
+        <v>4.97265338897705</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.92271947860718</v>
+        <v>4.92271900177002</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1144" t="n">
-        <v>5.19735908508301</v>
+        <v>5.19736003875732</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.30971240997314</v>
+        <v>5.3097128868103</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.33468008041382</v>
+        <v>5.3346791267395</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.65925550460815</v>
+        <v>5.65925455093384</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1149" t="n">
-        <v>5.71334981918335</v>
+        <v>5.71335029602051</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1150" t="n">
-        <v>5.73415660858154</v>
+        <v>5.7341570854187</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1151" t="n">
-        <v>6.81607246398926</v>
+        <v>6.81607294082642</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>6.58720636367798</v>
+        <v>6.58720588684082</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1156" t="n">
-        <v>8.0727596282959</v>
+        <v>8.07276058197021</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>9.55500030517578</v>
       </c>
       <c r="G1157" t="n">
-        <v>7.95208597183228</v>
+        <v>7.95208644866943</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.73986339569092</v>
+        <v>7.73986387252808</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G1159" t="n">
-        <v>7.39864301681519</v>
+        <v>7.3986439704895</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.36535453796387</v>
+        <v>7.36535358428955</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G1161" t="n">
-        <v>7.31958055496216</v>
+        <v>7.319580078125</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1162" t="n">
-        <v>7.59005975723267</v>
+        <v>7.59005880355835</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G1163" t="n">
-        <v>7.56925392150879</v>
+        <v>7.56925344467163</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>9</v>
       </c>
       <c r="G1164" t="n">
-        <v>7.49019002914429</v>
+        <v>7.49019050598145</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>7.4236102104187</v>
+        <v>7.42361164093018</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.48602914810181</v>
+        <v>7.48602962493896</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>9.17500019073486</v>
       </c>
       <c r="G1167" t="n">
-        <v>7.63583183288574</v>
+        <v>7.6358323097229</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G1168" t="n">
-        <v>7.63167095184326</v>
+        <v>7.63167190551758</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G1169" t="n">
-        <v>7.71073436737061</v>
+        <v>7.71073532104492</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1171" t="n">
-        <v>7.7315411567688</v>
+        <v>7.73154067993164</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G1172" t="n">
-        <v>7.70241212844849</v>
+        <v>7.70241355895996</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1174" t="n">
-        <v>7.73986339569092</v>
+        <v>7.73986387252808</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>7.66079902648926</v>
+        <v>7.66079998016357</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1177" t="n">
-        <v>7.5983829498291</v>
+        <v>7.59838199615479</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>9.26500034332275</v>
       </c>
       <c r="G1178" t="n">
-        <v>7.71073436737061</v>
+        <v>7.71073532104492</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1180" t="n">
-        <v>7.68992853164673</v>
+        <v>7.68992805480957</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1181" t="n">
-        <v>7.65663814544678</v>
+        <v>7.65663909912109</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1182" t="n">
-        <v>7.49851179122925</v>
+        <v>7.49851274490356</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>9</v>
       </c>
       <c r="G1183" t="n">
-        <v>7.49019002914429</v>
+        <v>7.49019050598145</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>7.7315411567688</v>
+        <v>7.73154067993164</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G1185" t="n">
-        <v>7.76899194717407</v>
+        <v>7.76899147033691</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1186" t="n">
-        <v>7.68992853164673</v>
+        <v>7.68992805480957</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G1187" t="n">
-        <v>7.68576622009277</v>
+        <v>7.68576717376709</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G1188" t="n">
-        <v>7.7148962020874</v>
+        <v>7.71489715576172</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1189" t="n">
-        <v>7.5484471321106</v>
+        <v>7.54844760894775</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G1190" t="n">
-        <v>7.39032173156738</v>
+        <v>7.39032077789307</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>9</v>
       </c>
       <c r="G1191" t="n">
-        <v>7.49019002914429</v>
+        <v>7.49019050598145</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>9</v>
       </c>
       <c r="G1192" t="n">
-        <v>7.49019002914429</v>
+        <v>7.49019050598145</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G1193" t="n">
-        <v>7.34454822540283</v>
+        <v>7.34454774856567</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>8.95499992370605</v>
       </c>
       <c r="G1194" t="n">
-        <v>7.45273876190186</v>
+        <v>7.45273971557617</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G1195" t="n">
-        <v>7.43193340301514</v>
+        <v>7.43193292617798</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1197" t="n">
-        <v>7.15729379653931</v>
+        <v>7.15729331970215</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G1198" t="n">
-        <v>7.09487342834473</v>
+        <v>7.09487438201904</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G1201" t="n">
-        <v>7.06158494949341</v>
+        <v>7.06158447265625</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G1203" t="n">
-        <v>7.06158494949341</v>
+        <v>7.06158447265625</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G1206" t="n">
-        <v>7.02829504013062</v>
+        <v>7.02829456329346</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>9.01500034332275</v>
       </c>
       <c r="G1207" t="n">
-        <v>7.50267362594604</v>
+        <v>7.5026741027832</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.61086559295654</v>
+        <v>7.61086511611938</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1210" t="n">
-        <v>7.5983829498291</v>
+        <v>7.59838199615479</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>7.66079902648926</v>
+        <v>7.66079998016357</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G1213" t="n">
-        <v>7.71905660629272</v>
+        <v>7.71905612945557</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G1215" t="n">
-        <v>8.08524417877197</v>
+        <v>8.08524322509766</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G1216" t="n">
-        <v>8.08108329772949</v>
+        <v>8.08108234405518</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G1217" t="n">
-        <v>8.30162715911865</v>
+        <v>8.30162811279297</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1218" t="n">
-        <v>8.0727596282959</v>
+        <v>8.07276058197021</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1223" t="n">
-        <v>7.81476449966431</v>
+        <v>7.81476545333862</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1224" t="n">
-        <v>7.82308721542358</v>
+        <v>7.82308673858643</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G1225" t="n">
-        <v>7.65247678756714</v>
+        <v>7.65247774124146</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>9.02999973297119</v>
       </c>
       <c r="G1226" t="n">
-        <v>7.51515674591064</v>
+        <v>7.51515817642212</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>9.48499965667725</v>
       </c>
       <c r="G1227" t="n">
-        <v>7.89382648468018</v>
+        <v>7.89382791519165</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G1232" t="n">
-        <v>8.17679119110107</v>
+        <v>8.17679214477539</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>9.90499973297119</v>
       </c>
       <c r="G1233" t="n">
-        <v>8.24337005615234</v>
+        <v>8.24336910247803</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1239" t="n">
-        <v>8.38901424407959</v>
+        <v>8.38901329040527</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1242" t="n">
-        <v>8.0727596282959</v>
+        <v>8.07276058197021</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1243" t="n">
-        <v>7.86469888687134</v>
+        <v>7.86469984054565</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1244" t="n">
-        <v>7.98953628540039</v>
+        <v>7.98953723907471</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G1245" t="n">
-        <v>8.08108329772949</v>
+        <v>8.08108234405518</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G1250" t="n">
-        <v>8.38068962097168</v>
+        <v>8.380690574646</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1251" t="n">
-        <v>8.78016757965088</v>
+        <v>8.7801685333252</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G1252" t="n">
-        <v>8.63036346435547</v>
+        <v>8.63036251068115</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G1253" t="n">
-        <v>8.28082084655762</v>
+        <v>8.2808198928833</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>8.82178020477295</v>
+        <v>8.82177925109863</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1259" t="n">
-        <v>9.38770580291748</v>
+        <v>9.38770484924316</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G1262" t="n">
-        <v>8.88003635406494</v>
+        <v>8.88003730773926</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1263" t="n">
-        <v>9.05480861663818</v>
+        <v>9.05480766296387</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1264" t="n">
-        <v>8.8883581161499</v>
+        <v>8.88835906982422</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1267" t="n">
-        <v>9.46260738372803</v>
+        <v>9.46260643005371</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1269" t="n">
-        <v>9.27951240539551</v>
+        <v>9.27951335906982</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G1270" t="n">
-        <v>9.3128023147583</v>
+        <v>9.31280326843262</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1271" t="n">
-        <v>9.30448055267334</v>
+        <v>9.30448246002197</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1273" t="n">
-        <v>9.38770580291748</v>
+        <v>9.38770484924316</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1274" t="n">
-        <v>9.86208343505859</v>
+        <v>9.86208248138428</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>11.5</v>
       </c>
       <c r="G1277" t="n">
-        <v>9.57079887390137</v>
+        <v>9.57079982757568</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G1278" t="n">
-        <v>9.5541524887085</v>
+        <v>9.55415344238281</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G1280" t="n">
-        <v>9.26286792755127</v>
+        <v>9.26286888122559</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>11.25</v>
       </c>
       <c r="G1281" t="n">
-        <v>9.36273670196533</v>
+        <v>9.36273765563965</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1282" t="n">
-        <v>8.65532970428467</v>
+        <v>8.65533065795898</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G1283" t="n">
-        <v>8.6802978515625</v>
+        <v>8.68029880523682</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G1285" t="n">
-        <v>8.86642456054688</v>
+        <v>8.86642551422119</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G1289" t="n">
-        <v>8.84942245483398</v>
+        <v>8.8494234085083</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1290" t="n">
-        <v>8.80691909790039</v>
+        <v>8.80691719055176</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>10.5</v>
       </c>
       <c r="G1291" t="n">
-        <v>8.92593097686768</v>
+        <v>8.92593002319336</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1292" t="n">
-        <v>9.04494380950928</v>
+        <v>9.04494476318359</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G1296" t="n">
-        <v>9.46148777008057</v>
+        <v>9.46148681640625</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G1297" t="n">
-        <v>9.51249217987061</v>
+        <v>9.51249313354492</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G1300" t="n">
-        <v>9.15545558929443</v>
+        <v>9.15545654296875</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G1303" t="n">
-        <v>8.9514331817627</v>
+        <v>8.95143413543701</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G1304" t="n">
-        <v>8.88342666625977</v>
+        <v>8.88342571258545</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1305" t="n">
-        <v>8.85792350769043</v>
+        <v>8.85792446136475</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G1307" t="n">
-        <v>9.15545558929443</v>
+        <v>9.15545654296875</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G1310" t="n">
-        <v>9.10445022583008</v>
+        <v>9.10444927215576</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G1311" t="n">
-        <v>9.15545558929443</v>
+        <v>9.15545654296875</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1317" t="n">
-        <v>9.18095874786377</v>
+        <v>9.18095779418945</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>10.5</v>
       </c>
       <c r="G1318" t="n">
-        <v>8.92593097686768</v>
+        <v>8.92593002319336</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1319" t="n">
-        <v>9.04494380950928</v>
+        <v>9.04494476318359</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1321" t="n">
-        <v>8.95993423461914</v>
+        <v>8.95993518829346</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1323" t="n">
-        <v>8.84092140197754</v>
+        <v>8.84092330932617</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1324" t="n">
-        <v>8.85792350769043</v>
+        <v>8.85792446136475</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1326" t="n">
-        <v>8.6709041595459</v>
+        <v>8.67090511322021</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G1327" t="n">
-        <v>8.89192771911621</v>
+        <v>8.89192867279053</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>10.5</v>
       </c>
       <c r="G1328" t="n">
-        <v>8.92593097686768</v>
+        <v>8.92593002319336</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G1331" t="n">
-        <v>9.19795894622803</v>
+        <v>9.19795989990234</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G1335" t="n">
-        <v>9.00243854522705</v>
+        <v>9.00243949890137</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1336" t="n">
-        <v>8.85792350769043</v>
+        <v>8.85792446136475</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G1337" t="n">
-        <v>8.83242225646973</v>
+        <v>8.83242130279541</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G1338" t="n">
-        <v>8.86642456054688</v>
+        <v>8.86642551422119</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>10.5</v>
       </c>
       <c r="G1340" t="n">
-        <v>8.92593097686768</v>
+        <v>8.92593002319336</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G1341" t="n">
-        <v>9.00243854522705</v>
+        <v>9.00243949890137</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G1342" t="n">
-        <v>9.0874490737915</v>
+        <v>9.08744716644287</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1344" t="n">
-        <v>8.95993423461914</v>
+        <v>8.95993518829346</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1345" t="n">
-        <v>8.95993423461914</v>
+        <v>8.95993518829346</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G1346" t="n">
-        <v>8.7899169921875</v>
+        <v>8.78991794586182</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G1347" t="n">
-        <v>8.7899169921875</v>
+        <v>8.78991794586182</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G1349" t="n">
-        <v>8.56039237976074</v>
+        <v>8.56039333343506</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1350" t="n">
-        <v>8.61989974975586</v>
+        <v>8.61990070343018</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G1352" t="n">
-        <v>8.84942245483398</v>
+        <v>8.8494234085083</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1353" t="n">
-        <v>8.82392120361328</v>
+        <v>8.82392024993896</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G1356" t="n">
-        <v>8.50938701629639</v>
+        <v>8.5093879699707</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G1357" t="n">
-        <v>8.50938701629639</v>
+        <v>8.5093879699707</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1360" t="n">
-        <v>8.68790721893311</v>
+        <v>8.68790626525879</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1361" t="n">
-        <v>8.70490837097168</v>
+        <v>8.70490741729736</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1364" t="n">
-        <v>8.48388481140137</v>
+        <v>8.48388385772705</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G1365" t="n">
-        <v>8.52638912200928</v>
+        <v>8.52639007568359</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>9.67000007629395</v>
       </c>
       <c r="G1368" t="n">
-        <v>8.22035598754883</v>
+        <v>8.22035694122314</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G1373" t="n">
-        <v>8.50938701629639</v>
+        <v>8.5093879699707</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>9.69499969482422</v>
       </c>
       <c r="G1378" t="n">
-        <v>8.24160861968994</v>
+        <v>8.24160957336426</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G1379" t="n">
-        <v>8.27136325836182</v>
+        <v>8.2713623046875</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1380" t="n">
-        <v>8.2118558883667</v>
+        <v>8.21185684204102</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G1381" t="n">
-        <v>8.32236862182617</v>
+        <v>8.32236766815186</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>9.72999954223633</v>
       </c>
       <c r="G1382" t="n">
-        <v>8.27136325836182</v>
+        <v>8.2713623046875</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G1383" t="n">
-        <v>8.47963428497314</v>
+        <v>8.47963619232178</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G1384" t="n">
-        <v>8.47963428497314</v>
+        <v>8.47963619232178</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1385" t="n">
-        <v>8.51788902282715</v>
+        <v>8.51788997650146</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G1386" t="n">
-        <v>8.47538471221924</v>
+        <v>8.47538375854492</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G1387" t="n">
-        <v>8.45838260650635</v>
+        <v>8.45838165283203</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G1388" t="n">
-        <v>8.45838260650635</v>
+        <v>8.45838165283203</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G1389" t="n">
-        <v>8.445631980896</v>
+        <v>8.44563102722168</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G1390" t="n">
-        <v>8.35212230682373</v>
+        <v>8.35212135314941</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G1391" t="n">
-        <v>8.3903751373291</v>
+        <v>8.39037609100342</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>8.43288040161133</v>
+        <v>8.43287944793701</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G1393" t="n">
-        <v>8.66240310668945</v>
+        <v>8.66240406036377</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G1394" t="n">
-        <v>8.52638912200928</v>
+        <v>8.52639007568359</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G1395" t="n">
-        <v>8.56039237976074</v>
+        <v>8.56039333343506</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G1396" t="n">
-        <v>8.64540195465088</v>
+        <v>8.6454029083252</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>9.69499969482422</v>
       </c>
       <c r="G1397" t="n">
-        <v>8.24160861968994</v>
+        <v>8.24160957336426</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1398" t="n">
-        <v>7.7868127822876</v>
+        <v>7.78681230545044</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1399" t="n">
-        <v>7.71880435943604</v>
+        <v>7.71880483627319</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>7.79531288146973</v>
+        <v>7.79531383514404</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G1402" t="n">
-        <v>7.71880435943604</v>
+        <v>7.71880483627319</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1403" t="n">
-        <v>7.85481977462769</v>
+        <v>7.85481929779053</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1404" t="n">
-        <v>7.82081460952759</v>
+        <v>7.8208155632019</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G1406" t="n">
-        <v>7.77406072616577</v>
+        <v>7.77406120300293</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G1407" t="n">
-        <v>7.79531288146973</v>
+        <v>7.79531383514404</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1408" t="n">
-        <v>7.7868127822876</v>
+        <v>7.78681230545044</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G1409" t="n">
-        <v>7.81656455993652</v>
+        <v>7.81656551361084</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1410" t="n">
-        <v>7.82506561279297</v>
+        <v>7.82506656646729</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G1411" t="n">
-        <v>7.81656455993652</v>
+        <v>7.81656551361084</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1414" t="n">
-        <v>7.39577150344849</v>
+        <v>7.39577054977417</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>8.66499996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>7.36601829528809</v>
+        <v>7.36601877212524</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1417" t="n">
-        <v>7.25975799560547</v>
+        <v>7.25975704193115</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1419" t="n">
-        <v>6.97072744369507</v>
+        <v>6.97072696685791</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G1421" t="n">
-        <v>6.93247318267822</v>
+        <v>6.93247270584106</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1422" t="n">
-        <v>7.05573606491089</v>
+        <v>7.05573654174805</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1424" t="n">
-        <v>6.97072744369507</v>
+        <v>6.97072696685791</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1425" t="n">
-        <v>7.2087516784668</v>
+        <v>7.20875215530396</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1431" t="n">
-        <v>6.93672370910645</v>
+        <v>6.9367241859436</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1432" t="n">
-        <v>7.02173328399658</v>
+        <v>7.02173233032227</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1433" t="n">
-        <v>7.07273817062378</v>
+        <v>7.07273769378662</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1437" t="n">
-        <v>7.13224458694458</v>
+        <v>7.13224411010742</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1438" t="n">
-        <v>7.11524248123169</v>
+        <v>7.11524200439453</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1439" t="n">
-        <v>7.27250862121582</v>
+        <v>7.27250957489014</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1440" t="n">
-        <v>7.32351350784302</v>
+        <v>7.32351398468018</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G1441" t="n">
-        <v>7.25975799560547</v>
+        <v>7.25975704193115</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.18749952316284</v>
+        <v>7.18749904632568</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G1443" t="n">
-        <v>7.28526020050049</v>
+        <v>7.28525924682617</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>8.5</v>
       </c>
       <c r="G1444" t="n">
-        <v>7.22575378417969</v>
+        <v>7.22575330734253</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1445" t="n">
-        <v>7.23425531387329</v>
+        <v>7.23425483703613</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1447" t="n">
-        <v>7.13224458694458</v>
+        <v>7.13224411010742</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G1448" t="n">
-        <v>6.93672370910645</v>
+        <v>6.9367241859436</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>8.25</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.01323127746582</v>
+        <v>7.01323175430298</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G1451" t="n">
-        <v>6.94522523880005</v>
+        <v>6.94522476196289</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>8.10999965667725</v>
       </c>
       <c r="G1453" t="n">
-        <v>6.89421939849854</v>
+        <v>6.89421844482422</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1454" t="n">
-        <v>6.76670598983765</v>
+        <v>6.7667064666748</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G1459" t="n">
-        <v>6.3544135093689</v>
+        <v>6.35441303253174</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1460" t="n">
-        <v>6.31190872192383</v>
+        <v>6.31190824508667</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G1461" t="n">
-        <v>6.3544135093689</v>
+        <v>6.35441303253174</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G1464" t="n">
-        <v>6.42667007446289</v>
+        <v>6.42667055130005</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G1468" t="n">
-        <v>6.36291408538818</v>
+        <v>6.36291360855103</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G1471" t="n">
-        <v>6.3544135093689</v>
+        <v>6.35441303253174</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G1472" t="n">
-        <v>6.32891082763672</v>
+        <v>6.32891035079956</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G1473" t="n">
-        <v>6.3544135093689</v>
+        <v>6.35441303253174</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G1474" t="n">
-        <v>6.43942165374756</v>
+        <v>6.4394211769104</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1475" t="n">
-        <v>6.6391921043396</v>
+        <v>6.63919258117676</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G1478" t="n">
-        <v>6.10788726806641</v>
+        <v>6.10788679122925</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.10363721847534</v>
+        <v>6.10363674163818</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1481" t="n">
-        <v>5.78060340881348</v>
+        <v>5.78060293197632</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G1485" t="n">
-        <v>5.97187280654907</v>
+        <v>5.97187328338623</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1488" t="n">
-        <v>5.36405992507935</v>
+        <v>5.36405944824219</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1490" t="n">
-        <v>5.43206644058228</v>
+        <v>5.43206739425659</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1493" t="n">
-        <v>5.5340781211853</v>
+        <v>5.53407764434814</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>6.39499998092651</v>
       </c>
       <c r="G1494" t="n">
-        <v>5.43631744384766</v>
+        <v>5.4363169670105</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1495" t="n">
-        <v>5.78910398483276</v>
+        <v>5.78910446166992</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1499" t="n">
-        <v>5.74659967422485</v>
+        <v>5.7465991973877</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>6.625</v>
       </c>
       <c r="G1500" t="n">
-        <v>5.63183784484863</v>
+        <v>5.63183736801147</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G1501" t="n">
-        <v>5.94637060165405</v>
+        <v>5.94637012481689</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>7</v>
       </c>
       <c r="G1503" t="n">
-        <v>5.95062160491943</v>
+        <v>5.95062112808228</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1506" t="n">
-        <v>6.11213779449463</v>
+        <v>6.11213731765747</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1508" t="n">
-        <v>6.2651538848877</v>
+        <v>6.26515340805054</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1510" t="n">
-        <v>5.89111471176147</v>
+        <v>5.89111423492432</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>7</v>
       </c>
       <c r="G1511" t="n">
-        <v>5.95062160491943</v>
+        <v>5.95062112808228</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G1514" t="n">
-        <v>6.00162649154663</v>
+        <v>6.00162601470947</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1515" t="n">
-        <v>6.03562927246094</v>
+        <v>6.0356297492981</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G1517" t="n">
-        <v>6.11213779449463</v>
+        <v>6.11213731765747</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>7.32499980926514</v>
       </c>
       <c r="G1519" t="n">
-        <v>6.22689962387085</v>
+        <v>6.22689867019653</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1521" t="n">
-        <v>6.03562927246094</v>
+        <v>6.0356297492981</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G1522" t="n">
-        <v>6.01437711715698</v>
+        <v>6.01437759399414</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>7</v>
       </c>
       <c r="G1523" t="n">
-        <v>5.95062160491943</v>
+        <v>5.95062112808228</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1526" t="n">
-        <v>6.188645362854</v>
+        <v>6.18864583969116</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G1529" t="n">
-        <v>6.36291408538818</v>
+        <v>6.36291360855103</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1532" t="n">
-        <v>6.01012659072876</v>
+        <v>6.01012706756592</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1533" t="n">
-        <v>6.01012659072876</v>
+        <v>6.01012706756592</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1534" t="n">
-        <v>6.36716365814209</v>
+        <v>6.36716413497925</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G1536" t="n">
-        <v>6.3544135093689</v>
+        <v>6.35441303253174</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>6.23114967346191</v>
+        <v>6.23115062713623</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G1540" t="n">
-        <v>5.99737548828125</v>
+        <v>5.99737501144409</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G1550" t="n">
-        <v>6.16264057159424</v>
+        <v>6.1626410484314</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1556" t="n">
-        <v>5.57551574707031</v>
+        <v>5.57551527023315</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1558" t="n">
-        <v>5.6103081703186</v>
+        <v>5.61030864715576</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G1559" t="n">
-        <v>5.30587244033813</v>
+        <v>5.30587291717529</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1561" t="n">
-        <v>5.49723196029663</v>
+        <v>5.49723243713379</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G1562" t="n">
-        <v>5.51897716522217</v>
+        <v>5.51897764205933</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G1564" t="n">
-        <v>5.53202438354492</v>
+        <v>5.53202486038208</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1565" t="n">
-        <v>5.69728994369507</v>
+        <v>5.69728946685791</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G1566" t="n">
-        <v>5.71033716201782</v>
+        <v>5.71033668518066</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1568" t="n">
-        <v>5.50592994689941</v>
+        <v>5.50593042373657</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G1569" t="n">
-        <v>5.41025018692017</v>
+        <v>5.41025066375732</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G1570" t="n">
-        <v>5.41459989547729</v>
+        <v>5.41459941864014</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G1571" t="n">
-        <v>5.4406943321228</v>
+        <v>5.44069385528564</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1572" t="n">
-        <v>5.4319953918457</v>
+        <v>5.43199586868286</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G1575" t="n">
-        <v>5.78427171707153</v>
+        <v>5.78427124023438</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G1576" t="n">
-        <v>5.67554426193237</v>
+        <v>5.67554473876953</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G1577" t="n">
-        <v>5.81906414031982</v>
+        <v>5.81906366348267</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G1578" t="n">
-        <v>5.7538275718689</v>
+        <v>5.75382709503174</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G1581" t="n">
-        <v>5.51897716522217</v>
+        <v>5.51897764205933</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G1582" t="n">
-        <v>5.64510059356689</v>
+        <v>5.64510011672974</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G1583" t="n">
-        <v>5.64075136184692</v>
+        <v>5.64075183868408</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G1586" t="n">
-        <v>5.72338438034058</v>
+        <v>5.72338390350342</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1589" t="n">
-        <v>5.79731798171997</v>
+        <v>5.79731845855713</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G1590" t="n">
-        <v>5.96258306503296</v>
+        <v>5.96258354187012</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1591" t="n">
-        <v>6.05391359329224</v>
+        <v>6.05391454696655</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1592" t="n">
-        <v>5.86255407333374</v>
+        <v>5.8625545501709</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1593" t="n">
-        <v>5.96693277359009</v>
+        <v>5.96693229675293</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1594" t="n">
-        <v>5.97128105163574</v>
+        <v>5.9712815284729</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1595" t="n">
-        <v>5.79731798171997</v>
+        <v>5.79731845855713</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>6.75</v>
       </c>
       <c r="G1597" t="n">
-        <v>5.87125253677368</v>
+        <v>5.87125301361084</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1600" t="n">
-        <v>6.07131052017212</v>
+        <v>6.07131004333496</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G1602" t="n">
-        <v>6.04521560668945</v>
+        <v>6.04521512985229</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1604" t="n">
-        <v>6.05391359329224</v>
+        <v>6.05391454696655</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>5.85385656356812</v>
+        <v>5.85385608673096</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1610" t="n">
-        <v>5.84515857696533</v>
+        <v>5.84515810012817</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>5.95823383331299</v>
+        <v>5.95823431015015</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G1617" t="n">
-        <v>5.63205337524414</v>
+        <v>5.63205289840698</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G1618" t="n">
-        <v>5.67554426193237</v>
+        <v>5.67554473876953</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1619" t="n">
-        <v>5.69728994369507</v>
+        <v>5.69728946685791</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1620" t="n">
-        <v>5.84515857696533</v>
+        <v>5.84515810012817</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G1631" t="n">
-        <v>5.30152320861816</v>
+        <v>5.30152368545532</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1633" t="n">
-        <v>5.49288272857666</v>
+        <v>5.49288320541382</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1635" t="n">
-        <v>5.6103081703186</v>
+        <v>5.61030864715576</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G1636" t="n">
-        <v>5.84515857696533</v>
+        <v>5.84515810012817</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.4319953918457</v>
+        <v>5.43199586868286</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1641" t="n">
-        <v>5.49288272857666</v>
+        <v>5.49288320541382</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G1642" t="n">
-        <v>5.5233268737793</v>
+        <v>5.52332639694214</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1645" t="n">
-        <v>5.62770366668701</v>
+        <v>5.62770414352417</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G1652" t="n">
-        <v>6.20613193511963</v>
+        <v>6.20613145828247</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1655" t="n">
-        <v>6.05391359329224</v>
+        <v>6.05391454696655</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G1670" t="n">
-        <v>6.16264057159424</v>
+        <v>6.1626410484314</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1673" t="n">
-        <v>6.32355642318726</v>
+        <v>6.32355690002441</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G1674" t="n">
-        <v>6.32790613174438</v>
+        <v>6.32790565490723</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G1675" t="n">
-        <v>6.32790613174438</v>
+        <v>6.32790565490723</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G1676" t="n">
-        <v>6.32355642318726</v>
+        <v>6.32355690002441</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>7.375</v>
       </c>
       <c r="G1677" t="n">
-        <v>6.41488695144653</v>
+        <v>6.41488742828369</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1678" t="n">
-        <v>6.4888219833374</v>
+        <v>6.48882150650024</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G1684" t="n">
-        <v>6.41923570632935</v>
+        <v>6.4192361831665</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G1685" t="n">
-        <v>6.3800950050354</v>
+        <v>6.38009452819824</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1687" t="n">
-        <v>6.51491546630859</v>
+        <v>6.51491594314575</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1689" t="n">
-        <v>6.39749097824097</v>
+        <v>6.39749050140381</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G1692" t="n">
-        <v>6.3800950050354</v>
+        <v>6.38009452819824</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G1695" t="n">
-        <v>6.34095335006714</v>
+        <v>6.34095287322998</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1702" t="n">
-        <v>6.43663311004639</v>
+        <v>6.43663263320923</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>7.52500009536743</v>
       </c>
       <c r="G1703" t="n">
-        <v>6.54535961151123</v>
+        <v>6.54536008834839</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>7.84499979019165</v>
       </c>
       <c r="G1704" t="n">
-        <v>6.82370042800903</v>
+        <v>6.82369995117188</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G1708" t="n">
-        <v>6.85849285125732</v>
+        <v>6.85849332809448</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>8.625</v>
       </c>
       <c r="G1711" t="n">
-        <v>7.50215673446655</v>
+        <v>7.50215625762939</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>8.56999969482422</v>
       </c>
       <c r="G1712" t="n">
-        <v>7.45431661605835</v>
+        <v>7.45431566238403</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1713" t="n">
-        <v>7.68046760559082</v>
+        <v>7.68046808242798</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>8.1850004196167</v>
       </c>
       <c r="G1715" t="n">
-        <v>7.11943817138672</v>
+        <v>7.11943769454956</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G1718" t="n">
-        <v>7.11508846282959</v>
+        <v>7.11508893966675</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G1719" t="n">
-        <v>7.07594633102417</v>
+        <v>7.07594680786133</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G1720" t="n">
-        <v>7.07594633102417</v>
+        <v>7.07594680786133</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G1721" t="n">
-        <v>7.17162609100342</v>
+        <v>7.17162656784058</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>8.49499988555908</v>
       </c>
       <c r="G1722" t="n">
-        <v>7.38907957077026</v>
+        <v>7.38908004760742</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G1726" t="n">
-        <v>7.35428762435913</v>
+        <v>7.35428667068481</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1729" t="n">
-        <v>7.18467426300049</v>
+        <v>7.18467330932617</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1732" t="n">
-        <v>7.21946620941162</v>
+        <v>7.21946668624878</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1733" t="n">
-        <v>7.12378597259521</v>
+        <v>7.12378644943237</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G1734" t="n">
-        <v>7.04985189437866</v>
+        <v>7.04985237121582</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G1736" t="n">
-        <v>7.14553260803223</v>
+        <v>7.14553213119507</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1738" t="n">
-        <v>7.18467426300049</v>
+        <v>7.18467330932617</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1739" t="n">
-        <v>7.28035354614258</v>
+        <v>7.28035306930542</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G1740" t="n">
-        <v>7.31514596939087</v>
+        <v>7.31514549255371</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>8.13500022888184</v>
       </c>
       <c r="G1747" t="n">
-        <v>7.07594633102417</v>
+        <v>7.07594680786133</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G1750" t="n">
-        <v>6.87588977813721</v>
+        <v>6.87588930130005</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>7.78499984741211</v>
       </c>
       <c r="G1752" t="n">
-        <v>6.77151155471802</v>
+        <v>6.77151107788086</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1753" t="n">
-        <v>6.56710481643677</v>
+        <v>6.56710529327393</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G1754" t="n">
-        <v>6.68018054962158</v>
+        <v>6.68018007278442</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>7.73000001907349</v>
       </c>
       <c r="G1755" t="n">
-        <v>6.72367143630981</v>
+        <v>6.72367191314697</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G1756" t="n">
-        <v>6.69322824478149</v>
+        <v>6.69322776794434</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G1757" t="n">
-        <v>6.68887901306152</v>
+        <v>6.68887853622437</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>8.15499973297119</v>
       </c>
       <c r="G1765" t="n">
-        <v>7.09334325790405</v>
+        <v>7.09334230422974</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1766" t="n">
-        <v>7.11073923110962</v>
+        <v>7.11073970794678</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G1767" t="n">
-        <v>6.98026657104492</v>
+        <v>6.98026752471924</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G1773" t="n">
-        <v>7.18467426300049</v>
+        <v>7.18467330932617</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>8.35499954223633</v>
       </c>
       <c r="G1777" t="n">
-        <v>7.26730537414551</v>
+        <v>7.26730585098267</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>8.1850004196167</v>
       </c>
       <c r="G1780" t="n">
-        <v>7.11943817138672</v>
+        <v>7.11943769454956</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1783" t="n">
-        <v>7.32384443283081</v>
+        <v>7.32384395599365</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G1785" t="n">
-        <v>7.32384443283081</v>
+        <v>7.32384395599365</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G1786" t="n">
-        <v>7.41082525253296</v>
+        <v>7.41082572937012</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1788" t="n">
-        <v>7.12378597259521</v>
+        <v>7.12378644943237</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -69064,6 +69064,32 @@
         <v>12.9200000762939</v>
       </c>
       <c r="H2642" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2643">
+      <c r="A2643" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2643" t="n">
+        <v>252719</v>
+      </c>
+      <c r="C2643" t="n">
+        <v>13.0699996948242</v>
+      </c>
+      <c r="D2643" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="E2643" t="n">
+        <v>12.9300003051758</v>
+      </c>
+      <c r="F2643" t="n">
+        <v>13</v>
+      </c>
+      <c r="G2643" t="n">
+        <v>13</v>
+      </c>
+      <c r="H2643" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -61338,8 +61338,31 @@
       <c r="E2651" t="n">
         <v>12.9799995422363</v>
       </c>
-      <c r="F2651"/>
+      <c r="F2651" t="n">
+        <v>12.9200000762939</v>
+      </c>
       <c r="G2651" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2652">
+      <c r="A2652" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2652" t="n">
+        <v>282267</v>
+      </c>
+      <c r="C2652" t="n">
+        <v>13.1000003814697</v>
+      </c>
+      <c r="D2652" t="n">
+        <v>12.8699998855591</v>
+      </c>
+      <c r="E2652" t="n">
+        <v>12.8999996185303</v>
+      </c>
+      <c r="F2652"/>
+      <c r="G2652" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -61361,8 +61361,31 @@
       <c r="E2652" t="n">
         <v>12.8999996185303</v>
       </c>
-      <c r="F2652"/>
+      <c r="F2652" t="n">
+        <v>12.9899997711182</v>
+      </c>
       <c r="G2652" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2653">
+      <c r="A2653" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2653" t="n">
+        <v>241330</v>
+      </c>
+      <c r="C2653" t="n">
+        <v>13.0799999237061</v>
+      </c>
+      <c r="D2653" t="n">
+        <v>12.7700004577637</v>
+      </c>
+      <c r="E2653" t="n">
+        <v>12.9799995422363</v>
+      </c>
+      <c r="F2653"/>
+      <c r="G2653" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -61379,13 +61379,36 @@
         <v>13.0799999237061</v>
       </c>
       <c r="D2653" t="n">
-        <v>12.7700004577637</v>
+        <v>12.75</v>
       </c>
       <c r="E2653" t="n">
         <v>12.9799995422363</v>
       </c>
-      <c r="F2653"/>
+      <c r="F2653" t="n">
+        <v>12.75</v>
+      </c>
       <c r="G2653" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2654">
+      <c r="A2654" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2654" t="n">
+        <v>216099</v>
+      </c>
+      <c r="C2654" t="n">
+        <v>13.0100002288818</v>
+      </c>
+      <c r="D2654" t="n">
+        <v>12.6400003433228</v>
+      </c>
+      <c r="E2654" t="n">
+        <v>12.6999998092651</v>
+      </c>
+      <c r="F2654"/>
+      <c r="G2654" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -61407,8 +61407,31 @@
       <c r="E2654" t="n">
         <v>12.6999998092651</v>
       </c>
-      <c r="F2654"/>
+      <c r="F2654" t="n">
+        <v>12.789999961853</v>
+      </c>
       <c r="G2654" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2655">
+      <c r="A2655" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2655" t="n">
+        <v>137359</v>
+      </c>
+      <c r="C2655" t="n">
+        <v>12.960000038147</v>
+      </c>
+      <c r="D2655" t="n">
+        <v>12.7600002288818</v>
+      </c>
+      <c r="E2655" t="n">
+        <v>12.8599996566772</v>
+      </c>
+      <c r="F2655"/>
+      <c r="G2655" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -61437,6 +61437,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2656">
+      <c r="A2656" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2656" t="n">
+        <v>240389</v>
+      </c>
+      <c r="C2656" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2656" t="n">
+        <v>12.6999998092651</v>
+      </c>
+      <c r="E2656" t="n">
+        <v>12.8500003814697</v>
+      </c>
+      <c r="F2656" t="n">
+        <v>12.7299995422363</v>
+      </c>
+      <c r="G2656" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TGYM.MI.xlsx
+++ b/data/TGYM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G2" t="n">
-        <v>2.90751266479492</v>
+        <v>2.9075129032135</v>
       </c>
       <c r="H2" t="n">
         <v>12077779</v>
@@ -456,7 +456,7 @@
         <v>3.83800005912781</v>
       </c>
       <c r="G3" t="n">
-        <v>3.08260607719421</v>
+        <v>3.08260631561279</v>
       </c>
       <c r="H3" t="n">
         <v>5546418</v>
@@ -485,7 +485,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G4" t="n">
-        <v>3.06814885139465</v>
+        <v>3.06814861297607</v>
       </c>
       <c r="H4" t="n">
         <v>2069150</v>
@@ -514,7 +514,7 @@
         <v>3.79800009727478</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0504789352417</v>
+        <v>3.05047917366028</v>
       </c>
       <c r="H5" t="n">
         <v>530952</v>
@@ -572,7 +572,7 @@
         <v>3.74799990653992</v>
       </c>
       <c r="G7" t="n">
-        <v>3.01031947135925</v>
+        <v>3.01031970977783</v>
       </c>
       <c r="H7" t="n">
         <v>613007</v>
@@ -688,7 +688,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G11" t="n">
-        <v>3.10830807685852</v>
+        <v>3.10830783843994</v>
       </c>
       <c r="H11" t="n">
         <v>302716</v>
@@ -717,7 +717,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G12" t="n">
-        <v>3.11473321914673</v>
+        <v>3.11473345756531</v>
       </c>
       <c r="H12" t="n">
         <v>495625</v>
@@ -746,7 +746,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G13" t="n">
-        <v>3.10509490966797</v>
+        <v>3.10509514808655</v>
       </c>
       <c r="H13" t="n">
         <v>432540</v>
@@ -775,7 +775,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G14" t="n">
-        <v>3.07618069648743</v>
+        <v>3.07618045806885</v>
       </c>
       <c r="H14" t="n">
         <v>329562</v>
@@ -862,7 +862,7 @@
         <v>3.87800002098083</v>
       </c>
       <c r="G17" t="n">
-        <v>3.11473321914673</v>
+        <v>3.11473345756531</v>
       </c>
       <c r="H17" t="n">
         <v>703085</v>
@@ -949,7 +949,7 @@
         <v>3.85400009155273</v>
       </c>
       <c r="G20" t="n">
-        <v>3.09545707702637</v>
+        <v>3.09545683860779</v>
       </c>
       <c r="H20" t="n">
         <v>152311</v>
@@ -1007,7 +1007,7 @@
         <v>4.03599977493286</v>
       </c>
       <c r="G22" t="n">
-        <v>3.24163603782654</v>
+        <v>3.24163579940796</v>
       </c>
       <c r="H22" t="n">
         <v>2215703</v>
@@ -1036,7 +1036,7 @@
         <v>4.08599996566772</v>
       </c>
       <c r="G23" t="n">
-        <v>3.28179478645325</v>
+        <v>3.28179502487183</v>
       </c>
       <c r="H23" t="n">
         <v>883458</v>
@@ -1065,7 +1065,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G24" t="n">
-        <v>3.37335681915283</v>
+        <v>3.37335729598999</v>
       </c>
       <c r="H24" t="n">
         <v>496061</v>
@@ -1094,7 +1094,7 @@
         <v>4.2039999961853</v>
       </c>
       <c r="G25" t="n">
-        <v>3.37657046318054</v>
+        <v>3.37657070159912</v>
       </c>
       <c r="H25" t="n">
         <v>820838</v>
@@ -1210,7 +1210,7 @@
         <v>3.96199989318848</v>
       </c>
       <c r="G29" t="n">
-        <v>3.18220019340515</v>
+        <v>3.18220043182373</v>
       </c>
       <c r="H29" t="n">
         <v>734711</v>
@@ -1239,7 +1239,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G30" t="n">
-        <v>3.09224462509155</v>
+        <v>3.09224438667297</v>
       </c>
       <c r="H30" t="n">
         <v>1009207</v>
@@ -1297,7 +1297,7 @@
         <v>3.77600002288818</v>
       </c>
       <c r="G32" t="n">
-        <v>3.03280901908875</v>
+        <v>3.03280878067017</v>
       </c>
       <c r="H32" t="n">
         <v>323753</v>
@@ -1326,7 +1326,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G33" t="n">
-        <v>3.11634016036987</v>
+        <v>3.11633992195129</v>
       </c>
       <c r="H33" t="n">
         <v>310036</v>
@@ -1355,7 +1355,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G34" t="n">
-        <v>3.05208492279053</v>
+        <v>3.05208516120911</v>
       </c>
       <c r="H34" t="n">
         <v>557758</v>
@@ -1384,7 +1384,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G35" t="n">
-        <v>3.09224462509155</v>
+        <v>3.09224438667297</v>
       </c>
       <c r="H35" t="n">
         <v>171266</v>
@@ -1413,7 +1413,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G36" t="n">
-        <v>3.10830807685852</v>
+        <v>3.10830783843994</v>
       </c>
       <c r="H36" t="n">
         <v>185762</v>
@@ -1442,7 +1442,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G37" t="n">
-        <v>3.12437200546265</v>
+        <v>3.12437152862549</v>
       </c>
       <c r="H37" t="n">
         <v>380957</v>
@@ -1500,7 +1500,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G39" t="n">
-        <v>3.14204168319702</v>
+        <v>3.14204144477844</v>
       </c>
       <c r="H39" t="n">
         <v>136060</v>
@@ -1529,7 +1529,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G40" t="n">
-        <v>2.97979855537415</v>
+        <v>2.97979879379272</v>
       </c>
       <c r="H40" t="n">
         <v>684300</v>
@@ -1558,7 +1558,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G41" t="n">
-        <v>2.93964028358459</v>
+        <v>2.93964004516602</v>
       </c>
       <c r="H41" t="n">
         <v>407560</v>
@@ -1587,7 +1587,7 @@
         <v>3.72199988365173</v>
       </c>
       <c r="G42" t="n">
-        <v>2.98943686485291</v>
+        <v>2.98943710327148</v>
       </c>
       <c r="H42" t="n">
         <v>311195</v>
@@ -1616,7 +1616,7 @@
         <v>3.82599997520447</v>
       </c>
       <c r="G43" t="n">
-        <v>3.07296776771545</v>
+        <v>3.07296752929688</v>
       </c>
       <c r="H43" t="n">
         <v>210719</v>
@@ -1645,7 +1645,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G44" t="n">
-        <v>3.17256259918213</v>
+        <v>3.17256236076355</v>
       </c>
       <c r="H44" t="n">
         <v>758567</v>
@@ -1674,7 +1674,7 @@
         <v>3.9539999961853</v>
       </c>
       <c r="G45" t="n">
-        <v>3.17577505111694</v>
+        <v>3.17577528953552</v>
       </c>
       <c r="H45" t="n">
         <v>165143</v>
@@ -1732,7 +1732,7 @@
         <v>3.94400000572205</v>
       </c>
       <c r="G47" t="n">
-        <v>3.16774296760559</v>
+        <v>3.16774320602417</v>
       </c>
       <c r="H47" t="n">
         <v>664780</v>
@@ -1906,7 +1906,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>3.02798986434937</v>
+        <v>3.02798962593079</v>
       </c>
       <c r="H53" t="n">
         <v>104387</v>
@@ -1935,7 +1935,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G54" t="n">
-        <v>3.06332945823669</v>
+        <v>3.06332969665527</v>
       </c>
       <c r="H54" t="n">
         <v>74082</v>
@@ -1964,7 +1964,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G55" t="n">
-        <v>3.02638363838196</v>
+        <v>3.0263831615448</v>
       </c>
       <c r="H55" t="n">
         <v>134715</v>
@@ -1993,7 +1993,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G56" t="n">
-        <v>3.02798986434937</v>
+        <v>3.02798962593079</v>
       </c>
       <c r="H56" t="n">
         <v>69428</v>
@@ -2051,7 +2051,7 @@
         <v>3.7960000038147</v>
       </c>
       <c r="G58" t="n">
-        <v>3.04887247085571</v>
+        <v>3.04887223243713</v>
       </c>
       <c r="H58" t="n">
         <v>132562</v>
@@ -2080,7 +2080,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G59" t="n">
-        <v>3.01995825767517</v>
+        <v>3.01995801925659</v>
       </c>
       <c r="H59" t="n">
         <v>243271</v>
@@ -2109,7 +2109,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G60" t="n">
-        <v>3.07618069648743</v>
+        <v>3.07618045806885</v>
       </c>
       <c r="H60" t="n">
         <v>131782</v>
@@ -2167,7 +2167,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.09224462509155</v>
+        <v>3.09224438667297</v>
       </c>
       <c r="H62" t="n">
         <v>138474</v>
@@ -2225,7 +2225,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05208492279053</v>
+        <v>3.05208516120911</v>
       </c>
       <c r="H64" t="n">
         <v>799099</v>
@@ -2254,7 +2254,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G65" t="n">
-        <v>3.15649890899658</v>
+        <v>3.156498670578</v>
       </c>
       <c r="H65" t="n">
         <v>187657</v>
@@ -2283,7 +2283,7 @@
         <v>3.87199997901917</v>
       </c>
       <c r="G66" t="n">
-        <v>3.10991430282593</v>
+        <v>3.10991454124451</v>
       </c>
       <c r="H66" t="n">
         <v>54407</v>
@@ -2312,7 +2312,7 @@
         <v>3.80200004577637</v>
       </c>
       <c r="G67" t="n">
-        <v>3.05369210243225</v>
+        <v>3.05369138717651</v>
       </c>
       <c r="H67" t="n">
         <v>232784</v>
@@ -2399,7 +2399,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>3.30910301208496</v>
+        <v>3.30910325050354</v>
       </c>
       <c r="H70" t="n">
         <v>1980454</v>
@@ -2457,7 +2457,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G72" t="n">
-        <v>3.44725036621094</v>
+        <v>3.44724988937378</v>
       </c>
       <c r="H72" t="n">
         <v>673655</v>
@@ -2515,7 +2515,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G74" t="n">
-        <v>3.47777032852173</v>
+        <v>3.47777104377747</v>
       </c>
       <c r="H74" t="n">
         <v>466148</v>
@@ -2544,7 +2544,7 @@
         <v>4.28200006484985</v>
       </c>
       <c r="G75" t="n">
-        <v>3.43921828269958</v>
+        <v>3.43921852111816</v>
       </c>
       <c r="H75" t="n">
         <v>1103849</v>
@@ -2602,7 +2602,7 @@
         <v>4.10400009155273</v>
       </c>
       <c r="G77" t="n">
-        <v>3.29625248908997</v>
+        <v>3.29625225067139</v>
       </c>
       <c r="H77" t="n">
         <v>396177</v>
@@ -2631,7 +2631,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G78" t="n">
-        <v>3.2609121799469</v>
+        <v>3.26091241836548</v>
       </c>
       <c r="H78" t="n">
         <v>312201</v>
@@ -2660,7 +2660,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>3.2609121799469</v>
+        <v>3.26091241836548</v>
       </c>
       <c r="H79" t="n">
         <v>87110</v>
@@ -2689,7 +2689,7 @@
         <v>4.03200006484985</v>
       </c>
       <c r="G80" t="n">
-        <v>3.23842334747314</v>
+        <v>3.23842358589172</v>
       </c>
       <c r="H80" t="n">
         <v>255441</v>
@@ -2718,7 +2718,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>3.30107116699219</v>
+        <v>3.30107164382935</v>
       </c>
       <c r="H81" t="n">
         <v>411788</v>
@@ -2776,7 +2776,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G83" t="n">
-        <v>3.31713485717773</v>
+        <v>3.31713509559631</v>
       </c>
       <c r="H83" t="n">
         <v>133194</v>
@@ -2805,7 +2805,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G84" t="n">
-        <v>3.29303932189941</v>
+        <v>3.29303979873657</v>
       </c>
       <c r="H84" t="n">
         <v>107404</v>
@@ -2834,7 +2834,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G85" t="n">
-        <v>3.2609121799469</v>
+        <v>3.26091241836548</v>
       </c>
       <c r="H85" t="n">
         <v>177386</v>
@@ -2863,7 +2863,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G86" t="n">
-        <v>3.32516646385193</v>
+        <v>3.32516622543335</v>
       </c>
       <c r="H86" t="n">
         <v>123566</v>
@@ -2921,7 +2921,7 @@
         <v>4.19600009918213</v>
       </c>
       <c r="G88" t="n">
-        <v>3.3701446056366</v>
+        <v>3.37014484405518</v>
       </c>
       <c r="H88" t="n">
         <v>175860</v>
@@ -2979,7 +2979,7 @@
         <v>4.29400014877319</v>
       </c>
       <c r="G90" t="n">
-        <v>3.44885683059692</v>
+        <v>3.44885635375977</v>
       </c>
       <c r="H90" t="n">
         <v>203030</v>
@@ -3008,7 +3008,7 @@
         <v>4.24399995803833</v>
       </c>
       <c r="G91" t="n">
-        <v>3.40869736671448</v>
+        <v>3.40869760513306</v>
       </c>
       <c r="H91" t="n">
         <v>141724</v>
@@ -3037,7 +3037,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G92" t="n">
-        <v>3.40548491477966</v>
+        <v>3.40548467636108</v>
       </c>
       <c r="H92" t="n">
         <v>193349</v>
@@ -3066,7 +3066,7 @@
         <v>4.26399993896484</v>
       </c>
       <c r="G93" t="n">
-        <v>3.42476105690002</v>
+        <v>3.42476058006287</v>
       </c>
       <c r="H93" t="n">
         <v>424802</v>
@@ -3095,7 +3095,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G94" t="n">
-        <v>3.40548491477966</v>
+        <v>3.40548467636108</v>
       </c>
       <c r="H94" t="n">
         <v>278384</v>
@@ -3124,7 +3124,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G95" t="n">
-        <v>3.38138937950134</v>
+        <v>3.38138890266418</v>
       </c>
       <c r="H95" t="n">
         <v>152895</v>
@@ -3182,7 +3182,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G97" t="n">
-        <v>3.30910301208496</v>
+        <v>3.30910325050354</v>
       </c>
       <c r="H97" t="n">
         <v>67040</v>
@@ -3240,7 +3240,7 @@
         <v>4.17399978637695</v>
       </c>
       <c r="G99" t="n">
-        <v>3.35247468948364</v>
+        <v>3.35247492790222</v>
       </c>
       <c r="H99" t="n">
         <v>217904</v>
@@ -3269,7 +3269,7 @@
         <v>4.26599979400635</v>
       </c>
       <c r="G100" t="n">
-        <v>3.42636728286743</v>
+        <v>3.42636704444885</v>
       </c>
       <c r="H100" t="n">
         <v>203777</v>
@@ -3298,7 +3298,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G101" t="n">
-        <v>3.39745283126831</v>
+        <v>3.39745306968689</v>
       </c>
       <c r="H101" t="n">
         <v>77789</v>
@@ -3356,7 +3356,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>3.44564318656921</v>
+        <v>3.44564390182495</v>
       </c>
       <c r="H103" t="n">
         <v>311944</v>
@@ -3414,7 +3414,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G105" t="n">
-        <v>3.49383425712585</v>
+        <v>3.49383473396301</v>
       </c>
       <c r="H105" t="n">
         <v>405770</v>
@@ -3443,7 +3443,7 @@
         <v>4.33599996566772</v>
       </c>
       <c r="G106" t="n">
-        <v>3.48258996009827</v>
+        <v>3.48258948326111</v>
       </c>
       <c r="H106" t="n">
         <v>225109</v>
@@ -3472,7 +3472,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G107" t="n">
-        <v>3.51471734046936</v>
+        <v>3.51471710205078</v>
       </c>
       <c r="H107" t="n">
         <v>376542</v>
@@ -3530,7 +3530,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G109" t="n">
-        <v>3.50186657905579</v>
+        <v>3.50186681747437</v>
       </c>
       <c r="H109" t="n">
         <v>202972</v>
@@ -3559,7 +3559,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>3.53399348258972</v>
+        <v>3.5339937210083</v>
       </c>
       <c r="H110" t="n">
         <v>793170</v>
@@ -3704,7 +3704,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>3.58218479156494</v>
+        <v>3.58218431472778</v>
       </c>
       <c r="H115" t="n">
         <v>701221</v>
@@ -3791,7 +3791,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G118" t="n">
-        <v>3.53399348258972</v>
+        <v>3.5339937210083</v>
       </c>
       <c r="H118" t="n">
         <v>371953</v>
@@ -3820,7 +3820,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G119" t="n">
-        <v>3.54202508926392</v>
+        <v>3.5420253276825</v>
       </c>
       <c r="H119" t="n">
         <v>325731</v>
@@ -3878,7 +3878,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G121" t="n">
-        <v>3.50186657905579</v>
+        <v>3.50186681747437</v>
       </c>
       <c r="H121" t="n">
         <v>564523</v>
@@ -3907,7 +3907,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G122" t="n">
-        <v>3.50186657905579</v>
+        <v>3.50186681747437</v>
       </c>
       <c r="H122" t="n">
         <v>908694</v>
@@ -3936,7 +3936,7 @@
         <v>4.24200010299683</v>
       </c>
       <c r="G123" t="n">
-        <v>3.40709066390991</v>
+        <v>3.40709137916565</v>
       </c>
       <c r="H123" t="n">
         <v>362530</v>
@@ -3994,7 +3994,7 @@
         <v>4.16200017929077</v>
       </c>
       <c r="G125" t="n">
-        <v>3.34283709526062</v>
+        <v>3.34283685684204</v>
       </c>
       <c r="H125" t="n">
         <v>612073</v>
@@ -4023,7 +4023,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G126" t="n">
-        <v>3.32034754753113</v>
+        <v>3.32034707069397</v>
       </c>
       <c r="H126" t="n">
         <v>298982</v>
@@ -4052,7 +4052,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G127" t="n">
-        <v>3.27858209609985</v>
+        <v>3.2785816192627</v>
       </c>
       <c r="H127" t="n">
         <v>883348</v>
@@ -4081,7 +4081,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G128" t="n">
-        <v>3.22878503799438</v>
+        <v>3.22878456115723</v>
       </c>
       <c r="H128" t="n">
         <v>610819</v>
@@ -4139,7 +4139,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G130" t="n">
-        <v>3.30107116699219</v>
+        <v>3.30107164382935</v>
       </c>
       <c r="H130" t="n">
         <v>185659</v>
@@ -4168,7 +4168,7 @@
         <v>4.06799983978271</v>
       </c>
       <c r="G131" t="n">
-        <v>3.26733732223511</v>
+        <v>3.26733756065369</v>
       </c>
       <c r="H131" t="n">
         <v>190952</v>
@@ -4197,7 +4197,7 @@
         <v>4.00600004196167</v>
       </c>
       <c r="G132" t="n">
-        <v>3.21754050254822</v>
+        <v>3.2175407409668</v>
       </c>
       <c r="H132" t="n">
         <v>254655</v>
@@ -4226,7 +4226,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G133" t="n">
-        <v>3.18541288375854</v>
+        <v>3.1854133605957</v>
       </c>
       <c r="H133" t="n">
         <v>377784</v>
@@ -4313,7 +4313,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G136" t="n">
-        <v>3.09866952896118</v>
+        <v>3.09866976737976</v>
       </c>
       <c r="H136" t="n">
         <v>1725561</v>
@@ -4342,7 +4342,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G137" t="n">
-        <v>3.07618069648743</v>
+        <v>3.07618045806885</v>
       </c>
       <c r="H137" t="n">
         <v>628982</v>
@@ -4371,7 +4371,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>3.05208492279053</v>
+        <v>3.05208516120911</v>
       </c>
       <c r="H138" t="n">
         <v>561787</v>
@@ -4400,7 +4400,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G139" t="n">
-        <v>3.05208492279053</v>
+        <v>3.05208516120911</v>
       </c>
       <c r="H139" t="n">
         <v>586423</v>
@@ -4429,7 +4429,7 @@
         <v>3.76200008392334</v>
       </c>
       <c r="G140" t="n">
-        <v>3.02156472206116</v>
+        <v>3.02156400680542</v>
       </c>
       <c r="H140" t="n">
         <v>339829</v>
@@ -4487,7 +4487,7 @@
         <v>3.7720000743866</v>
       </c>
       <c r="G142" t="n">
-        <v>3.02959656715393</v>
+        <v>3.02959632873535</v>
       </c>
       <c r="H142" t="n">
         <v>406436</v>
@@ -4603,7 +4603,7 @@
         <v>3.82200002670288</v>
       </c>
       <c r="G146" t="n">
-        <v>3.06975507736206</v>
+        <v>3.06975531578064</v>
       </c>
       <c r="H146" t="n">
         <v>486399</v>
@@ -4661,7 +4661,7 @@
         <v>4.05800008773804</v>
       </c>
       <c r="G148" t="n">
-        <v>3.25930619239807</v>
+        <v>3.25930643081665</v>
       </c>
       <c r="H148" t="n">
         <v>668163</v>
@@ -4719,7 +4719,7 @@
         <v>4.11800003051758</v>
       </c>
       <c r="G150" t="n">
-        <v>3.30749654769897</v>
+        <v>3.30749702453613</v>
       </c>
       <c r="H150" t="n">
         <v>449081</v>
@@ -4748,7 +4748,7 @@
         <v>4.16800022125244</v>
       </c>
       <c r="G151" t="n">
-        <v>3.34765577316284</v>
+        <v>3.34765553474426</v>
       </c>
       <c r="H151" t="n">
         <v>298680</v>
@@ -4777,7 +4777,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G152" t="n">
-        <v>3.2609121799469</v>
+        <v>3.26091241836548</v>
       </c>
       <c r="H152" t="n">
         <v>1639289</v>
@@ -4835,7 +4835,7 @@
         <v>3.97199988365173</v>
       </c>
       <c r="G154" t="n">
-        <v>3.19023203849792</v>
+        <v>3.1902322769165</v>
       </c>
       <c r="H154" t="n">
         <v>259580</v>
@@ -4893,7 +4893,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G156" t="n">
-        <v>3.2609121799469</v>
+        <v>3.26091241836548</v>
       </c>
       <c r="H156" t="n">
         <v>360580</v>
@@ -4980,7 +4980,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G159" t="n">
-        <v>3.39745283126831</v>
+        <v>3.39745306968689</v>
       </c>
       <c r="H159" t="n">
         <v>327352</v>
@@ -5009,7 +5009,7 @@
         <v>4.25799989700317</v>
       </c>
       <c r="G160" t="n">
-        <v>3.41994142532349</v>
+        <v>3.41994166374207</v>
       </c>
       <c r="H160" t="n">
         <v>282787</v>
@@ -5067,7 +5067,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G162" t="n">
-        <v>3.50186657905579</v>
+        <v>3.50186681747437</v>
       </c>
       <c r="H162" t="n">
         <v>672061</v>
@@ -5096,7 +5096,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>3.55005717277527</v>
+        <v>3.55005693435669</v>
       </c>
       <c r="H163" t="n">
         <v>1107883</v>
@@ -5125,7 +5125,7 @@
         <v>4.39799976348877</v>
       </c>
       <c r="G164" t="n">
-        <v>3.53238725662231</v>
+        <v>3.53238749504089</v>
       </c>
       <c r="H164" t="n">
         <v>598088</v>
@@ -5154,7 +5154,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>3.49383425712585</v>
+        <v>3.49383473396301</v>
       </c>
       <c r="H165" t="n">
         <v>768174</v>
@@ -5183,7 +5183,7 @@
         <v>4.37200021743774</v>
       </c>
       <c r="G166" t="n">
-        <v>3.51150441169739</v>
+        <v>3.51150465011597</v>
       </c>
       <c r="H166" t="n">
         <v>507187</v>
@@ -5212,7 +5212,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G167" t="n">
-        <v>3.51793003082275</v>
+        <v>3.51792979240417</v>
       </c>
       <c r="H167" t="n">
         <v>279292</v>
@@ -5241,7 +5241,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G168" t="n">
-        <v>3.56772708892822</v>
+        <v>3.5677273273468</v>
       </c>
       <c r="H168" t="n">
         <v>343498</v>
@@ -5270,7 +5270,7 @@
         <v>4.4060001373291</v>
       </c>
       <c r="G169" t="n">
-        <v>3.53881239891052</v>
+        <v>3.5388126373291</v>
       </c>
       <c r="H169" t="n">
         <v>139582</v>
@@ -5299,7 +5299,7 @@
         <v>4.48600006103516</v>
       </c>
       <c r="G170" t="n">
-        <v>3.60306763648987</v>
+        <v>3.60306715965271</v>
       </c>
       <c r="H170" t="n">
         <v>583667</v>
@@ -5328,7 +5328,7 @@
         <v>4.4520001411438</v>
       </c>
       <c r="G171" t="n">
-        <v>3.57575869560242</v>
+        <v>3.57575917243958</v>
       </c>
       <c r="H171" t="n">
         <v>440026</v>
@@ -5357,7 +5357,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G172" t="n">
-        <v>3.55166363716125</v>
+        <v>3.55166339874268</v>
       </c>
       <c r="H172" t="n">
         <v>129754</v>
@@ -5386,7 +5386,7 @@
         <v>4.43200016021729</v>
       </c>
       <c r="G173" t="n">
-        <v>3.55969548225403</v>
+        <v>3.55969524383545</v>
       </c>
       <c r="H173" t="n">
         <v>147634</v>
@@ -5415,7 +5415,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G174" t="n">
-        <v>3.68499135971069</v>
+        <v>3.68499112129211</v>
       </c>
       <c r="H174" t="n">
         <v>193382</v>
@@ -5444,7 +5444,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G175" t="n">
-        <v>3.69462966918945</v>
+        <v>3.69462943077087</v>
       </c>
       <c r="H175" t="n">
         <v>238020</v>
@@ -5473,7 +5473,7 @@
         <v>4.55399990081787</v>
       </c>
       <c r="G176" t="n">
-        <v>3.65768337249756</v>
+        <v>3.6576828956604</v>
       </c>
       <c r="H176" t="n">
         <v>156694</v>
@@ -5531,7 +5531,7 @@
         <v>4.61800003051758</v>
       </c>
       <c r="G178" t="n">
-        <v>3.70908665657043</v>
+        <v>3.70908617973328</v>
       </c>
       <c r="H178" t="n">
         <v>89377</v>
@@ -5560,7 +5560,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G179" t="n">
-        <v>3.72354459762573</v>
+        <v>3.72354483604431</v>
       </c>
       <c r="H179" t="n">
         <v>190146</v>
@@ -5618,7 +5618,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G181" t="n">
-        <v>3.83759570121765</v>
+        <v>3.83759593963623</v>
       </c>
       <c r="H181" t="n">
         <v>791649</v>
@@ -5647,7 +5647,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G182" t="n">
-        <v>3.72675633430481</v>
+        <v>3.72675681114197</v>
       </c>
       <c r="H182" t="n">
         <v>546096</v>
@@ -5676,7 +5676,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G183" t="n">
-        <v>3.91951966285706</v>
+        <v>3.91952037811279</v>
       </c>
       <c r="H183" t="n">
         <v>579585</v>
@@ -5705,7 +5705,7 @@
         <v>4.78800010681152</v>
       </c>
       <c r="G184" t="n">
-        <v>3.84562706947327</v>
+        <v>3.84562730789185</v>
       </c>
       <c r="H184" t="n">
         <v>904676</v>
@@ -5763,7 +5763,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G186" t="n">
-        <v>3.82313871383667</v>
+        <v>3.82313895225525</v>
       </c>
       <c r="H186" t="n">
         <v>298166</v>
@@ -5792,7 +5792,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G187" t="n">
-        <v>3.85526514053345</v>
+        <v>3.85526609420776</v>
       </c>
       <c r="H187" t="n">
         <v>302213</v>
@@ -5850,7 +5850,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G189" t="n">
-        <v>3.79743695259094</v>
+        <v>3.79743671417236</v>
       </c>
       <c r="H189" t="n">
         <v>493777</v>
@@ -5908,7 +5908,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G191" t="n">
-        <v>3.79261755943298</v>
+        <v>3.79261708259583</v>
       </c>
       <c r="H191" t="n">
         <v>386473</v>
@@ -5937,7 +5937,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G192" t="n">
-        <v>3.89381814002991</v>
+        <v>3.89381790161133</v>
       </c>
       <c r="H192" t="n">
         <v>448831</v>
@@ -5966,7 +5966,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G193" t="n">
-        <v>3.82313871383667</v>
+        <v>3.82313895225525</v>
       </c>
       <c r="H193" t="n">
         <v>308097</v>
@@ -5995,7 +5995,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G194" t="n">
-        <v>3.72675633430481</v>
+        <v>3.72675681114197</v>
       </c>
       <c r="H194" t="n">
         <v>468393</v>
@@ -6053,7 +6053,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G196" t="n">
-        <v>3.78297972679138</v>
+        <v>3.78297924995422</v>
       </c>
       <c r="H196" t="n">
         <v>366384</v>
@@ -6082,7 +6082,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.89381814002991</v>
+        <v>3.89381790161133</v>
       </c>
       <c r="H197" t="n">
         <v>181707</v>
@@ -6140,7 +6140,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G199" t="n">
-        <v>3.85526514053345</v>
+        <v>3.85526609420776</v>
       </c>
       <c r="H199" t="n">
         <v>383644</v>
@@ -6169,7 +6169,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G200" t="n">
-        <v>3.89542484283447</v>
+        <v>3.89542412757874</v>
       </c>
       <c r="H200" t="n">
         <v>163561</v>
@@ -6198,7 +6198,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G201" t="n">
-        <v>3.81832003593445</v>
+        <v>3.81831908226013</v>
       </c>
       <c r="H201" t="n">
         <v>370261</v>
@@ -6227,7 +6227,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G202" t="n">
-        <v>3.80064940452576</v>
+        <v>3.8006489276886</v>
       </c>
       <c r="H202" t="n">
         <v>251113</v>
@@ -6256,7 +6256,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G203" t="n">
-        <v>3.75085258483887</v>
+        <v>3.75085234642029</v>
       </c>
       <c r="H203" t="n">
         <v>390479</v>
@@ -6285,7 +6285,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G204" t="n">
-        <v>3.84402084350586</v>
+        <v>3.84402060508728</v>
       </c>
       <c r="H204" t="n">
         <v>245549</v>
@@ -6314,7 +6314,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G205" t="n">
-        <v>3.87132906913757</v>
+        <v>3.87132930755615</v>
       </c>
       <c r="H205" t="n">
         <v>157069</v>
@@ -6343,7 +6343,7 @@
         <v>4.92399978637695</v>
       </c>
       <c r="G206" t="n">
-        <v>3.95485925674438</v>
+        <v>3.95485973358154</v>
       </c>
       <c r="H206" t="n">
         <v>480892</v>
@@ -6401,7 +6401,7 @@
         <v>4.85799980163574</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90184998512268</v>
+        <v>3.90184950828552</v>
       </c>
       <c r="H208" t="n">
         <v>95274</v>
@@ -6459,7 +6459,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G210" t="n">
-        <v>3.87132906913757</v>
+        <v>3.87132930755615</v>
       </c>
       <c r="H210" t="n">
         <v>196979</v>
@@ -6488,7 +6488,7 @@
         <v>4.89400005340576</v>
       </c>
       <c r="G211" t="n">
-        <v>3.93076467514038</v>
+        <v>3.93076515197754</v>
       </c>
       <c r="H211" t="n">
         <v>186334</v>
@@ -6517,7 +6517,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G212" t="n">
-        <v>3.98377442359924</v>
+        <v>3.9837749004364</v>
       </c>
       <c r="H212" t="n">
         <v>476692</v>
@@ -6604,7 +6604,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G215" t="n">
-        <v>3.94361567497253</v>
+        <v>3.94361519813538</v>
       </c>
       <c r="H215" t="n">
         <v>162673</v>
@@ -6633,7 +6633,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G216" t="n">
-        <v>3.96931719779968</v>
+        <v>3.96931672096252</v>
       </c>
       <c r="H216" t="n">
         <v>335691</v>
@@ -6662,7 +6662,7 @@
         <v>5</v>
       </c>
       <c r="G217" t="n">
-        <v>4.01590156555176</v>
+        <v>4.01590204238892</v>
       </c>
       <c r="H217" t="n">
         <v>449215</v>
@@ -6691,7 +6691,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G218" t="n">
-        <v>4.01108264923096</v>
+        <v>4.01108169555664</v>
       </c>
       <c r="H218" t="n">
         <v>233142</v>
@@ -6720,7 +6720,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G219" t="n">
-        <v>4.08818769454956</v>
+        <v>4.08818817138672</v>
       </c>
       <c r="H219" t="n">
         <v>737410</v>
@@ -6749,7 +6749,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G220" t="n">
-        <v>4.20063400268555</v>
+        <v>4.20063352584839</v>
       </c>
       <c r="H220" t="n">
         <v>1260619</v>
@@ -6778,7 +6778,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G221" t="n">
-        <v>4.3612699508667</v>
+        <v>4.36126899719238</v>
       </c>
       <c r="H221" t="n">
         <v>900907</v>
@@ -6836,7 +6836,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G223" t="n">
-        <v>4.25284004211426</v>
+        <v>4.2528395652771</v>
       </c>
       <c r="H223" t="n">
         <v>776210</v>
@@ -6865,7 +6865,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G224" t="n">
-        <v>4.2970142364502</v>
+        <v>4.29701471328735</v>
       </c>
       <c r="H224" t="n">
         <v>796607</v>
@@ -6894,7 +6894,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G225" t="n">
-        <v>4.51387405395508</v>
+        <v>4.51387310028076</v>
       </c>
       <c r="H225" t="n">
         <v>1018653</v>
@@ -6923,7 +6923,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G226" t="n">
-        <v>4.6785249710083</v>
+        <v>4.67852544784546</v>
       </c>
       <c r="H226" t="n">
         <v>1310648</v>
@@ -6981,7 +6981,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G228" t="n">
-        <v>4.9034161567688</v>
+        <v>4.90341663360596</v>
       </c>
       <c r="H228" t="n">
         <v>3004424</v>
@@ -7010,7 +7010,7 @@
         <v>5.875</v>
       </c>
       <c r="G229" t="n">
-        <v>4.71868419647217</v>
+        <v>4.71868371963501</v>
       </c>
       <c r="H229" t="n">
         <v>1865543</v>
@@ -7068,7 +7068,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G231" t="n">
-        <v>4.74679517745972</v>
+        <v>4.74679565429688</v>
       </c>
       <c r="H231" t="n">
         <v>919184</v>
@@ -7242,7 +7242,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>5.10019445419312</v>
+        <v>5.10019493103027</v>
       </c>
       <c r="H237" t="n">
         <v>1114196</v>
@@ -7300,7 +7300,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G239" t="n">
-        <v>5.07609987258911</v>
+        <v>5.07609939575195</v>
       </c>
       <c r="H239" t="n">
         <v>760860</v>
@@ -7329,7 +7329,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G240" t="n">
-        <v>5.19256067276001</v>
+        <v>5.19256162643433</v>
       </c>
       <c r="H240" t="n">
         <v>1832524</v>
@@ -7387,7 +7387,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G242" t="n">
-        <v>5.27287912368774</v>
+        <v>5.27287817001343</v>
       </c>
       <c r="H242" t="n">
         <v>618521</v>
@@ -7474,7 +7474,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G245" t="n">
-        <v>5.46965789794922</v>
+        <v>5.46965837478638</v>
       </c>
       <c r="H245" t="n">
         <v>1017551</v>
@@ -7532,7 +7532,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G247" t="n">
-        <v>5.20862436294556</v>
+        <v>5.20862531661987</v>
       </c>
       <c r="H247" t="n">
         <v>1584376</v>
@@ -7590,7 +7590,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G249" t="n">
-        <v>5.44957780838013</v>
+        <v>5.44957828521729</v>
       </c>
       <c r="H249" t="n">
         <v>645486</v>
@@ -7619,7 +7619,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>5.49375295639038</v>
+        <v>5.49375343322754</v>
       </c>
       <c r="H250" t="n">
         <v>749096</v>
@@ -7677,7 +7677,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>5.60619974136353</v>
+        <v>5.60619926452637</v>
       </c>
       <c r="H252" t="n">
         <v>773502</v>
@@ -7735,7 +7735,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G254" t="n">
-        <v>5.69856452941895</v>
+        <v>5.69856405258179</v>
       </c>
       <c r="H254" t="n">
         <v>1236193</v>
@@ -7764,7 +7764,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G255" t="n">
-        <v>5.71864366531372</v>
+        <v>5.71864414215088</v>
       </c>
       <c r="H255" t="n">
         <v>1090441</v>
@@ -7822,7 +7822,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G257" t="n">
-        <v>5.68250131607056</v>
+        <v>5.68250036239624</v>
       </c>
       <c r="H257" t="n">
         <v>963358</v>
@@ -7880,7 +7880,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G259" t="n">
-        <v>5.38130807876587</v>
+        <v>5.38130855560303</v>
       </c>
       <c r="H259" t="n">
         <v>970912</v>
@@ -7909,7 +7909,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G260" t="n">
-        <v>5.38933944702148</v>
+        <v>5.3893404006958</v>
       </c>
       <c r="H260" t="n">
         <v>669092</v>
@@ -7938,7 +7938,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G261" t="n">
-        <v>5.36926078796387</v>
+        <v>5.36926031112671</v>
       </c>
       <c r="H261" t="n">
         <v>537195</v>
@@ -7967,7 +7967,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G262" t="n">
-        <v>5.46965789794922</v>
+        <v>5.46965837478638</v>
       </c>
       <c r="H262" t="n">
         <v>703316</v>
@@ -7996,7 +7996,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>5.50580072402954</v>
+        <v>5.5058012008667</v>
       </c>
       <c r="H263" t="n">
         <v>676673</v>
@@ -8025,7 +8025,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>5.46162700653076</v>
+        <v>5.46162605285645</v>
       </c>
       <c r="H264" t="n">
         <v>522042</v>
@@ -8054,7 +8054,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G265" t="n">
-        <v>5.49375295639038</v>
+        <v>5.49375343322754</v>
       </c>
       <c r="H265" t="n">
         <v>538125</v>
@@ -8083,7 +8083,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G266" t="n">
-        <v>5.54240703582764</v>
+        <v>5.54240751266479</v>
       </c>
       <c r="H266" t="n">
         <v>512945</v>
@@ -8112,7 +8112,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G267" t="n">
-        <v>5.59511423110962</v>
+        <v>5.59511470794678</v>
       </c>
       <c r="H267" t="n">
         <v>823701</v>
@@ -8141,7 +8141,7 @@
         <v>6.61499977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>5.36401128768921</v>
+        <v>5.36401081085205</v>
       </c>
       <c r="H268" t="n">
         <v>980988</v>
@@ -8170,7 +8170,7 @@
         <v>6.75</v>
       </c>
       <c r="G269" t="n">
-        <v>5.47348117828369</v>
+        <v>5.47348070144653</v>
       </c>
       <c r="H269" t="n">
         <v>1243146</v>
@@ -8199,7 +8199,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>5.55456924438477</v>
+        <v>5.55456972122192</v>
       </c>
       <c r="H270" t="n">
         <v>784034</v>
@@ -8228,7 +8228,7 @@
         <v>6.90999984741211</v>
       </c>
       <c r="G271" t="n">
-        <v>5.60322380065918</v>
+        <v>5.60322284698486</v>
       </c>
       <c r="H271" t="n">
         <v>612681</v>
@@ -8286,7 +8286,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G273" t="n">
-        <v>5.68431234359741</v>
+        <v>5.68431186676025</v>
       </c>
       <c r="H273" t="n">
         <v>492654</v>
@@ -8315,7 +8315,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G274" t="n">
-        <v>5.59511423110962</v>
+        <v>5.59511470794678</v>
       </c>
       <c r="H274" t="n">
         <v>306867</v>
@@ -8344,7 +8344,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G275" t="n">
-        <v>5.70053052902222</v>
+        <v>5.70053005218506</v>
       </c>
       <c r="H275" t="n">
         <v>623116</v>
@@ -8373,7 +8373,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G276" t="n">
-        <v>5.7451286315918</v>
+        <v>5.74512767791748</v>
       </c>
       <c r="H276" t="n">
         <v>552619</v>
@@ -8460,7 +8460,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G279" t="n">
-        <v>5.68431234359741</v>
+        <v>5.68431186676025</v>
       </c>
       <c r="H279" t="n">
         <v>19536694</v>
@@ -8489,7 +8489,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G280" t="n">
-        <v>5.73701953887939</v>
+        <v>5.73701906204224</v>
       </c>
       <c r="H280" t="n">
         <v>449238</v>
@@ -8576,7 +8576,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G283" t="n">
-        <v>5.63160467147827</v>
+        <v>5.63160371780396</v>
       </c>
       <c r="H283" t="n">
         <v>451788</v>
@@ -8605,7 +8605,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G284" t="n">
-        <v>5.65593099594116</v>
+        <v>5.65593004226685</v>
       </c>
       <c r="H284" t="n">
         <v>382910</v>
@@ -8634,7 +8634,7 @@
         <v>6.83500003814697</v>
       </c>
       <c r="G285" t="n">
-        <v>5.54240703582764</v>
+        <v>5.54240751266479</v>
       </c>
       <c r="H285" t="n">
         <v>431885</v>
@@ -8663,7 +8663,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G286" t="n">
-        <v>5.55051612854004</v>
+        <v>5.55051565170288</v>
       </c>
       <c r="H286" t="n">
         <v>407518</v>
@@ -8692,7 +8692,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G287" t="n">
-        <v>5.59511423110962</v>
+        <v>5.59511470794678</v>
       </c>
       <c r="H287" t="n">
         <v>406942</v>
@@ -8721,7 +8721,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G288" t="n">
-        <v>5.7086386680603</v>
+        <v>5.70863819122314</v>
       </c>
       <c r="H288" t="n">
         <v>632233</v>
@@ -8750,7 +8750,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G289" t="n">
-        <v>5.68431234359741</v>
+        <v>5.68431186676025</v>
       </c>
       <c r="H289" t="n">
         <v>480079</v>
@@ -8808,7 +8808,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G291" t="n">
-        <v>5.66809463500977</v>
+        <v>5.66809368133545</v>
       </c>
       <c r="H291" t="n">
         <v>464166</v>
@@ -8837,7 +8837,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G292" t="n">
-        <v>5.66809463500977</v>
+        <v>5.66809368133545</v>
       </c>
       <c r="H292" t="n">
         <v>539876</v>
@@ -9040,7 +9040,7 @@
         <v>6.84499979019165</v>
       </c>
       <c r="G299" t="n">
-        <v>5.55051612854004</v>
+        <v>5.55051565170288</v>
       </c>
       <c r="H299" t="n">
         <v>570123</v>
@@ -9069,7 +9069,7 @@
         <v>6.74499988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>5.46942710876465</v>
+        <v>5.46942663192749</v>
       </c>
       <c r="H300" t="n">
         <v>468702</v>
@@ -9098,7 +9098,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G301" t="n">
-        <v>5.53024339675903</v>
+        <v>5.53024291992188</v>
       </c>
       <c r="H301" t="n">
         <v>780909</v>
@@ -9127,7 +9127,7 @@
         <v>6.75500011444092</v>
       </c>
       <c r="G302" t="n">
-        <v>5.47753572463989</v>
+        <v>5.47753620147705</v>
       </c>
       <c r="H302" t="n">
         <v>372222</v>
@@ -9243,7 +9243,7 @@
         <v>6.74499988555908</v>
       </c>
       <c r="G306" t="n">
-        <v>5.46942710876465</v>
+        <v>5.46942663192749</v>
       </c>
       <c r="H306" t="n">
         <v>207456</v>
@@ -9330,7 +9330,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G309" t="n">
-        <v>5.45726346969604</v>
+        <v>5.4572639465332</v>
       </c>
       <c r="H309" t="n">
         <v>202930</v>
@@ -9446,7 +9446,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G313" t="n">
-        <v>5.23426961898804</v>
+        <v>5.2342700958252</v>
       </c>
       <c r="H313" t="n">
         <v>914089</v>
@@ -9504,7 +9504,7 @@
         <v>6.25</v>
       </c>
       <c r="G315" t="n">
-        <v>5.06803846359253</v>
+        <v>5.06803798675537</v>
       </c>
       <c r="H315" t="n">
         <v>475804</v>
@@ -9533,7 +9533,7 @@
         <v>6.2350001335144</v>
       </c>
       <c r="G316" t="n">
-        <v>5.05587530136108</v>
+        <v>5.05587482452393</v>
       </c>
       <c r="H316" t="n">
         <v>619286</v>
@@ -9562,7 +9562,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G317" t="n">
-        <v>5.20588970184326</v>
+        <v>5.2058892250061</v>
       </c>
       <c r="H317" t="n">
         <v>593744</v>
@@ -9591,7 +9591,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>5.03154850006104</v>
+        <v>5.03154802322388</v>
       </c>
       <c r="H318" t="n">
         <v>436148</v>
@@ -9620,7 +9620,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G319" t="n">
-        <v>5.10047435760498</v>
+        <v>5.10047388076782</v>
       </c>
       <c r="H319" t="n">
         <v>305179</v>
@@ -9649,7 +9649,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G320" t="n">
-        <v>5.01127624511719</v>
+        <v>5.01127576828003</v>
       </c>
       <c r="H320" t="n">
         <v>272764</v>
@@ -9678,7 +9678,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G321" t="n">
-        <v>5.05992889404297</v>
+        <v>5.05992984771729</v>
       </c>
       <c r="H321" t="n">
         <v>288368</v>
@@ -9707,7 +9707,7 @@
         <v>6.2649998664856</v>
       </c>
       <c r="G322" t="n">
-        <v>5.08020162582397</v>
+        <v>5.08020210266113</v>
       </c>
       <c r="H322" t="n">
         <v>477773</v>
@@ -9736,7 +9736,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G323" t="n">
-        <v>5.25454235076904</v>
+        <v>5.2545428276062</v>
       </c>
       <c r="H323" t="n">
         <v>658969</v>
@@ -9765,7 +9765,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>5.30319595336914</v>
+        <v>5.30319547653198</v>
       </c>
       <c r="H324" t="n">
         <v>433816</v>
@@ -9881,7 +9881,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>5.64782238006592</v>
+        <v>5.64782285690308</v>
       </c>
       <c r="H328" t="n">
         <v>585948</v>
@@ -9910,7 +9910,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>5.50591707229614</v>
+        <v>5.5059175491333</v>
       </c>
       <c r="H329" t="n">
         <v>405442</v>
@@ -9939,7 +9939,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G330" t="n">
-        <v>5.61133241653442</v>
+        <v>5.61133193969727</v>
       </c>
       <c r="H330" t="n">
         <v>815862</v>
@@ -9968,7 +9968,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G331" t="n">
-        <v>5.62754917144775</v>
+        <v>5.62755012512207</v>
       </c>
       <c r="H331" t="n">
         <v>359489</v>
@@ -9997,7 +9997,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G332" t="n">
-        <v>5.59511423110962</v>
+        <v>5.59511470794678</v>
       </c>
       <c r="H332" t="n">
         <v>399791</v>
@@ -10026,7 +10026,7 @@
         <v>6.99499988555908</v>
       </c>
       <c r="G333" t="n">
-        <v>5.67214822769165</v>
+        <v>5.67214870452881</v>
       </c>
       <c r="H333" t="n">
         <v>390070</v>
@@ -10055,7 +10055,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G334" t="n">
-        <v>5.66403961181641</v>
+        <v>5.66404008865356</v>
       </c>
       <c r="H334" t="n">
         <v>498383</v>
@@ -10084,7 +10084,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G335" t="n">
-        <v>5.7451286315918</v>
+        <v>5.74512767791748</v>
       </c>
       <c r="H335" t="n">
         <v>314405</v>
@@ -10113,7 +10113,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G336" t="n">
-        <v>5.76540088653564</v>
+        <v>5.76540040969849</v>
       </c>
       <c r="H336" t="n">
         <v>529259</v>
@@ -10229,7 +10229,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G340" t="n">
-        <v>5.83838033676147</v>
+        <v>5.83837985992432</v>
       </c>
       <c r="H340" t="n">
         <v>369474</v>
@@ -10345,7 +10345,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G344" t="n">
-        <v>5.82621717453003</v>
+        <v>5.82621622085571</v>
       </c>
       <c r="H344" t="n">
         <v>966029</v>
@@ -10461,7 +10461,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G348" t="n">
-        <v>5.86676120758057</v>
+        <v>5.86676168441772</v>
       </c>
       <c r="H348" t="n">
         <v>679592</v>
@@ -10490,7 +10490,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G349" t="n">
-        <v>5.9600133895874</v>
+        <v>5.96001291275024</v>
       </c>
       <c r="H349" t="n">
         <v>644982</v>
@@ -10548,7 +10548,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>6.06542873382568</v>
+        <v>6.06542825698853</v>
       </c>
       <c r="H351" t="n">
         <v>646782</v>
@@ -10577,7 +10577,7 @@
         <v>7.4850001335144</v>
       </c>
       <c r="G352" t="n">
-        <v>6.06948280334473</v>
+        <v>6.06948328018188</v>
       </c>
       <c r="H352" t="n">
         <v>250837</v>
@@ -10606,7 +10606,7 @@
         <v>7.5</v>
       </c>
       <c r="G353" t="n">
-        <v>6.08164596557617</v>
+        <v>6.08164644241333</v>
       </c>
       <c r="H353" t="n">
         <v>469064</v>
@@ -10664,7 +10664,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G355" t="n">
-        <v>6.07353687286377</v>
+        <v>6.07353639602661</v>
       </c>
       <c r="H355" t="n">
         <v>431516</v>
@@ -10693,7 +10693,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G356" t="n">
-        <v>6.01272106170654</v>
+        <v>6.01272058486938</v>
       </c>
       <c r="H356" t="n">
         <v>487093</v>
@@ -10722,7 +10722,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G357" t="n">
-        <v>6.05731916427612</v>
+        <v>6.05731964111328</v>
       </c>
       <c r="H357" t="n">
         <v>432038</v>
@@ -10751,7 +10751,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G358" t="n">
-        <v>6.02893877029419</v>
+        <v>6.02893924713135</v>
       </c>
       <c r="H358" t="n">
         <v>275024</v>
@@ -10780,7 +10780,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G359" t="n">
-        <v>6.04110145568848</v>
+        <v>6.04110193252563</v>
       </c>
       <c r="H359" t="n">
         <v>230614</v>
@@ -10809,7 +10809,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G360" t="n">
-        <v>5.87486934661865</v>
+        <v>5.87486982345581</v>
       </c>
       <c r="H360" t="n">
         <v>497470</v>
@@ -10925,7 +10925,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G364" t="n">
-        <v>6.07759094238281</v>
+        <v>6.07759141921997</v>
       </c>
       <c r="H364" t="n">
         <v>541549</v>
@@ -10954,7 +10954,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>6.04921054840088</v>
+        <v>6.04921102523804</v>
       </c>
       <c r="H365" t="n">
         <v>511334</v>
@@ -10983,7 +10983,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G366" t="n">
-        <v>5.951904296875</v>
+        <v>5.95190477371216</v>
       </c>
       <c r="H366" t="n">
         <v>437739</v>
@@ -11012,7 +11012,7 @@
         <v>7.25</v>
       </c>
       <c r="G367" t="n">
-        <v>5.87892484664917</v>
+        <v>5.87892436981201</v>
       </c>
       <c r="H367" t="n">
         <v>581486</v>
@@ -11041,7 +11041,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G368" t="n">
-        <v>6.04110145568848</v>
+        <v>6.04110193252563</v>
       </c>
       <c r="H368" t="n">
         <v>923183</v>
@@ -11157,7 +11157,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G372" t="n">
-        <v>5.76945495605469</v>
+        <v>5.76945447921753</v>
       </c>
       <c r="H372" t="n">
         <v>800931</v>
@@ -11186,7 +11186,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G373" t="n">
-        <v>5.83027124404907</v>
+        <v>5.83027172088623</v>
       </c>
       <c r="H373" t="n">
         <v>366616</v>
@@ -11215,7 +11215,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G374" t="n">
-        <v>5.83838033676147</v>
+        <v>5.83837985992432</v>
       </c>
       <c r="H374" t="n">
         <v>256515</v>
@@ -11244,7 +11244,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G375" t="n">
-        <v>5.76945495605469</v>
+        <v>5.76945447921753</v>
       </c>
       <c r="H375" t="n">
         <v>267941</v>
@@ -11273,7 +11273,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G376" t="n">
-        <v>5.83027124404907</v>
+        <v>5.83027172088623</v>
       </c>
       <c r="H376" t="n">
         <v>313812</v>
@@ -11331,7 +11331,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G378" t="n">
-        <v>5.70053052902222</v>
+        <v>5.70053005218506</v>
       </c>
       <c r="H378" t="n">
         <v>397166</v>
@@ -11360,7 +11360,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G379" t="n">
-        <v>5.7451286315918</v>
+        <v>5.74512767791748</v>
       </c>
       <c r="H379" t="n">
         <v>226882</v>
@@ -11389,7 +11389,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G380" t="n">
-        <v>5.76945495605469</v>
+        <v>5.76945447921753</v>
       </c>
       <c r="H380" t="n">
         <v>472001</v>
@@ -11418,7 +11418,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G381" t="n">
-        <v>5.89514255523682</v>
+        <v>5.89514207839966</v>
       </c>
       <c r="H381" t="n">
         <v>1010035</v>
@@ -11447,7 +11447,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G382" t="n">
-        <v>5.9600133895874</v>
+        <v>5.96001291275024</v>
       </c>
       <c r="H382" t="n">
         <v>466603</v>
@@ -11476,7 +11476,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G383" t="n">
-        <v>6.11813640594482</v>
+        <v>6.11813592910767</v>
       </c>
       <c r="H383" t="n">
         <v>720113</v>
@@ -11563,7 +11563,7 @@
         <v>8.34500026702881</v>
       </c>
       <c r="G386" t="n">
-        <v>6.76684474945068</v>
+        <v>6.76684522628784</v>
       </c>
       <c r="H386" t="n">
         <v>1413459</v>
@@ -11679,7 +11679,7 @@
         <v>8.26500034332275</v>
       </c>
       <c r="G390" t="n">
-        <v>6.7019739151001</v>
+        <v>6.70197486877441</v>
       </c>
       <c r="H390" t="n">
         <v>536029</v>
@@ -11708,7 +11708,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G391" t="n">
-        <v>6.63304805755615</v>
+        <v>6.63304853439331</v>
       </c>
       <c r="H391" t="n">
         <v>586518</v>
@@ -11766,7 +11766,7 @@
         <v>8</v>
       </c>
       <c r="G393" t="n">
-        <v>6.48708915710449</v>
+        <v>6.48708868026733</v>
       </c>
       <c r="H393" t="n">
         <v>885457</v>
@@ -11853,7 +11853,7 @@
         <v>7.80499982833862</v>
       </c>
       <c r="G396" t="n">
-        <v>6.32896661758423</v>
+        <v>6.32896614074707</v>
       </c>
       <c r="H396" t="n">
         <v>929166</v>
@@ -11911,7 +11911,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G398" t="n">
-        <v>6.41005516052246</v>
+        <v>6.41005563735962</v>
       </c>
       <c r="H398" t="n">
         <v>209985</v>
@@ -11940,7 +11940,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G399" t="n">
-        <v>6.34113025665283</v>
+        <v>6.34112977981567</v>
       </c>
       <c r="H399" t="n">
         <v>267762</v>
@@ -11969,7 +11969,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>6.4546537399292</v>
+        <v>6.45465421676636</v>
       </c>
       <c r="H400" t="n">
         <v>247941</v>
@@ -11998,7 +11998,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G401" t="n">
-        <v>6.53574228286743</v>
+        <v>6.53574275970459</v>
       </c>
       <c r="H401" t="n">
         <v>597937</v>
@@ -12085,7 +12085,7 @@
         <v>8.01000022888184</v>
       </c>
       <c r="G404" t="n">
-        <v>6.49519824981689</v>
+        <v>6.49519777297974</v>
       </c>
       <c r="H404" t="n">
         <v>375799</v>
@@ -12114,7 +12114,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G405" t="n">
-        <v>6.41410875320435</v>
+        <v>6.4141092300415</v>
       </c>
       <c r="H405" t="n">
         <v>435321</v>
@@ -12172,7 +12172,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G407" t="n">
-        <v>6.33302068710327</v>
+        <v>6.33302116394043</v>
       </c>
       <c r="H407" t="n">
         <v>442303</v>
@@ -12201,7 +12201,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G408" t="n">
-        <v>6.53979635238647</v>
+        <v>6.53979587554932</v>
       </c>
       <c r="H408" t="n">
         <v>746360</v>
@@ -12230,7 +12230,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G409" t="n">
-        <v>6.43843603134155</v>
+        <v>6.43843650817871</v>
       </c>
       <c r="H409" t="n">
         <v>476518</v>
@@ -12259,7 +12259,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G410" t="n">
-        <v>6.50736045837402</v>
+        <v>6.50736141204834</v>
       </c>
       <c r="H410" t="n">
         <v>412497</v>
@@ -12288,7 +12288,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G411" t="n">
-        <v>6.41410875320435</v>
+        <v>6.4141092300415</v>
       </c>
       <c r="H411" t="n">
         <v>315312</v>
@@ -12375,7 +12375,7 @@
         <v>8</v>
       </c>
       <c r="G414" t="n">
-        <v>6.48708915710449</v>
+        <v>6.48708868026733</v>
       </c>
       <c r="H414" t="n">
         <v>149108</v>
@@ -12404,7 +12404,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G415" t="n">
-        <v>6.4546537399292</v>
+        <v>6.45465421676636</v>
       </c>
       <c r="H415" t="n">
         <v>243119</v>
@@ -12433,7 +12433,7 @@
         <v>7.93499994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>6.43438148498535</v>
+        <v>6.43438196182251</v>
       </c>
       <c r="H416" t="n">
         <v>138919</v>
@@ -12462,7 +12462,7 @@
         <v>8</v>
       </c>
       <c r="G417" t="n">
-        <v>6.48708915710449</v>
+        <v>6.48708868026733</v>
       </c>
       <c r="H417" t="n">
         <v>230322</v>
@@ -12491,7 +12491,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>6.49114322662354</v>
+        <v>6.49114418029785</v>
       </c>
       <c r="H418" t="n">
         <v>241697</v>
@@ -12520,7 +12520,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G419" t="n">
-        <v>6.6087212562561</v>
+        <v>6.60872173309326</v>
       </c>
       <c r="H419" t="n">
         <v>465583</v>
@@ -12549,7 +12549,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G420" t="n">
-        <v>6.72630071640015</v>
+        <v>6.72630023956299</v>
       </c>
       <c r="H420" t="n">
         <v>281728</v>
@@ -12578,7 +12578,7 @@
         <v>8.1850004196167</v>
       </c>
       <c r="G421" t="n">
-        <v>6.63710355758667</v>
+        <v>6.63710308074951</v>
       </c>
       <c r="H421" t="n">
         <v>362425</v>
@@ -12665,7 +12665,7 @@
         <v>8.125</v>
       </c>
       <c r="G424" t="n">
-        <v>6.58844947814941</v>
+        <v>6.58844995498657</v>
       </c>
       <c r="H424" t="n">
         <v>241186</v>
@@ -12694,7 +12694,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G425" t="n">
-        <v>6.56817770004272</v>
+        <v>6.56817817687988</v>
       </c>
       <c r="H425" t="n">
         <v>155084</v>
@@ -12723,7 +12723,7 @@
         <v>8.1850004196167</v>
       </c>
       <c r="G426" t="n">
-        <v>6.63710355758667</v>
+        <v>6.63710308074951</v>
       </c>
       <c r="H426" t="n">
         <v>190102</v>
@@ -12781,7 +12781,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G428" t="n">
-        <v>6.4546537399292</v>
+        <v>6.45465421676636</v>
       </c>
       <c r="H428" t="n">
         <v>377682</v>
@@ -12810,7 +12810,7 @@
         <v>8.0649995803833</v>
       </c>
       <c r="G429" t="n">
-        <v>6.53979635238647</v>
+        <v>6.53979587554932</v>
       </c>
       <c r="H429" t="n">
         <v>220024</v>
@@ -12897,7 +12897,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G432" t="n">
-        <v>7.30203008651733</v>
+        <v>7.30202960968018</v>
       </c>
       <c r="H432" t="n">
         <v>1288124</v>
@@ -12926,7 +12926,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G433" t="n">
-        <v>7.31419324874878</v>
+        <v>7.3141942024231</v>
       </c>
       <c r="H433" t="n">
         <v>1097765</v>
@@ -12955,7 +12955,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G434" t="n">
-        <v>7.34257555007935</v>
+        <v>7.34257364273071</v>
       </c>
       <c r="H434" t="n">
         <v>367444</v>
@@ -12984,7 +12984,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G435" t="n">
-        <v>7.31419324874878</v>
+        <v>7.3141942024231</v>
       </c>
       <c r="H435" t="n">
         <v>278409</v>
@@ -13042,7 +13042,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>7.33041048049927</v>
+        <v>7.33041000366211</v>
       </c>
       <c r="H437" t="n">
         <v>214202</v>
@@ -13100,7 +13100,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G439" t="n">
-        <v>7.81288814544678</v>
+        <v>7.81288909912109</v>
       </c>
       <c r="H439" t="n">
         <v>1138662</v>
@@ -13129,7 +13129,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G440" t="n">
-        <v>7.62233066558838</v>
+        <v>7.62232971191406</v>
       </c>
       <c r="H440" t="n">
         <v>863579</v>
@@ -13158,7 +13158,7 @@
         <v>9.5</v>
       </c>
       <c r="G441" t="n">
-        <v>7.70341873168945</v>
+        <v>7.70341777801514</v>
       </c>
       <c r="H441" t="n">
         <v>516361</v>
@@ -13187,7 +13187,7 @@
         <v>9.5</v>
       </c>
       <c r="G442" t="n">
-        <v>7.70341873168945</v>
+        <v>7.70341777801514</v>
       </c>
       <c r="H442" t="n">
         <v>359016</v>
@@ -13216,7 +13216,7 @@
         <v>9.45499992370605</v>
       </c>
       <c r="G443" t="n">
-        <v>7.66692781448364</v>
+        <v>7.6669282913208</v>
       </c>
       <c r="H443" t="n">
         <v>173608</v>
@@ -13274,7 +13274,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G445" t="n">
-        <v>7.61827564239502</v>
+        <v>7.61827421188354</v>
       </c>
       <c r="H445" t="n">
         <v>363186</v>
@@ -13332,7 +13332,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G447" t="n">
-        <v>7.78450632095337</v>
+        <v>7.784508228302</v>
       </c>
       <c r="H447" t="n">
         <v>274208</v>
@@ -13390,7 +13390,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G449" t="n">
-        <v>7.152015209198</v>
+        <v>7.15201616287231</v>
       </c>
       <c r="H449" t="n">
         <v>1155537</v>
@@ -13419,7 +13419,7 @@
         <v>8.97500038146973</v>
       </c>
       <c r="G450" t="n">
-        <v>7.27770471572876</v>
+        <v>7.27770328521729</v>
       </c>
       <c r="H450" t="n">
         <v>393229</v>
@@ -13448,7 +13448,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G451" t="n">
-        <v>7.1560697555542</v>
+        <v>7.15607023239136</v>
       </c>
       <c r="H451" t="n">
         <v>329087</v>
@@ -13477,7 +13477,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G452" t="n">
-        <v>7.00605630874634</v>
+        <v>7.0060567855835</v>
       </c>
       <c r="H452" t="n">
         <v>1550877</v>
@@ -13506,7 +13506,7 @@
         <v>8.75</v>
       </c>
       <c r="G453" t="n">
-        <v>7.0952525138855</v>
+        <v>7.09525442123413</v>
       </c>
       <c r="H453" t="n">
         <v>1028130</v>
@@ -13535,7 +13535,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G454" t="n">
-        <v>7.28175830841064</v>
+        <v>7.28175783157349</v>
       </c>
       <c r="H454" t="n">
         <v>969717</v>
@@ -13564,7 +13564,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>7.33446502685547</v>
+        <v>7.33446598052979</v>
       </c>
       <c r="H455" t="n">
         <v>983307</v>
@@ -13622,7 +13622,7 @@
         <v>8.83500003814697</v>
       </c>
       <c r="G457" t="n">
-        <v>7.16417932510376</v>
+        <v>7.1641788482666</v>
       </c>
       <c r="H457" t="n">
         <v>893167</v>
@@ -13680,7 +13680,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G459" t="n">
-        <v>7.11958026885986</v>
+        <v>7.11958074569702</v>
       </c>
       <c r="H459" t="n">
         <v>410163</v>
@@ -13709,7 +13709,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G460" t="n">
-        <v>7.152015209198</v>
+        <v>7.15201616287231</v>
       </c>
       <c r="H460" t="n">
         <v>340226</v>
@@ -13738,7 +13738,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G461" t="n">
-        <v>7.24932241439819</v>
+        <v>7.24932193756104</v>
       </c>
       <c r="H461" t="n">
         <v>284318</v>
@@ -13767,7 +13767,7 @@
         <v>8.89000034332275</v>
       </c>
       <c r="G462" t="n">
-        <v>7.20877885818481</v>
+        <v>7.20877742767334</v>
       </c>
       <c r="H462" t="n">
         <v>252718</v>
@@ -13796,7 +13796,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G463" t="n">
-        <v>7.07092761993408</v>
+        <v>7.07092714309692</v>
       </c>
       <c r="H463" t="n">
         <v>402947</v>
@@ -13825,7 +13825,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G464" t="n">
-        <v>7.11958026885986</v>
+        <v>7.11958074569702</v>
       </c>
       <c r="H464" t="n">
         <v>296622</v>
@@ -13854,7 +13854,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G465" t="n">
-        <v>6.90469646453857</v>
+        <v>6.90469598770142</v>
       </c>
       <c r="H465" t="n">
         <v>313200</v>
@@ -13912,7 +13912,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G467" t="n">
-        <v>6.92902183532715</v>
+        <v>6.92902278900146</v>
       </c>
       <c r="H467" t="n">
         <v>196929</v>
@@ -13941,7 +13941,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G468" t="n">
-        <v>6.83982515335083</v>
+        <v>6.83982419967651</v>
       </c>
       <c r="H468" t="n">
         <v>395966</v>
@@ -13970,7 +13970,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G469" t="n">
-        <v>6.67359256744385</v>
+        <v>6.67359352111816</v>
       </c>
       <c r="H469" t="n">
         <v>740308</v>
@@ -13999,7 +13999,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G470" t="n">
-        <v>6.62899494171143</v>
+        <v>6.62899446487427</v>
       </c>
       <c r="H470" t="n">
         <v>416714</v>
@@ -14057,7 +14057,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G472" t="n">
-        <v>6.56412363052368</v>
+        <v>6.56412315368652</v>
       </c>
       <c r="H472" t="n">
         <v>487271</v>
@@ -14115,7 +14115,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G474" t="n">
-        <v>6.6695384979248</v>
+        <v>6.66953897476196</v>
       </c>
       <c r="H474" t="n">
         <v>272288</v>
@@ -14144,7 +14144,7 @@
         <v>8.78499984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>7.12363433837891</v>
+        <v>7.12363386154175</v>
       </c>
       <c r="H475" t="n">
         <v>744606</v>
@@ -14173,7 +14173,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G476" t="n">
-        <v>7.06281709671021</v>
+        <v>7.06281805038452</v>
       </c>
       <c r="H476" t="n">
         <v>414113</v>
@@ -14202,7 +14202,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G477" t="n">
-        <v>6.95334768295288</v>
+        <v>6.9533486366272</v>
       </c>
       <c r="H477" t="n">
         <v>307389</v>
@@ -14231,7 +14231,7 @@
         <v>8.54500007629395</v>
       </c>
       <c r="G478" t="n">
-        <v>6.92902183532715</v>
+        <v>6.92902278900146</v>
       </c>
       <c r="H478" t="n">
         <v>313057</v>
@@ -14376,7 +14376,7 @@
         <v>9</v>
       </c>
       <c r="G483" t="n">
-        <v>7.29797649383545</v>
+        <v>7.29797601699829</v>
       </c>
       <c r="H483" t="n">
         <v>887374</v>
@@ -14405,7 +14405,7 @@
         <v>9</v>
       </c>
       <c r="G484" t="n">
-        <v>7.29797649383545</v>
+        <v>7.29797601699829</v>
       </c>
       <c r="H484" t="n">
         <v>470514</v>
@@ -14434,7 +14434,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G485" t="n">
-        <v>7.17634248733521</v>
+        <v>7.17634296417236</v>
       </c>
       <c r="H485" t="n">
         <v>329070</v>
@@ -14463,7 +14463,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>7.13174295425415</v>
+        <v>7.13174390792847</v>
       </c>
       <c r="H486" t="n">
         <v>658309</v>
@@ -14492,7 +14492,7 @@
         <v>8.78999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>7.12768793106079</v>
+        <v>7.12768983840942</v>
       </c>
       <c r="H487" t="n">
         <v>333175</v>
@@ -14521,7 +14521,7 @@
         <v>8.91499996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>7.22905015945435</v>
+        <v>7.22904968261719</v>
       </c>
       <c r="H488" t="n">
         <v>522260</v>
@@ -14550,7 +14550,7 @@
         <v>8.8149995803833</v>
       </c>
       <c r="G489" t="n">
-        <v>7.14796018600464</v>
+        <v>7.1479606628418</v>
       </c>
       <c r="H489" t="n">
         <v>1048680</v>
@@ -14579,7 +14579,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G490" t="n">
-        <v>7.78450632095337</v>
+        <v>7.784508228302</v>
       </c>
       <c r="H490" t="n">
         <v>1535668</v>
@@ -14608,7 +14608,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G491" t="n">
-        <v>8.08453464508057</v>
+        <v>8.08453559875488</v>
       </c>
       <c r="H491" t="n">
         <v>1410719</v>
@@ -14637,7 +14637,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G492" t="n">
-        <v>7.97911977767944</v>
+        <v>7.97912073135376</v>
       </c>
       <c r="H492" t="n">
         <v>935236</v>
@@ -14666,7 +14666,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G493" t="n">
-        <v>8.25482082366943</v>
+        <v>8.25482177734375</v>
       </c>
       <c r="H493" t="n">
         <v>972051</v>
@@ -14724,7 +14724,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G495" t="n">
-        <v>8.26292991638184</v>
+        <v>8.26293087005615</v>
       </c>
       <c r="H495" t="n">
         <v>733524</v>
@@ -14753,7 +14753,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G496" t="n">
-        <v>7.99533700942993</v>
+        <v>7.99533796310425</v>
       </c>
       <c r="H496" t="n">
         <v>807259</v>
@@ -14782,7 +14782,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G497" t="n">
-        <v>8.10075283050537</v>
+        <v>8.10075378417969</v>
       </c>
       <c r="H497" t="n">
         <v>514515</v>
@@ -14840,7 +14840,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>7.94668388366699</v>
+        <v>7.94668483734131</v>
       </c>
       <c r="H499" t="n">
         <v>421496</v>
@@ -14869,7 +14869,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G500" t="n">
-        <v>8.05209827423096</v>
+        <v>8.05210018157959</v>
       </c>
       <c r="H500" t="n">
         <v>406796</v>
@@ -14898,7 +14898,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>8.03588104248047</v>
+        <v>8.03588199615479</v>
       </c>
       <c r="H501" t="n">
         <v>278465</v>
@@ -14985,7 +14985,7 @@
         <v>9.875</v>
       </c>
       <c r="G504" t="n">
-        <v>8.00750160217285</v>
+        <v>8.00750064849854</v>
       </c>
       <c r="H504" t="n">
         <v>329977</v>
@@ -15014,7 +15014,7 @@
         <v>9.9350004196167</v>
       </c>
       <c r="G505" t="n">
-        <v>8.05615329742432</v>
+        <v>8.05615425109863</v>
       </c>
       <c r="H505" t="n">
         <v>204740</v>
@@ -15043,7 +15043,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G506" t="n">
-        <v>8.3034725189209</v>
+        <v>8.30347347259521</v>
       </c>
       <c r="H506" t="n">
         <v>471266</v>
@@ -15101,7 +15101,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G508" t="n">
-        <v>8.21427631378174</v>
+        <v>8.21427726745605</v>
       </c>
       <c r="H508" t="n">
         <v>411815</v>
@@ -15130,7 +15130,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G509" t="n">
-        <v>8.25482082366943</v>
+        <v>8.25482177734375</v>
       </c>
       <c r="H509" t="n">
         <v>242244</v>
@@ -15188,7 +15188,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G511" t="n">
-        <v>8.32780170440674</v>
+        <v>8.32780075073242</v>
       </c>
       <c r="H511" t="n">
         <v>305325</v>
@@ -15217,7 +15217,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G512" t="n">
-        <v>8.3683443069458</v>
+        <v>8.36834526062012</v>
       </c>
       <c r="H512" t="n">
         <v>380092</v>
@@ -15304,7 +15304,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G515" t="n">
-        <v>8.55484867095947</v>
+        <v>8.55484962463379</v>
       </c>
       <c r="H515" t="n">
         <v>1324355</v>
@@ -15333,7 +15333,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G516" t="n">
-        <v>8.66837310791016</v>
+        <v>8.66837215423584</v>
       </c>
       <c r="H516" t="n">
         <v>772796</v>
@@ -15391,7 +15391,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G518" t="n">
-        <v>8.67648220062256</v>
+        <v>8.67648124694824</v>
       </c>
       <c r="H518" t="n">
         <v>989608</v>
@@ -15420,7 +15420,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G519" t="n">
-        <v>8.70891571044922</v>
+        <v>8.70891761779785</v>
       </c>
       <c r="H519" t="n">
         <v>680336</v>
@@ -15449,7 +15449,7 @@
         <v>10.5</v>
       </c>
       <c r="G520" t="n">
-        <v>8.51430511474609</v>
+        <v>8.51430416107178</v>
       </c>
       <c r="H520" t="n">
         <v>646195</v>
@@ -15478,7 +15478,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G521" t="n">
-        <v>8.49808788299561</v>
+        <v>8.49808597564697</v>
       </c>
       <c r="H521" t="n">
         <v>669753</v>
@@ -15507,7 +15507,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G522" t="n">
-        <v>8.5224142074585</v>
+        <v>8.52241325378418</v>
       </c>
       <c r="H522" t="n">
         <v>415123</v>
@@ -15536,7 +15536,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G523" t="n">
-        <v>8.27914810180664</v>
+        <v>8.27914714813232</v>
       </c>
       <c r="H523" t="n">
         <v>535858</v>
@@ -15623,7 +15623,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G526" t="n">
-        <v>8.54912090301514</v>
+        <v>8.5491189956665</v>
       </c>
       <c r="H526" t="n">
         <v>390798</v>
@@ -15652,7 +15652,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G527" t="n">
-        <v>8.61456680297852</v>
+        <v>8.61456775665283</v>
       </c>
       <c r="H527" t="n">
         <v>365341</v>
@@ -15681,7 +15681,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G528" t="n">
-        <v>8.59820652008057</v>
+        <v>8.59820556640625</v>
       </c>
       <c r="H528" t="n">
         <v>590184</v>
@@ -15739,7 +15739,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G530" t="n">
-        <v>8.09916496276855</v>
+        <v>8.09916591644287</v>
       </c>
       <c r="H530" t="n">
         <v>1517592</v>
@@ -15884,7 +15884,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G535" t="n">
-        <v>8.68819618225098</v>
+        <v>8.68819522857666</v>
       </c>
       <c r="H535" t="n">
         <v>441933</v>
@@ -15942,7 +15942,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G537" t="n">
-        <v>8.61456680297852</v>
+        <v>8.61456775665283</v>
       </c>
       <c r="H537" t="n">
         <v>246871</v>
@@ -15971,7 +15971,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G538" t="n">
-        <v>8.42640495300293</v>
+        <v>8.42640590667725</v>
       </c>
       <c r="H538" t="n">
         <v>500661</v>
@@ -16000,7 +16000,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G539" t="n">
-        <v>8.68819618225098</v>
+        <v>8.68819522857666</v>
       </c>
       <c r="H539" t="n">
         <v>202860</v>
@@ -16029,7 +16029,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>8.67183399200439</v>
+        <v>8.67183494567871</v>
       </c>
       <c r="H540" t="n">
         <v>303113</v>
@@ -16058,7 +16058,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G541" t="n">
-        <v>8.65547180175781</v>
+        <v>8.65547275543213</v>
       </c>
       <c r="H541" t="n">
         <v>231641</v>
@@ -16087,7 +16087,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G542" t="n">
-        <v>8.66365432739258</v>
+        <v>8.66365242004395</v>
       </c>
       <c r="H542" t="n">
         <v>326289</v>
@@ -16145,7 +16145,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G544" t="n">
-        <v>8.57366275787354</v>
+        <v>8.5736608505249</v>
       </c>
       <c r="H544" t="n">
         <v>254235</v>
@@ -16203,7 +16203,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>8.42640495300293</v>
+        <v>8.42640590667725</v>
       </c>
       <c r="H546" t="n">
         <v>635624</v>
@@ -16232,7 +16232,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G547" t="n">
-        <v>8.46730899810791</v>
+        <v>8.46731090545654</v>
       </c>
       <c r="H547" t="n">
         <v>278379</v>
@@ -16261,7 +16261,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G548" t="n">
-        <v>8.46730899810791</v>
+        <v>8.46731090545654</v>
       </c>
       <c r="H548" t="n">
         <v>229312</v>
@@ -16319,7 +16319,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G550" t="n">
-        <v>8.57366275787354</v>
+        <v>8.5736608505249</v>
       </c>
       <c r="H550" t="n">
         <v>349321</v>
@@ -16348,7 +16348,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G551" t="n">
-        <v>8.32005214691162</v>
+        <v>8.32005310058594</v>
       </c>
       <c r="H551" t="n">
         <v>417587</v>
@@ -16406,7 +16406,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G553" t="n">
-        <v>8.30368900299072</v>
+        <v>8.30368995666504</v>
       </c>
       <c r="H553" t="n">
         <v>294109</v>
@@ -16435,7 +16435,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G554" t="n">
-        <v>8.107346534729</v>
+        <v>8.10734748840332</v>
       </c>
       <c r="H554" t="n">
         <v>332792</v>
@@ -16464,7 +16464,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G555" t="n">
-        <v>8.43458652496338</v>
+        <v>8.43458557128906</v>
       </c>
       <c r="H555" t="n">
         <v>469765</v>
@@ -16493,7 +16493,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G556" t="n">
-        <v>8.107346534729</v>
+        <v>8.10734748840332</v>
       </c>
       <c r="H556" t="n">
         <v>372171</v>
@@ -16580,7 +16580,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G559" t="n">
-        <v>8.21369934082031</v>
+        <v>8.213698387146</v>
       </c>
       <c r="H559" t="n">
         <v>169386</v>
@@ -16609,7 +16609,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G560" t="n">
-        <v>8.27096557617188</v>
+        <v>8.27096652984619</v>
       </c>
       <c r="H560" t="n">
         <v>197274</v>
@@ -16638,7 +16638,7 @@
         <v>9.86499977111816</v>
       </c>
       <c r="G561" t="n">
-        <v>8.07053279876709</v>
+        <v>8.07053184509277</v>
       </c>
       <c r="H561" t="n">
         <v>347176</v>
@@ -16696,7 +16696,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G563" t="n">
-        <v>8.32005214691162</v>
+        <v>8.32005310058594</v>
       </c>
       <c r="H563" t="n">
         <v>584764</v>
@@ -16754,7 +16754,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G565" t="n">
-        <v>8.54912090301514</v>
+        <v>8.5491189956665</v>
       </c>
       <c r="H565" t="n">
         <v>289915</v>
@@ -16812,7 +16812,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G567" t="n">
-        <v>8.42640495300293</v>
+        <v>8.42640590667725</v>
       </c>
       <c r="H567" t="n">
         <v>158617</v>
@@ -16870,7 +16870,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G569" t="n">
-        <v>8.01735591888428</v>
+        <v>8.01735687255859</v>
       </c>
       <c r="H569" t="n">
         <v>470176</v>
@@ -16928,7 +16928,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G571" t="n">
-        <v>7.85373592376709</v>
+        <v>7.85373783111572</v>
       </c>
       <c r="H571" t="n">
         <v>774936</v>
@@ -16957,7 +16957,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G572" t="n">
-        <v>7.78010749816895</v>
+        <v>7.7801079750061</v>
       </c>
       <c r="H572" t="n">
         <v>613933</v>
@@ -16986,7 +16986,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G573" t="n">
-        <v>7.64921236038208</v>
+        <v>7.64921283721924</v>
       </c>
       <c r="H573" t="n">
         <v>834015</v>
@@ -17015,7 +17015,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G574" t="n">
-        <v>7.88236999511719</v>
+        <v>7.8823709487915</v>
       </c>
       <c r="H574" t="n">
         <v>419935</v>
@@ -17044,7 +17044,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G575" t="n">
-        <v>7.62876033782959</v>
+        <v>7.62875986099243</v>
       </c>
       <c r="H575" t="n">
         <v>393848</v>
@@ -17073,7 +17073,7 @@
         <v>9.42500019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>7.71056985855103</v>
+        <v>7.71056938171387</v>
       </c>
       <c r="H576" t="n">
         <v>361574</v>
@@ -17102,7 +17102,7 @@
         <v>9.14000034332275</v>
       </c>
       <c r="G577" t="n">
-        <v>7.47741174697876</v>
+        <v>7.47741270065308</v>
       </c>
       <c r="H577" t="n">
         <v>345202</v>
@@ -17131,7 +17131,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G578" t="n">
-        <v>7.72284173965454</v>
+        <v>7.72284078598022</v>
       </c>
       <c r="H578" t="n">
         <v>756759</v>
@@ -17160,7 +17160,7 @@
         <v>9.29500007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>7.60421657562256</v>
+        <v>7.60421705245972</v>
       </c>
       <c r="H579" t="n">
         <v>257789</v>
@@ -17189,7 +17189,7 @@
         <v>9.21000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>7.53467893600464</v>
+        <v>7.53467988967896</v>
       </c>
       <c r="H580" t="n">
         <v>352772</v>
@@ -17247,7 +17247,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G582" t="n">
-        <v>7.73102188110352</v>
+        <v>7.73102235794067</v>
       </c>
       <c r="H582" t="n">
         <v>519793</v>
@@ -17276,7 +17276,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G583" t="n">
-        <v>7.58376550674438</v>
+        <v>7.58376455307007</v>
       </c>
       <c r="H583" t="n">
         <v>449459</v>
@@ -17305,7 +17305,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G584" t="n">
-        <v>7.45696020126343</v>
+        <v>7.45695924758911</v>
       </c>
       <c r="H584" t="n">
         <v>216927</v>
@@ -17334,7 +17334,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G585" t="n">
-        <v>7.43650770187378</v>
+        <v>7.43650674819946</v>
       </c>
       <c r="H585" t="n">
         <v>290925</v>
@@ -17363,7 +17363,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G586" t="n">
-        <v>7.69011783599854</v>
+        <v>7.69011735916138</v>
       </c>
       <c r="H586" t="n">
         <v>792177</v>
@@ -17392,7 +17392,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G587" t="n">
-        <v>7.41196489334106</v>
+        <v>7.41196441650391</v>
       </c>
       <c r="H587" t="n">
         <v>472024</v>
@@ -17421,7 +17421,7 @@
         <v>9.16499996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>7.49786424636841</v>
+        <v>7.49786376953125</v>
       </c>
       <c r="H588" t="n">
         <v>177149</v>
@@ -17450,7 +17450,7 @@
         <v>9.41499996185303</v>
       </c>
       <c r="G589" t="n">
-        <v>7.70238828659058</v>
+        <v>7.70238780975342</v>
       </c>
       <c r="H589" t="n">
         <v>490660</v>
@@ -17479,7 +17479,7 @@
         <v>9.35499954223633</v>
       </c>
       <c r="G590" t="n">
-        <v>7.6533031463623</v>
+        <v>7.65330219268799</v>
       </c>
       <c r="H590" t="n">
         <v>214347</v>
@@ -17508,7 +17508,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G591" t="n">
-        <v>7.48150300979614</v>
+        <v>7.48150205612183</v>
       </c>
       <c r="H591" t="n">
         <v>306385</v>
@@ -17537,7 +17537,7 @@
         <v>9.26000022888184</v>
       </c>
       <c r="G592" t="n">
-        <v>7.57558393478394</v>
+        <v>7.57558345794678</v>
       </c>
       <c r="H592" t="n">
         <v>385472</v>
@@ -17566,7 +17566,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>7.60830736160278</v>
+        <v>7.60830783843994</v>
       </c>
       <c r="H593" t="n">
         <v>212290</v>
@@ -17624,7 +17624,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G595" t="n">
-        <v>7.31379270553589</v>
+        <v>7.31379175186157</v>
       </c>
       <c r="H595" t="n">
         <v>1987864</v>
@@ -17653,7 +17653,7 @@
         <v>8.75</v>
       </c>
       <c r="G596" t="n">
-        <v>7.15835285186768</v>
+        <v>7.15835428237915</v>
       </c>
       <c r="H596" t="n">
         <v>706536</v>
@@ -17682,7 +17682,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G597" t="n">
-        <v>7.01927614212036</v>
+        <v>7.01927709579468</v>
       </c>
       <c r="H597" t="n">
         <v>566591</v>
@@ -17711,7 +17711,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G598" t="n">
-        <v>7.0642728805542</v>
+        <v>7.06427145004272</v>
       </c>
       <c r="H598" t="n">
         <v>782685</v>
@@ -17769,7 +17769,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G600" t="n">
-        <v>7.52649784088135</v>
+        <v>7.52649831771851</v>
       </c>
       <c r="H600" t="n">
         <v>916870</v>
@@ -17827,7 +17827,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G602" t="n">
-        <v>8.02553653717041</v>
+        <v>8.02553844451904</v>
       </c>
       <c r="H602" t="n">
         <v>599158</v>
@@ -17914,7 +17914,7 @@
         <v>10</v>
       </c>
       <c r="G605" t="n">
-        <v>8.18097591400146</v>
+        <v>8.18097686767578</v>
       </c>
       <c r="H605" t="n">
         <v>446845</v>
@@ -17943,7 +17943,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G606" t="n">
-        <v>8.05826091766357</v>
+        <v>8.05826187133789</v>
       </c>
       <c r="H606" t="n">
         <v>285819</v>
@@ -17972,7 +17972,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G607" t="n">
-        <v>8.08689498901367</v>
+        <v>8.08689594268799</v>
       </c>
       <c r="H607" t="n">
         <v>199571</v>
@@ -18030,7 +18030,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G609" t="n">
-        <v>8.37731838226318</v>
+        <v>8.3773193359375</v>
       </c>
       <c r="H609" t="n">
         <v>298043</v>
@@ -18088,7 +18088,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G611" t="n">
-        <v>8.43458652496338</v>
+        <v>8.43458557128906</v>
       </c>
       <c r="H611" t="n">
         <v>946908</v>
@@ -18117,7 +18117,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G612" t="n">
-        <v>8.89272022247314</v>
+        <v>8.89271926879883</v>
       </c>
       <c r="H612" t="n">
         <v>1821355</v>
@@ -18378,7 +18378,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G621" t="n">
-        <v>8.86817932128906</v>
+        <v>8.86817836761475</v>
       </c>
       <c r="H621" t="n">
         <v>361423</v>
@@ -18407,7 +18407,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G622" t="n">
-        <v>8.50821399688721</v>
+        <v>8.50821495056152</v>
       </c>
       <c r="H622" t="n">
         <v>615526</v>
@@ -18436,7 +18436,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G623" t="n">
-        <v>8.54912090301514</v>
+        <v>8.5491189956665</v>
       </c>
       <c r="H623" t="n">
         <v>483533</v>
@@ -18465,7 +18465,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G624" t="n">
-        <v>8.4182243347168</v>
+        <v>8.41822338104248</v>
       </c>
       <c r="H624" t="n">
         <v>689398</v>
@@ -18552,7 +18552,7 @@
         <v>9.78499984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>8.00508594512939</v>
+        <v>8.00508499145508</v>
       </c>
       <c r="H627" t="n">
         <v>398562</v>
@@ -18610,7 +18610,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G629" t="n">
-        <v>8.20551681518555</v>
+        <v>8.20551776885986</v>
       </c>
       <c r="H629" t="n">
         <v>514012</v>
@@ -18697,7 +18697,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G632" t="n">
-        <v>7.88236999511719</v>
+        <v>7.8823709487915</v>
       </c>
       <c r="H632" t="n">
         <v>327645</v>
@@ -18726,7 +18726,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G633" t="n">
-        <v>7.84146451950073</v>
+        <v>7.84146499633789</v>
       </c>
       <c r="H633" t="n">
         <v>144617</v>
@@ -18755,7 +18755,7 @@
         <v>9.29500007629395</v>
       </c>
       <c r="G634" t="n">
-        <v>7.60421657562256</v>
+        <v>7.60421705245972</v>
       </c>
       <c r="H634" t="n">
         <v>344085</v>
@@ -18784,7 +18784,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G635" t="n">
-        <v>7.68602752685547</v>
+        <v>7.68602609634399</v>
       </c>
       <c r="H635" t="n">
         <v>264471</v>
@@ -18813,7 +18813,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G636" t="n">
-        <v>8.02553653717041</v>
+        <v>8.02553844451904</v>
       </c>
       <c r="H636" t="n">
         <v>375015</v>
@@ -18871,7 +18871,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G638" t="n">
-        <v>8.12370777130127</v>
+        <v>8.1237096786499</v>
       </c>
       <c r="H638" t="n">
         <v>371966</v>
@@ -18900,7 +18900,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G639" t="n">
-        <v>7.935546875</v>
+        <v>7.93554592132568</v>
       </c>
       <c r="H639" t="n">
         <v>571794</v>
@@ -18987,7 +18987,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>8.42640495300293</v>
+        <v>8.42640590667725</v>
       </c>
       <c r="H642" t="n">
         <v>506134</v>
@@ -19016,7 +19016,7 @@
         <v>10.25</v>
       </c>
       <c r="G643" t="n">
-        <v>8.38549995422363</v>
+        <v>8.38550090789795</v>
       </c>
       <c r="H643" t="n">
         <v>356537</v>
@@ -19074,7 +19074,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G645" t="n">
-        <v>8.45094680786133</v>
+        <v>8.45094871520996</v>
       </c>
       <c r="H645" t="n">
         <v>224852</v>
@@ -19103,7 +19103,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G646" t="n">
-        <v>8.45094680786133</v>
+        <v>8.45094871520996</v>
       </c>
       <c r="H646" t="n">
         <v>226420</v>
@@ -19132,7 +19132,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G647" t="n">
-        <v>8.21369934082031</v>
+        <v>8.213698387146</v>
       </c>
       <c r="H647" t="n">
         <v>289761</v>
@@ -19161,7 +19161,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G648" t="n">
-        <v>7.85373592376709</v>
+        <v>7.85373783111572</v>
       </c>
       <c r="H648" t="n">
         <v>673543</v>
@@ -19190,7 +19190,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G649" t="n">
-        <v>8.05826091766357</v>
+        <v>8.05826187133789</v>
       </c>
       <c r="H649" t="n">
         <v>621948</v>
@@ -19248,7 +19248,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G651" t="n">
-        <v>7.68602752685547</v>
+        <v>7.68602609634399</v>
       </c>
       <c r="H651" t="n">
         <v>590227</v>
@@ -19277,7 +19277,7 @@
         <v>9.69499969482422</v>
       </c>
       <c r="G652" t="n">
-        <v>7.93145561218262</v>
+        <v>7.9314546585083</v>
       </c>
       <c r="H652" t="n">
         <v>532182</v>
@@ -19306,7 +19306,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G653" t="n">
-        <v>7.8619179725647</v>
+        <v>7.86191701889038</v>
       </c>
       <c r="H653" t="n">
         <v>484844</v>
@@ -19335,7 +19335,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G654" t="n">
-        <v>7.40787410736084</v>
+        <v>7.40787315368652</v>
       </c>
       <c r="H654" t="n">
         <v>858682</v>
@@ -19364,7 +19364,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G655" t="n">
-        <v>7.58376550674438</v>
+        <v>7.58376455307007</v>
       </c>
       <c r="H655" t="n">
         <v>961945</v>
@@ -19393,7 +19393,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G656" t="n">
-        <v>7.69011783599854</v>
+        <v>7.69011735916138</v>
       </c>
       <c r="H656" t="n">
         <v>988359</v>
@@ -19422,7 +19422,7 @@
         <v>9.625</v>
       </c>
       <c r="G657" t="n">
-        <v>7.87418842315674</v>
+        <v>7.87418937683105</v>
       </c>
       <c r="H657" t="n">
         <v>276866</v>
@@ -19451,7 +19451,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>8.11552906036377</v>
+        <v>8.11552810668945</v>
       </c>
       <c r="H658" t="n">
         <v>558980</v>
@@ -19480,7 +19480,7 @@
         <v>9.65499973297119</v>
       </c>
       <c r="G659" t="n">
-        <v>7.89873361587524</v>
+        <v>7.89873266220093</v>
       </c>
       <c r="H659" t="n">
         <v>502797</v>
@@ -19509,7 +19509,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G660" t="n">
-        <v>8.02553653717041</v>
+        <v>8.02553844451904</v>
       </c>
       <c r="H660" t="n">
         <v>392487</v>
@@ -19538,7 +19538,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G661" t="n">
-        <v>7.935546875</v>
+        <v>7.93554592132568</v>
       </c>
       <c r="H661" t="n">
         <v>425488</v>
@@ -19625,7 +19625,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G664" t="n">
-        <v>7.95190763473511</v>
+        <v>7.95190858840942</v>
       </c>
       <c r="H664" t="n">
         <v>348408</v>
@@ -19654,7 +19654,7 @@
         <v>9.77499961853027</v>
       </c>
       <c r="G665" t="n">
-        <v>7.99690198898315</v>
+        <v>7.99690389633179</v>
       </c>
       <c r="H665" t="n">
         <v>324862</v>
@@ -19799,7 +19799,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G670" t="n">
-        <v>7.8619179725647</v>
+        <v>7.86191701889038</v>
       </c>
       <c r="H670" t="n">
         <v>441699</v>
@@ -19828,7 +19828,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G671" t="n">
-        <v>8.107346534729</v>
+        <v>8.10734748840332</v>
       </c>
       <c r="H671" t="n">
         <v>414312</v>
@@ -19886,7 +19886,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G673" t="n">
-        <v>7.83328533172607</v>
+        <v>7.83328437805176</v>
       </c>
       <c r="H673" t="n">
         <v>501766</v>
@@ -19915,7 +19915,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G674" t="n">
-        <v>7.52649784088135</v>
+        <v>7.52649831771851</v>
       </c>
       <c r="H674" t="n">
         <v>466816</v>
@@ -19944,7 +19944,7 @@
         <v>9.47500038146973</v>
       </c>
       <c r="G675" t="n">
-        <v>7.75147485733032</v>
+        <v>7.75147438049316</v>
       </c>
       <c r="H675" t="n">
         <v>446246</v>
@@ -19973,7 +19973,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G676" t="n">
-        <v>7.73102188110352</v>
+        <v>7.73102235794067</v>
       </c>
       <c r="H676" t="n">
         <v>349187</v>
@@ -20002,7 +20002,7 @@
         <v>9.38500022888184</v>
       </c>
       <c r="G677" t="n">
-        <v>7.67784595489502</v>
+        <v>7.67784547805786</v>
       </c>
       <c r="H677" t="n">
         <v>609776</v>
@@ -20031,7 +20031,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G678" t="n">
-        <v>7.49377346038818</v>
+        <v>7.4937744140625</v>
       </c>
       <c r="H678" t="n">
         <v>345996</v>
@@ -20060,7 +20060,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G679" t="n">
-        <v>7.65739297866821</v>
+        <v>7.65739345550537</v>
       </c>
       <c r="H679" t="n">
         <v>318339</v>
@@ -20118,7 +20118,7 @@
         <v>9.29500007629395</v>
       </c>
       <c r="G681" t="n">
-        <v>7.60421657562256</v>
+        <v>7.60421705245972</v>
       </c>
       <c r="H681" t="n">
         <v>302584</v>
@@ -20176,7 +20176,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G683" t="n">
-        <v>8.07462310791016</v>
+        <v>8.07462215423584</v>
       </c>
       <c r="H683" t="n">
         <v>417479</v>
@@ -20205,7 +20205,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G684" t="n">
-        <v>8.05826091766357</v>
+        <v>8.05826187133789</v>
       </c>
       <c r="H684" t="n">
         <v>532388</v>
@@ -20263,7 +20263,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G686" t="n">
-        <v>8.06644058227539</v>
+        <v>8.06644248962402</v>
       </c>
       <c r="H686" t="n">
         <v>210290</v>
@@ -20292,7 +20292,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G687" t="n">
-        <v>8.03780937194824</v>
+        <v>8.03780841827393</v>
       </c>
       <c r="H687" t="n">
         <v>274818</v>
@@ -20321,7 +20321,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G688" t="n">
-        <v>8.01735591888428</v>
+        <v>8.01735687255859</v>
       </c>
       <c r="H688" t="n">
         <v>445963</v>
@@ -20408,7 +20408,7 @@
         <v>9.90999984741211</v>
       </c>
       <c r="G691" t="n">
-        <v>8.107346534729</v>
+        <v>8.10734748840332</v>
       </c>
       <c r="H691" t="n">
         <v>213471</v>
@@ -20495,7 +20495,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>8.03780937194824</v>
+        <v>8.03780841827393</v>
       </c>
       <c r="H694" t="n">
         <v>132555</v>
@@ -20524,7 +20524,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G695" t="n">
-        <v>8.05008125305176</v>
+        <v>8.05008029937744</v>
       </c>
       <c r="H695" t="n">
         <v>181571</v>
@@ -20553,7 +20553,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>8.08280467987061</v>
+        <v>8.08280372619629</v>
       </c>
       <c r="H696" t="n">
         <v>266104</v>
@@ -20640,7 +20640,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G699" t="n">
-        <v>8.46730899810791</v>
+        <v>8.46731090545654</v>
       </c>
       <c r="H699" t="n">
         <v>264854</v>
@@ -20669,7 +20669,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G700" t="n">
-        <v>8.37731838226318</v>
+        <v>8.3773193359375</v>
       </c>
       <c r="H700" t="n">
         <v>309492</v>
@@ -20785,7 +20785,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G704" t="n">
-        <v>8.47549057006836</v>
+        <v>8.47549152374268</v>
       </c>
       <c r="H704" t="n">
         <v>323226</v>
@@ -20872,7 +20872,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G707" t="n">
-        <v>8.32005214691162</v>
+        <v>8.32005310058594</v>
       </c>
       <c r="H707" t="n">
         <v>308436</v>
@@ -20988,7 +20988,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G711" t="n">
-        <v>8.43458652496338</v>
+        <v>8.43458557128906</v>
       </c>
       <c r="H711" t="n">
         <v>434828</v>
@@ -21017,7 +21017,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G712" t="n">
-        <v>8.54093837738037</v>
+        <v>8.54093742370605</v>
       </c>
       <c r="H712" t="n">
         <v>207288</v>
@@ -21075,7 +21075,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G714" t="n">
-        <v>8.62274932861328</v>
+        <v>8.62274837493896</v>
       </c>
       <c r="H714" t="n">
         <v>252173</v>
@@ -21162,7 +21162,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G717" t="n">
-        <v>8.66365432739258</v>
+        <v>8.66365242004395</v>
       </c>
       <c r="H717" t="n">
         <v>265470</v>
@@ -21191,7 +21191,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G718" t="n">
-        <v>8.71273899078369</v>
+        <v>8.71273803710938</v>
       </c>
       <c r="H718" t="n">
         <v>166740</v>
@@ -21249,7 +21249,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G720" t="n">
-        <v>9.34267330169678</v>
+        <v>9.34267425537109</v>
       </c>
       <c r="H720" t="n">
         <v>1065033</v>
@@ -21278,7 +21278,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G721" t="n">
-        <v>9.21177864074707</v>
+        <v>9.21177768707275</v>
       </c>
       <c r="H721" t="n">
         <v>658351</v>
@@ -21365,7 +21365,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G724" t="n">
-        <v>9.37539863586426</v>
+        <v>9.37539768218994</v>
       </c>
       <c r="H724" t="n">
         <v>355669</v>
@@ -21510,7 +21510,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G729" t="n">
-        <v>9.48175048828125</v>
+        <v>9.48175144195557</v>
       </c>
       <c r="H729" t="n">
         <v>498855</v>
@@ -21539,7 +21539,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>9.32631301879883</v>
+        <v>9.32631206512451</v>
       </c>
       <c r="H730" t="n">
         <v>513279</v>
@@ -21568,7 +21568,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>9.32631301879883</v>
+        <v>9.32631206512451</v>
       </c>
       <c r="H731" t="n">
         <v>283035</v>
@@ -21597,7 +21597,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G732" t="n">
-        <v>9.18723678588867</v>
+        <v>9.18723583221436</v>
       </c>
       <c r="H732" t="n">
         <v>552882</v>
@@ -21626,7 +21626,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G733" t="n">
-        <v>9.32631301879883</v>
+        <v>9.32631206512451</v>
       </c>
       <c r="H733" t="n">
         <v>298013</v>
@@ -21684,7 +21684,7 @@
         <v>11.0100002288818</v>
       </c>
       <c r="G735" t="n">
-        <v>9.00725555419922</v>
+        <v>9.00725364685059</v>
       </c>
       <c r="H735" t="n">
         <v>784665</v>
@@ -21713,7 +21713,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G736" t="n">
-        <v>8.87635898590088</v>
+        <v>8.8763599395752</v>
       </c>
       <c r="H736" t="n">
         <v>671137</v>
@@ -21800,7 +21800,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G739" t="n">
-        <v>9.10542583465576</v>
+        <v>9.10542678833008</v>
       </c>
       <c r="H739" t="n">
         <v>290873</v>
@@ -21829,7 +21829,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G740" t="n">
-        <v>9.10542583465576</v>
+        <v>9.10542678833008</v>
       </c>
       <c r="H740" t="n">
         <v>223076</v>
@@ -21858,7 +21858,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G741" t="n">
-        <v>8.80273056030273</v>
+        <v>8.80272960662842</v>
       </c>
       <c r="H741" t="n">
         <v>1078628</v>
@@ -21916,7 +21916,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>8.67183399200439</v>
+        <v>8.67183494567871</v>
       </c>
       <c r="H743" t="n">
         <v>709865</v>
@@ -22003,7 +22003,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G746" t="n">
-        <v>8.90908241271973</v>
+        <v>8.90908145904541</v>
       </c>
       <c r="H746" t="n">
         <v>269783</v>
@@ -22032,7 +22032,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G747" t="n">
-        <v>8.89272022247314</v>
+        <v>8.89271926879883</v>
       </c>
       <c r="H747" t="n">
         <v>338107</v>
@@ -22090,7 +22090,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>8.46730899810791</v>
+        <v>8.46731090545654</v>
       </c>
       <c r="H749" t="n">
         <v>3268981</v>
@@ -22119,7 +22119,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G750" t="n">
-        <v>8.41004180908203</v>
+        <v>8.41004276275635</v>
       </c>
       <c r="H750" t="n">
         <v>1307947</v>
@@ -22177,7 +22177,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G752" t="n">
-        <v>8.68819618225098</v>
+        <v>8.68819522857666</v>
       </c>
       <c r="H752" t="n">
         <v>1257597</v>
@@ -22206,7 +22206,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G753" t="n">
-        <v>8.68819618225098</v>
+        <v>8.68819522857666</v>
       </c>
       <c r="H753" t="n">
         <v>461208</v>
@@ -22235,7 +22235,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>8.87635898590088</v>
+        <v>8.8763599395752</v>
       </c>
       <c r="H754" t="n">
         <v>1030042</v>
@@ -22351,7 +22351,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G758" t="n">
-        <v>8.90090179443359</v>
+        <v>8.90090084075928</v>
       </c>
       <c r="H758" t="n">
         <v>341721</v>
@@ -22438,7 +22438,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G761" t="n">
-        <v>8.90090179443359</v>
+        <v>8.90090084075928</v>
       </c>
       <c r="H761" t="n">
         <v>354026</v>
@@ -22496,7 +22496,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G763" t="n">
-        <v>8.78636741638184</v>
+        <v>8.78636837005615</v>
       </c>
       <c r="H763" t="n">
         <v>273398</v>
@@ -22525,7 +22525,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G764" t="n">
-        <v>8.75364398956299</v>
+        <v>8.75364303588867</v>
       </c>
       <c r="H764" t="n">
         <v>332522</v>
@@ -22554,7 +22554,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G765" t="n">
-        <v>8.46730899810791</v>
+        <v>8.46731090545654</v>
       </c>
       <c r="H765" t="n">
         <v>454304</v>
@@ -22612,7 +22612,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>8.46730899810791</v>
+        <v>8.46731090545654</v>
       </c>
       <c r="H767" t="n">
         <v>292358</v>
@@ -22757,7 +22757,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G772" t="n">
-        <v>8.62274932861328</v>
+        <v>8.62274837493896</v>
       </c>
       <c r="H772" t="n">
         <v>754105</v>
@@ -22786,7 +22786,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G773" t="n">
-        <v>8.61456680297852</v>
+        <v>8.61456775665283</v>
       </c>
       <c r="H773" t="n">
         <v>304844</v>
@@ -22815,7 +22815,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G774" t="n">
-        <v>8.66365432739258</v>
+        <v>8.66365242004395</v>
       </c>
       <c r="H774" t="n">
         <v>322022</v>
@@ -22844,7 +22844,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G775" t="n">
-        <v>8.68029880523682</v>
+        <v>8.6802978515625</v>
       </c>
       <c r="H775" t="n">
         <v>378111</v>
@@ -22873,7 +22873,7 @@
         <v>10.210000038147</v>
       </c>
       <c r="G776" t="n">
-        <v>8.49720478057861</v>
+        <v>8.4972038269043</v>
       </c>
       <c r="H776" t="n">
         <v>440764</v>
@@ -22902,7 +22902,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G777" t="n">
-        <v>8.43062496185303</v>
+        <v>8.43062591552734</v>
       </c>
       <c r="H777" t="n">
         <v>169673</v>
@@ -22960,7 +22960,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G779" t="n">
-        <v>8.57210636138916</v>
+        <v>8.57210731506348</v>
       </c>
       <c r="H779" t="n">
         <v>618688</v>
@@ -22989,7 +22989,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G780" t="n">
-        <v>8.4389476776123</v>
+        <v>8.43894863128662</v>
       </c>
       <c r="H780" t="n">
         <v>334423</v>
@@ -23018,7 +23018,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>8.82177925109863</v>
+        <v>8.82178020477295</v>
       </c>
       <c r="H781" t="n">
         <v>1032920</v>
@@ -23047,7 +23047,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G782" t="n">
-        <v>8.57210636138916</v>
+        <v>8.57210731506348</v>
       </c>
       <c r="H782" t="n">
         <v>591926</v>
@@ -23076,7 +23076,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G783" t="n">
-        <v>8.68029880523682</v>
+        <v>8.6802978515625</v>
       </c>
       <c r="H783" t="n">
         <v>281762</v>
@@ -23192,7 +23192,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G787" t="n">
-        <v>8.48888301849365</v>
+        <v>8.48888206481934</v>
       </c>
       <c r="H787" t="n">
         <v>686851</v>
@@ -23221,7 +23221,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G788" t="n">
-        <v>8.4389476776123</v>
+        <v>8.43894863128662</v>
       </c>
       <c r="H788" t="n">
         <v>350852</v>
@@ -23250,7 +23250,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G789" t="n">
-        <v>8.36404609680176</v>
+        <v>8.36404705047607</v>
       </c>
       <c r="H789" t="n">
         <v>783143</v>
@@ -23279,7 +23279,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G790" t="n">
-        <v>8.33075523376465</v>
+        <v>8.33075618743896</v>
       </c>
       <c r="H790" t="n">
         <v>361673</v>
@@ -23308,7 +23308,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G791" t="n">
-        <v>8.33907794952393</v>
+        <v>8.33907890319824</v>
       </c>
       <c r="H791" t="n">
         <v>250466</v>
@@ -23337,7 +23337,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G792" t="n">
-        <v>8.2308874130249</v>
+        <v>8.23088645935059</v>
       </c>
       <c r="H792" t="n">
         <v>304699</v>
@@ -23366,7 +23366,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G793" t="n">
-        <v>8.33075523376465</v>
+        <v>8.33075618743896</v>
       </c>
       <c r="H793" t="n">
         <v>375242</v>
@@ -23395,7 +23395,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G794" t="n">
-        <v>8.27665996551514</v>
+        <v>8.27665901184082</v>
       </c>
       <c r="H794" t="n">
         <v>413922</v>
@@ -23424,7 +23424,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G795" t="n">
-        <v>8.15598487854004</v>
+        <v>8.15598583221436</v>
       </c>
       <c r="H795" t="n">
         <v>198057</v>
@@ -23453,7 +23453,7 @@
         <v>9.75</v>
       </c>
       <c r="G796" t="n">
-        <v>8.11437225341797</v>
+        <v>8.11437320709229</v>
       </c>
       <c r="H796" t="n">
         <v>379460</v>
@@ -23540,7 +23540,7 @@
         <v>9.83500003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>8.18511486053467</v>
+        <v>8.18511390686035</v>
       </c>
       <c r="H799" t="n">
         <v>779543</v>
@@ -23569,7 +23569,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G800" t="n">
-        <v>8.16430759429932</v>
+        <v>8.16430854797363</v>
       </c>
       <c r="H800" t="n">
         <v>206321</v>
@@ -23627,7 +23627,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G802" t="n">
-        <v>8.13933849334717</v>
+        <v>8.1393404006958</v>
       </c>
       <c r="H802" t="n">
         <v>210429</v>
@@ -23656,7 +23656,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G803" t="n">
-        <v>8.12269496917725</v>
+        <v>8.12269592285156</v>
       </c>
       <c r="H803" t="n">
         <v>169413</v>
@@ -23801,7 +23801,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G808" t="n">
-        <v>8.59707355499268</v>
+        <v>8.59707450866699</v>
       </c>
       <c r="H808" t="n">
         <v>1189901</v>
@@ -23859,7 +23859,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G810" t="n">
-        <v>8.36404609680176</v>
+        <v>8.36404705047607</v>
       </c>
       <c r="H810" t="n">
         <v>400586</v>
@@ -23888,7 +23888,7 @@
         <v>9.96500015258789</v>
       </c>
       <c r="G811" t="n">
-        <v>8.29330539703369</v>
+        <v>8.29330444335938</v>
       </c>
       <c r="H811" t="n">
         <v>539559</v>
@@ -23917,7 +23917,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G812" t="n">
-        <v>8.17678928375244</v>
+        <v>8.17679119110107</v>
       </c>
       <c r="H812" t="n">
         <v>710827</v>
@@ -23975,7 +23975,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G814" t="n">
-        <v>8.4389476776123</v>
+        <v>8.43894863128662</v>
       </c>
       <c r="H814" t="n">
         <v>429849</v>
@@ -24033,7 +24033,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G816" t="n">
-        <v>8.37236785888672</v>
+        <v>8.37236881256104</v>
       </c>
       <c r="H816" t="n">
         <v>223264</v>
@@ -24149,7 +24149,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G820" t="n">
-        <v>8.45559310913086</v>
+        <v>8.45559215545654</v>
       </c>
       <c r="H820" t="n">
         <v>379243</v>
@@ -24178,7 +24178,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G821" t="n">
-        <v>8.45559310913086</v>
+        <v>8.45559215545654</v>
       </c>
       <c r="H821" t="n">
         <v>239717</v>
@@ -24236,7 +24236,7 @@
         <v>10.0600004196167</v>
       </c>
       <c r="G823" t="n">
-        <v>8.37236785888672</v>
+        <v>8.37236881256104</v>
       </c>
       <c r="H823" t="n">
         <v>190413</v>
@@ -24265,7 +24265,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G824" t="n">
-        <v>8.42230319976807</v>
+        <v>8.42230224609375</v>
       </c>
       <c r="H824" t="n">
         <v>128364</v>
@@ -24294,7 +24294,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G825" t="n">
-        <v>8.33075523376465</v>
+        <v>8.33075618743896</v>
       </c>
       <c r="H825" t="n">
         <v>116209</v>
@@ -24323,7 +24323,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G826" t="n">
-        <v>8.05611610412598</v>
+        <v>8.05611515045166</v>
       </c>
       <c r="H826" t="n">
         <v>416839</v>
@@ -24352,7 +24352,7 @@
         <v>9.75</v>
       </c>
       <c r="G827" t="n">
-        <v>8.11437225341797</v>
+        <v>8.11437320709229</v>
       </c>
       <c r="H827" t="n">
         <v>278556</v>
@@ -24410,7 +24410,7 @@
         <v>9.64500045776367</v>
       </c>
       <c r="G829" t="n">
-        <v>8.02698707580566</v>
+        <v>8.02698802947998</v>
       </c>
       <c r="H829" t="n">
         <v>417303</v>
@@ -24468,7 +24468,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G831" t="n">
-        <v>7.88966751098633</v>
+        <v>7.88966655731201</v>
       </c>
       <c r="H831" t="n">
         <v>199448</v>
@@ -24497,7 +24497,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G832" t="n">
-        <v>7.75650787353516</v>
+        <v>7.75650691986084</v>
       </c>
       <c r="H832" t="n">
         <v>356645</v>
@@ -24526,7 +24526,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G833" t="n">
-        <v>8.05611610412598</v>
+        <v>8.05611515045166</v>
       </c>
       <c r="H833" t="n">
         <v>646709</v>
@@ -24584,7 +24584,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G835" t="n">
-        <v>7.82308673858643</v>
+        <v>7.82308721542358</v>
       </c>
       <c r="H835" t="n">
         <v>340826</v>
@@ -24613,7 +24613,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G836" t="n">
-        <v>7.76066875457764</v>
+        <v>7.76066923141479</v>
       </c>
       <c r="H836" t="n">
         <v>412835</v>
@@ -24642,7 +24642,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G837" t="n">
-        <v>7.66079998016357</v>
+        <v>7.66079950332642</v>
       </c>
       <c r="H837" t="n">
         <v>261618</v>
@@ -24671,7 +24671,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G838" t="n">
-        <v>7.68992757797241</v>
+        <v>7.68992853164673</v>
       </c>
       <c r="H838" t="n">
         <v>234612</v>
@@ -24700,7 +24700,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G839" t="n">
-        <v>7.59838247299194</v>
+        <v>7.59838151931763</v>
       </c>
       <c r="H839" t="n">
         <v>834614</v>
@@ -24729,7 +24729,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G840" t="n">
-        <v>7.59005880355835</v>
+        <v>7.59005832672119</v>
       </c>
       <c r="H840" t="n">
         <v>249357</v>
@@ -24787,7 +24787,7 @@
         <v>9.73999977111816</v>
       </c>
       <c r="G842" t="n">
-        <v>8.10605144500732</v>
+        <v>8.10605049133301</v>
       </c>
       <c r="H842" t="n">
         <v>495566</v>
@@ -24903,7 +24903,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G846" t="n">
-        <v>7.58589839935303</v>
+        <v>7.58589792251587</v>
       </c>
       <c r="H846" t="n">
         <v>2379822</v>
@@ -24932,7 +24932,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G847" t="n">
-        <v>7.81476497650146</v>
+        <v>7.81476545333862</v>
       </c>
       <c r="H847" t="n">
         <v>826883</v>
@@ -24961,7 +24961,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G848" t="n">
-        <v>7.66079998016357</v>
+        <v>7.66079950332642</v>
       </c>
       <c r="H848" t="n">
         <v>546004</v>
@@ -25019,7 +25019,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G850" t="n">
-        <v>7.58173704147339</v>
+        <v>7.58173656463623</v>
       </c>
       <c r="H850" t="n">
         <v>245277</v>
@@ -25048,7 +25048,7 @@
         <v>9.11499977111816</v>
       </c>
       <c r="G851" t="n">
-        <v>7.58589839935303</v>
+        <v>7.58589792251587</v>
       </c>
       <c r="H851" t="n">
         <v>375010</v>
@@ -25077,7 +25077,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G852" t="n">
-        <v>7.59838247299194</v>
+        <v>7.59838151931763</v>
       </c>
       <c r="H852" t="n">
         <v>793437</v>
@@ -25106,7 +25106,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G853" t="n">
-        <v>7.44025421142578</v>
+        <v>7.4402551651001</v>
       </c>
       <c r="H853" t="n">
         <v>1087057</v>
@@ -25193,7 +25193,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G856" t="n">
-        <v>8.13933849334717</v>
+        <v>8.1393404006958</v>
       </c>
       <c r="H856" t="n">
         <v>1884702</v>
@@ -25222,7 +25222,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G857" t="n">
-        <v>8.17678928375244</v>
+        <v>8.17679119110107</v>
       </c>
       <c r="H857" t="n">
         <v>803761</v>
@@ -25280,7 +25280,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G859" t="n">
-        <v>8.26417636871338</v>
+        <v>8.2641773223877</v>
       </c>
       <c r="H859" t="n">
         <v>594758</v>
@@ -25309,7 +25309,7 @@
         <v>9.94499969482422</v>
       </c>
       <c r="G860" t="n">
-        <v>8.27665996551514</v>
+        <v>8.27665901184082</v>
       </c>
       <c r="H860" t="n">
         <v>359477</v>
@@ -25338,7 +25338,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G861" t="n">
-        <v>8.1684684753418</v>
+        <v>8.16846752166748</v>
       </c>
       <c r="H861" t="n">
         <v>559114</v>
@@ -25367,7 +25367,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G862" t="n">
-        <v>8.28082275390625</v>
+        <v>8.28082180023193</v>
       </c>
       <c r="H862" t="n">
         <v>226432</v>
@@ -25425,7 +25425,7 @@
         <v>9.67500019073486</v>
       </c>
       <c r="G864" t="n">
-        <v>8.05195426940918</v>
+        <v>8.0519552230835</v>
       </c>
       <c r="H864" t="n">
         <v>1003775</v>
@@ -25483,7 +25483,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G866" t="n">
-        <v>8.07276153564453</v>
+        <v>8.07276058197021</v>
       </c>
       <c r="H866" t="n">
         <v>527067</v>
@@ -25512,7 +25512,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G867" t="n">
-        <v>8.31411075592041</v>
+        <v>8.31411170959473</v>
       </c>
       <c r="H867" t="n">
         <v>594371</v>
@@ -25541,7 +25541,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G868" t="n">
-        <v>8.380690574646</v>
+        <v>8.38068962097168</v>
       </c>
       <c r="H868" t="n">
         <v>333358</v>
@@ -25570,7 +25570,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>8.48888301849365</v>
+        <v>8.48888206481934</v>
       </c>
       <c r="H869" t="n">
         <v>334075</v>
@@ -25599,7 +25599,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G870" t="n">
-        <v>8.56378364562988</v>
+        <v>8.56378269195557</v>
       </c>
       <c r="H870" t="n">
         <v>554173</v>
@@ -25628,7 +25628,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G871" t="n">
-        <v>8.48888301849365</v>
+        <v>8.48888206481934</v>
       </c>
       <c r="H871" t="n">
         <v>1094381</v>
@@ -25686,7 +25686,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G873" t="n">
-        <v>8.45559310913086</v>
+        <v>8.45559215545654</v>
       </c>
       <c r="H873" t="n">
         <v>664283</v>
@@ -25744,7 +25744,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G875" t="n">
-        <v>8.33907794952393</v>
+        <v>8.33907890319824</v>
       </c>
       <c r="H875" t="n">
         <v>209099</v>
@@ -25773,7 +25773,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>8.36404609680176</v>
+        <v>8.36404705047607</v>
       </c>
       <c r="H876" t="n">
         <v>432876</v>
@@ -25831,7 +25831,7 @@
         <v>10.5</v>
       </c>
       <c r="G878" t="n">
-        <v>8.73855400085449</v>
+        <v>8.73855495452881</v>
       </c>
       <c r="H878" t="n">
         <v>634417</v>
@@ -25860,7 +25860,7 @@
         <v>10.5</v>
       </c>
       <c r="G879" t="n">
-        <v>8.73855400085449</v>
+        <v>8.73855495452881</v>
       </c>
       <c r="H879" t="n">
         <v>407080</v>
@@ -25889,7 +25889,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G880" t="n">
-        <v>8.85507011413574</v>
+        <v>8.85506916046143</v>
       </c>
       <c r="H880" t="n">
         <v>1020333</v>
@@ -25918,7 +25918,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G881" t="n">
-        <v>8.68029880523682</v>
+        <v>8.6802978515625</v>
       </c>
       <c r="H881" t="n">
         <v>303608</v>
@@ -25947,7 +25947,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G882" t="n">
-        <v>8.73023128509521</v>
+        <v>8.73023223876953</v>
       </c>
       <c r="H882" t="n">
         <v>429456</v>
@@ -26005,7 +26005,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G884" t="n">
-        <v>8.76352119445801</v>
+        <v>8.76352310180664</v>
       </c>
       <c r="H884" t="n">
         <v>304864</v>
@@ -26034,7 +26034,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G885" t="n">
-        <v>8.81345748901367</v>
+        <v>8.81345653533936</v>
       </c>
       <c r="H885" t="n">
         <v>304262</v>
@@ -26063,7 +26063,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G886" t="n">
-        <v>8.380690574646</v>
+        <v>8.38068962097168</v>
       </c>
       <c r="H886" t="n">
         <v>1553395</v>
@@ -26121,7 +26121,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G888" t="n">
-        <v>8.07276153564453</v>
+        <v>8.07276058197021</v>
       </c>
       <c r="H888" t="n">
         <v>998913</v>
@@ -26208,7 +26208,7 @@
         <v>9.66499996185303</v>
       </c>
       <c r="G891" t="n">
-        <v>8.04363250732422</v>
+        <v>8.0436315536499</v>
       </c>
       <c r="H891" t="n">
         <v>326427</v>
@@ -26237,7 +26237,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G892" t="n">
-        <v>8.22256278991699</v>
+        <v>8.22256374359131</v>
       </c>
       <c r="H892" t="n">
         <v>788796</v>
@@ -26266,7 +26266,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G893" t="n">
-        <v>8.1684684753418</v>
+        <v>8.16846752166748</v>
       </c>
       <c r="H893" t="n">
         <v>328576</v>
@@ -26324,7 +26324,7 @@
         <v>9.98999977111816</v>
       </c>
       <c r="G895" t="n">
-        <v>8.31411075592041</v>
+        <v>8.31411170959473</v>
       </c>
       <c r="H895" t="n">
         <v>308009</v>
@@ -26411,7 +26411,7 @@
         <v>10.0299997329712</v>
       </c>
       <c r="G898" t="n">
-        <v>8.34739971160889</v>
+        <v>8.3474006652832</v>
       </c>
       <c r="H898" t="n">
         <v>540009</v>
@@ -26556,7 +26556,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G903" t="n">
-        <v>8.56378364562988</v>
+        <v>8.56378269195557</v>
       </c>
       <c r="H903" t="n">
         <v>446739</v>
@@ -26585,7 +26585,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G904" t="n">
-        <v>8.38901233673096</v>
+        <v>8.38901329040527</v>
       </c>
       <c r="H904" t="n">
         <v>224386</v>
@@ -26614,7 +26614,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G905" t="n">
-        <v>8.43062496185303</v>
+        <v>8.43062591552734</v>
       </c>
       <c r="H905" t="n">
         <v>164571</v>
@@ -26643,7 +26643,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G906" t="n">
-        <v>8.53881645202637</v>
+        <v>8.53881549835205</v>
       </c>
       <c r="H906" t="n">
         <v>337394</v>
@@ -26672,7 +26672,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G907" t="n">
-        <v>8.52217102050781</v>
+        <v>8.52217197418213</v>
       </c>
       <c r="H907" t="n">
         <v>124850</v>
@@ -26701,7 +26701,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G908" t="n">
-        <v>8.69694328308105</v>
+        <v>8.69694232940674</v>
       </c>
       <c r="H908" t="n">
         <v>525277</v>
@@ -26730,7 +26730,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G909" t="n">
-        <v>8.68029880523682</v>
+        <v>8.6802978515625</v>
       </c>
       <c r="H909" t="n">
         <v>384374</v>
@@ -26788,7 +26788,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G911" t="n">
-        <v>9.12138652801514</v>
+        <v>9.12138748168945</v>
       </c>
       <c r="H911" t="n">
         <v>1309365</v>
@@ -26817,7 +26817,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G912" t="n">
-        <v>9.4043493270874</v>
+        <v>9.40435123443604</v>
       </c>
       <c r="H912" t="n">
         <v>1011160</v>
@@ -26904,7 +26904,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G915" t="n">
-        <v>9.13803195953369</v>
+        <v>9.13803100585938</v>
       </c>
       <c r="H915" t="n">
         <v>729728</v>
@@ -26962,7 +26962,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G917" t="n">
-        <v>9.4376392364502</v>
+        <v>9.43764019012451</v>
       </c>
       <c r="H917" t="n">
         <v>905986</v>
@@ -27020,7 +27020,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G919" t="n">
-        <v>9.4043493270874</v>
+        <v>9.40435123443604</v>
       </c>
       <c r="H919" t="n">
         <v>270820</v>
@@ -27049,7 +27049,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>9.4043493270874</v>
+        <v>9.40435123443604</v>
       </c>
       <c r="H920" t="n">
         <v>413801</v>
@@ -27136,7 +27136,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G923" t="n">
-        <v>9.39602756500244</v>
+        <v>9.39602661132812</v>
       </c>
       <c r="H923" t="n">
         <v>597298</v>
@@ -27165,7 +27165,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G924" t="n">
-        <v>9.57911968231201</v>
+        <v>9.57912158966064</v>
       </c>
       <c r="H924" t="n">
         <v>1045039</v>
@@ -27223,7 +27223,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G926" t="n">
-        <v>9.61241054534912</v>
+        <v>9.61241149902344</v>
       </c>
       <c r="H926" t="n">
         <v>318881</v>
@@ -27252,7 +27252,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G927" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H927" t="n">
         <v>480625</v>
@@ -27455,7 +27455,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G934" t="n">
-        <v>9.84543991088867</v>
+        <v>9.84543800354004</v>
       </c>
       <c r="H934" t="n">
         <v>430176</v>
@@ -27513,7 +27513,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>9.90369510650635</v>
+        <v>9.90369606018066</v>
       </c>
       <c r="H936" t="n">
         <v>345710</v>
@@ -27542,7 +27542,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G937" t="n">
-        <v>9.83711624145508</v>
+        <v>9.83711528778076</v>
       </c>
       <c r="H937" t="n">
         <v>671948</v>
@@ -27571,7 +27571,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G938" t="n">
-        <v>9.76221370697021</v>
+        <v>9.76221466064453</v>
       </c>
       <c r="H938" t="n">
         <v>219318</v>
@@ -27687,7 +27687,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G942" t="n">
-        <v>9.97859764099121</v>
+        <v>9.97859859466553</v>
       </c>
       <c r="H942" t="n">
         <v>193247</v>
@@ -27745,7 +27745,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>10.0701456069946</v>
+        <v>10.0701446533203</v>
       </c>
       <c r="H944" t="n">
         <v>242049</v>
@@ -27774,7 +27774,7 @@
         <v>12</v>
       </c>
       <c r="G945" t="n">
-        <v>9.98692035675049</v>
+        <v>9.98691940307617</v>
       </c>
       <c r="H945" t="n">
         <v>308288</v>
@@ -27832,7 +27832,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G947" t="n">
-        <v>9.87040615081787</v>
+        <v>9.87040424346924</v>
       </c>
       <c r="H947" t="n">
         <v>159151</v>
@@ -27861,7 +27861,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G948" t="n">
-        <v>9.90369510650635</v>
+        <v>9.90369606018066</v>
       </c>
       <c r="H948" t="n">
         <v>138549</v>
@@ -27890,7 +27890,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>9.65402412414551</v>
+        <v>9.65402317047119</v>
       </c>
       <c r="H949" t="n">
         <v>260575</v>
@@ -27919,7 +27919,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G950" t="n">
-        <v>9.77053642272949</v>
+        <v>9.77053737640381</v>
       </c>
       <c r="H950" t="n">
         <v>199288</v>
@@ -27948,7 +27948,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G951" t="n">
-        <v>9.82047176361084</v>
+        <v>9.82047080993652</v>
       </c>
       <c r="H951" t="n">
         <v>313543</v>
@@ -28006,7 +28006,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G953" t="n">
-        <v>9.34609317779541</v>
+        <v>9.34609222412109</v>
       </c>
       <c r="H953" t="n">
         <v>342977</v>
@@ -28093,7 +28093,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G956" t="n">
-        <v>9.82047176361084</v>
+        <v>9.82047080993652</v>
       </c>
       <c r="H956" t="n">
         <v>255407</v>
@@ -28122,7 +28122,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G957" t="n">
-        <v>9.56247520446777</v>
+        <v>9.56247615814209</v>
       </c>
       <c r="H957" t="n">
         <v>3009358</v>
@@ -28238,7 +28238,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G961" t="n">
-        <v>9.82047176361084</v>
+        <v>9.82047080993652</v>
       </c>
       <c r="H961" t="n">
         <v>379687</v>
@@ -28267,7 +28267,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G962" t="n">
-        <v>9.67066860198975</v>
+        <v>9.67066764831543</v>
       </c>
       <c r="H962" t="n">
         <v>440498</v>
@@ -28296,7 +28296,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G963" t="n">
-        <v>9.66234493255615</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H963" t="n">
         <v>434309</v>
@@ -28383,7 +28383,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G966" t="n">
-        <v>9.4043493270874</v>
+        <v>9.40435123443604</v>
       </c>
       <c r="H966" t="n">
         <v>587037</v>
@@ -28441,7 +28441,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G968" t="n">
-        <v>9.12970924377441</v>
+        <v>9.12971019744873</v>
       </c>
       <c r="H968" t="n">
         <v>436552</v>
@@ -28470,7 +28470,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G969" t="n">
-        <v>8.42230319976807</v>
+        <v>8.42230224609375</v>
       </c>
       <c r="H969" t="n">
         <v>1092305</v>
@@ -28557,7 +28557,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G972" t="n">
-        <v>7.87302112579346</v>
+        <v>7.87302207946777</v>
       </c>
       <c r="H972" t="n">
         <v>1259113</v>
@@ -28586,7 +28586,7 @@
         <v>9.44499969482422</v>
       </c>
       <c r="G973" t="n">
-        <v>7.86053943634033</v>
+        <v>7.8605375289917</v>
       </c>
       <c r="H973" t="n">
         <v>1223946</v>
@@ -28615,7 +28615,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G974" t="n">
-        <v>7.56925344467163</v>
+        <v>7.56925392150879</v>
       </c>
       <c r="H974" t="n">
         <v>1528046</v>
@@ -28644,7 +28644,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G975" t="n">
-        <v>7.76066875457764</v>
+        <v>7.76066923141479</v>
       </c>
       <c r="H975" t="n">
         <v>1655481</v>
@@ -28673,7 +28673,7 @@
         <v>8.97000026702881</v>
       </c>
       <c r="G976" t="n">
-        <v>7.46522331237793</v>
+        <v>7.46522283554077</v>
       </c>
       <c r="H976" t="n">
         <v>986040</v>
@@ -28702,7 +28702,7 @@
         <v>8.72500038146973</v>
       </c>
       <c r="G977" t="n">
-        <v>7.26132440567017</v>
+        <v>7.26132345199585</v>
       </c>
       <c r="H977" t="n">
         <v>601934</v>
@@ -28731,7 +28731,7 @@
         <v>8.60499954223633</v>
       </c>
       <c r="G978" t="n">
-        <v>7.16145372390747</v>
+        <v>7.16145324707031</v>
       </c>
       <c r="H978" t="n">
         <v>1506737</v>
@@ -28760,7 +28760,7 @@
         <v>8.25</v>
       </c>
       <c r="G979" t="n">
-        <v>6.86600780487061</v>
+        <v>6.86600732803345</v>
       </c>
       <c r="H979" t="n">
         <v>2017620</v>
@@ -28847,7 +28847,7 @@
         <v>6.625</v>
       </c>
       <c r="G982" t="n">
-        <v>5.51361274719238</v>
+        <v>5.51361179351807</v>
       </c>
       <c r="H982" t="n">
         <v>1063380</v>
@@ -28905,7 +28905,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G984" t="n">
-        <v>4.89359045028687</v>
+        <v>4.89359092712402</v>
       </c>
       <c r="H984" t="n">
         <v>2058172</v>
@@ -28934,7 +28934,7 @@
         <v>6</v>
       </c>
       <c r="G985" t="n">
-        <v>4.99346017837524</v>
+        <v>4.99345970153809</v>
       </c>
       <c r="H985" t="n">
         <v>1174791</v>
@@ -28963,7 +28963,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G986" t="n">
-        <v>4.93520307540894</v>
+        <v>4.93520212173462</v>
       </c>
       <c r="H986" t="n">
         <v>1064844</v>
@@ -29050,7 +29050,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G989" t="n">
-        <v>5.49280595779419</v>
+        <v>5.49280548095703</v>
       </c>
       <c r="H989" t="n">
         <v>677985</v>
@@ -29079,7 +29079,7 @@
         <v>6.85500001907349</v>
       </c>
       <c r="G990" t="n">
-        <v>5.70502853393555</v>
+        <v>5.70502805709839</v>
       </c>
       <c r="H990" t="n">
         <v>843020</v>
@@ -29108,7 +29108,7 @@
         <v>6.5</v>
       </c>
       <c r="G991" t="n">
-        <v>5.40958213806152</v>
+        <v>5.40958166122437</v>
       </c>
       <c r="H991" t="n">
         <v>718982</v>
@@ -29137,7 +29137,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G992" t="n">
-        <v>5.16823148727417</v>
+        <v>5.16823101043701</v>
       </c>
       <c r="H992" t="n">
         <v>1446561</v>
@@ -29166,7 +29166,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G993" t="n">
-        <v>4.89359045028687</v>
+        <v>4.89359092712402</v>
       </c>
       <c r="H993" t="n">
         <v>1020941</v>
@@ -29224,7 +29224,7 @@
         <v>6</v>
       </c>
       <c r="G995" t="n">
-        <v>4.99346017837524</v>
+        <v>4.99345970153809</v>
       </c>
       <c r="H995" t="n">
         <v>1625338</v>
@@ -29253,7 +29253,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G996" t="n">
-        <v>5.06836175918579</v>
+        <v>5.06836271286011</v>
       </c>
       <c r="H996" t="n">
         <v>1171946</v>
@@ -29311,7 +29311,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G998" t="n">
-        <v>4.67720699310303</v>
+        <v>4.67720746994019</v>
       </c>
       <c r="H998" t="n">
         <v>1226089</v>
@@ -29340,7 +29340,7 @@
         <v>6.22499990463257</v>
       </c>
       <c r="G999" t="n">
-        <v>5.18071413040161</v>
+        <v>5.18071460723877</v>
       </c>
       <c r="H999" t="n">
         <v>1864428</v>
@@ -29398,7 +29398,7 @@
         <v>6.125</v>
       </c>
       <c r="G1001" t="n">
-        <v>5.0974907875061</v>
+        <v>5.09748983383179</v>
       </c>
       <c r="H1001" t="n">
         <v>871831</v>
@@ -29427,7 +29427,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1002" t="n">
-        <v>5.1099739074707</v>
+        <v>5.10997438430786</v>
       </c>
       <c r="H1002" t="n">
         <v>1082379</v>
@@ -29456,7 +29456,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1003" t="n">
-        <v>5.1099739074707</v>
+        <v>5.10997438430786</v>
       </c>
       <c r="H1003" t="n">
         <v>841254</v>
@@ -29485,7 +29485,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1004" t="n">
-        <v>4.92688035964966</v>
+        <v>4.92688083648682</v>
       </c>
       <c r="H1004" t="n">
         <v>953735</v>
@@ -29659,7 +29659,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.92688035964966</v>
+        <v>4.92688083648682</v>
       </c>
       <c r="H1010" t="n">
         <v>613415</v>
@@ -29775,7 +29775,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1014" t="n">
-        <v>5.96718502044678</v>
+        <v>5.96718454360962</v>
       </c>
       <c r="H1014" t="n">
         <v>668847</v>
@@ -29804,7 +29804,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>5.60099840164185</v>
+        <v>5.60099792480469</v>
       </c>
       <c r="H1015" t="n">
         <v>1251440</v>
@@ -29833,7 +29833,7 @@
         <v>6.53000020980835</v>
       </c>
       <c r="G1016" t="n">
-        <v>5.43454933166504</v>
+        <v>5.43454885482788</v>
       </c>
       <c r="H1016" t="n">
         <v>606207</v>
@@ -29862,7 +29862,7 @@
         <v>6.4850001335144</v>
       </c>
       <c r="G1017" t="n">
-        <v>5.39709758758545</v>
+        <v>5.39709806442261</v>
       </c>
       <c r="H1017" t="n">
         <v>445894</v>
@@ -29891,7 +29891,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G1018" t="n">
-        <v>5.49280595779419</v>
+        <v>5.49280548095703</v>
       </c>
       <c r="H1018" t="n">
         <v>375381</v>
@@ -29920,7 +29920,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1019" t="n">
-        <v>5.76744604110718</v>
+        <v>5.76744651794434</v>
       </c>
       <c r="H1019" t="n">
         <v>717767</v>
@@ -29978,7 +29978,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1021" t="n">
-        <v>5.99215221405029</v>
+        <v>5.99215126037598</v>
       </c>
       <c r="H1021" t="n">
         <v>958351</v>
@@ -30007,7 +30007,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G1022" t="n">
-        <v>6.02128076553345</v>
+        <v>6.02128124237061</v>
       </c>
       <c r="H1022" t="n">
         <v>864858</v>
@@ -30065,7 +30065,7 @@
         <v>6.625</v>
       </c>
       <c r="G1024" t="n">
-        <v>5.51361274719238</v>
+        <v>5.51361179351807</v>
       </c>
       <c r="H1024" t="n">
         <v>1114931</v>
@@ -30094,7 +30094,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1025" t="n">
-        <v>5.57603073120117</v>
+        <v>5.57603025436401</v>
       </c>
       <c r="H1025" t="n">
         <v>460507</v>
@@ -30152,7 +30152,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G1027" t="n">
-        <v>5.70918941497803</v>
+        <v>5.70918989181519</v>
       </c>
       <c r="H1027" t="n">
         <v>885602</v>
@@ -30181,7 +30181,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G1028" t="n">
-        <v>5.65093231201172</v>
+        <v>5.65093278884888</v>
       </c>
       <c r="H1028" t="n">
         <v>644873</v>
@@ -30210,7 +30210,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G1029" t="n">
-        <v>5.5635461807251</v>
+        <v>5.56354665756226</v>
       </c>
       <c r="H1029" t="n">
         <v>592773</v>
@@ -30239,7 +30239,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G1030" t="n">
-        <v>5.55106258392334</v>
+        <v>5.5510630607605</v>
       </c>
       <c r="H1030" t="n">
         <v>581497</v>
@@ -30268,7 +30268,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G1031" t="n">
-        <v>5.9422173500061</v>
+        <v>5.94221782684326</v>
       </c>
       <c r="H1031" t="n">
         <v>984976</v>
@@ -30355,7 +30355,7 @@
         <v>7.5</v>
       </c>
       <c r="G1034" t="n">
-        <v>6.24182462692261</v>
+        <v>6.24182510375977</v>
       </c>
       <c r="H1034" t="n">
         <v>1086584</v>
@@ -30384,7 +30384,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1035" t="n">
-        <v>6.17940664291382</v>
+        <v>6.17940711975098</v>
       </c>
       <c r="H1035" t="n">
         <v>1199480</v>
@@ -30442,7 +30442,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1037" t="n">
-        <v>6.67043113708496</v>
+        <v>6.6704306602478</v>
       </c>
       <c r="H1037" t="n">
         <v>1037559</v>
@@ -30471,7 +30471,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1038" t="n">
-        <v>6.82439565658569</v>
+        <v>6.82439517974854</v>
       </c>
       <c r="H1038" t="n">
         <v>1475942</v>
@@ -30558,7 +30558,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1041" t="n">
-        <v>7.11984252929688</v>
+        <v>7.11984205245972</v>
       </c>
       <c r="H1041" t="n">
         <v>1274883</v>
@@ -30703,7 +30703,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G1046" t="n">
-        <v>6.4582085609436</v>
+        <v>6.45820903778076</v>
       </c>
       <c r="H1046" t="n">
         <v>1021789</v>
@@ -30761,7 +30761,7 @@
         <v>7.94000005722046</v>
       </c>
       <c r="G1048" t="n">
-        <v>6.60801267623901</v>
+        <v>6.60801219940186</v>
       </c>
       <c r="H1048" t="n">
         <v>431003</v>
@@ -30819,7 +30819,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G1050" t="n">
-        <v>6.52478790283203</v>
+        <v>6.52478742599487</v>
       </c>
       <c r="H1050" t="n">
         <v>472349</v>
@@ -31022,7 +31022,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1057" t="n">
-        <v>6.1752462387085</v>
+        <v>6.17524576187134</v>
       </c>
       <c r="H1057" t="n">
         <v>800959</v>
@@ -31080,7 +31080,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1059" t="n">
-        <v>6.04208660125732</v>
+        <v>6.04208707809448</v>
       </c>
       <c r="H1059" t="n">
         <v>684206</v>
@@ -31109,7 +31109,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1060" t="n">
-        <v>5.90892791748047</v>
+        <v>5.90892744064331</v>
       </c>
       <c r="H1060" t="n">
         <v>588429</v>
@@ -31196,7 +31196,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G1063" t="n">
-        <v>5.99215221405029</v>
+        <v>5.99215126037598</v>
       </c>
       <c r="H1063" t="n">
         <v>452481</v>
@@ -31225,7 +31225,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1064" t="n">
-        <v>5.97134637832642</v>
+        <v>5.97134590148926</v>
       </c>
       <c r="H1064" t="n">
         <v>379577</v>
@@ -31254,7 +31254,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G1065" t="n">
-        <v>5.93805646896362</v>
+        <v>5.93805694580078</v>
       </c>
       <c r="H1065" t="n">
         <v>524072</v>
@@ -31283,7 +31283,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1066" t="n">
-        <v>6.25014734268188</v>
+        <v>6.25014781951904</v>
       </c>
       <c r="H1066" t="n">
         <v>781909</v>
@@ -31312,7 +31312,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1067" t="n">
-        <v>6.13363361358643</v>
+        <v>6.13363313674927</v>
       </c>
       <c r="H1067" t="n">
         <v>469941</v>
@@ -31341,7 +31341,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1068" t="n">
-        <v>6.35833930969238</v>
+        <v>6.35833883285522</v>
       </c>
       <c r="H1068" t="n">
         <v>834157</v>
@@ -31370,7 +31370,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G1069" t="n">
-        <v>6.25014734268188</v>
+        <v>6.25014781951904</v>
       </c>
       <c r="H1069" t="n">
         <v>262656</v>
@@ -31399,7 +31399,7 @@
         <v>7.5</v>
       </c>
       <c r="G1070" t="n">
-        <v>6.24182462692261</v>
+        <v>6.24182510375977</v>
       </c>
       <c r="H1070" t="n">
         <v>529879</v>
@@ -31428,7 +31428,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G1071" t="n">
-        <v>6.1752462387085</v>
+        <v>6.17524576187134</v>
       </c>
       <c r="H1071" t="n">
         <v>318226</v>
@@ -31486,7 +31486,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G1073" t="n">
-        <v>6.36250019073486</v>
+        <v>6.36249971389771</v>
       </c>
       <c r="H1073" t="n">
         <v>480398</v>
@@ -31515,7 +31515,7 @@
         <v>7.5</v>
       </c>
       <c r="G1074" t="n">
-        <v>6.24182462692261</v>
+        <v>6.24182510375977</v>
       </c>
       <c r="H1074" t="n">
         <v>315075</v>
@@ -31573,7 +31573,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.95470094680786</v>
+        <v>5.95470142364502</v>
       </c>
       <c r="H1076" t="n">
         <v>622120</v>
@@ -31689,7 +31689,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.97550678253174</v>
+        <v>5.9755072593689</v>
       </c>
       <c r="H1080" t="n">
         <v>380321</v>
@@ -31747,7 +31747,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1082" t="n">
-        <v>5.96302318572998</v>
+        <v>5.9630241394043</v>
       </c>
       <c r="H1082" t="n">
         <v>562106</v>
@@ -31776,7 +31776,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.07121562957764</v>
+        <v>6.07121467590332</v>
       </c>
       <c r="H1083" t="n">
         <v>326816</v>
@@ -31805,7 +31805,7 @@
         <v>7.10500001907349</v>
       </c>
       <c r="G1084" t="n">
-        <v>5.91308927536011</v>
+        <v>5.91308879852295</v>
       </c>
       <c r="H1084" t="n">
         <v>289747</v>
@@ -31834,7 +31834,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G1085" t="n">
-        <v>5.89228248596191</v>
+        <v>5.89228296279907</v>
       </c>
       <c r="H1085" t="n">
         <v>551184</v>
@@ -31892,7 +31892,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.27095413208008</v>
+        <v>6.27095365524292</v>
       </c>
       <c r="H1087" t="n">
         <v>635715</v>
@@ -31979,7 +31979,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1090" t="n">
-        <v>6.13363361358643</v>
+        <v>6.13363313674927</v>
       </c>
       <c r="H1090" t="n">
         <v>171282</v>
@@ -32008,7 +32008,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1091" t="n">
-        <v>6.12531089782715</v>
+        <v>6.12531185150146</v>
       </c>
       <c r="H1091" t="n">
         <v>166762</v>
@@ -32037,7 +32037,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1092" t="n">
-        <v>6.08369874954224</v>
+        <v>6.08369827270508</v>
       </c>
       <c r="H1092" t="n">
         <v>237272</v>
@@ -32066,7 +32066,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G1093" t="n">
-        <v>6.02128076553345</v>
+        <v>6.02128124237061</v>
       </c>
       <c r="H1093" t="n">
         <v>207899</v>
@@ -32095,7 +32095,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G1094" t="n">
-        <v>5.96718502044678</v>
+        <v>5.96718454360962</v>
       </c>
       <c r="H1094" t="n">
         <v>148889</v>
@@ -32124,7 +32124,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G1095" t="n">
-        <v>6.04208660125732</v>
+        <v>6.04208707809448</v>
       </c>
       <c r="H1095" t="n">
         <v>432595</v>
@@ -32269,7 +32269,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G1100" t="n">
-        <v>6.19605159759521</v>
+        <v>6.19605207443237</v>
       </c>
       <c r="H1100" t="n">
         <v>191184</v>
@@ -32298,7 +32298,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G1101" t="n">
-        <v>6.27095413208008</v>
+        <v>6.27095365524292</v>
       </c>
       <c r="H1101" t="n">
         <v>521997</v>
@@ -32356,7 +32356,7 @@
         <v>7.82999992370605</v>
       </c>
       <c r="G1103" t="n">
-        <v>6.5164647102356</v>
+        <v>6.51646566390991</v>
       </c>
       <c r="H1103" t="n">
         <v>959400</v>
@@ -32414,7 +32414,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G1105" t="n">
-        <v>6.86184692382812</v>
+        <v>6.86184644699097</v>
       </c>
       <c r="H1105" t="n">
         <v>1014586</v>
@@ -32443,7 +32443,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1106" t="n">
-        <v>7.0324559211731</v>
+        <v>7.03245639801025</v>
       </c>
       <c r="H1106" t="n">
         <v>630127</v>
@@ -32472,7 +32472,7 @@
         <v>8.60999965667725</v>
       </c>
       <c r="G1107" t="n">
-        <v>7.16561508178711</v>
+        <v>7.16561460494995</v>
       </c>
       <c r="H1107" t="n">
         <v>918715</v>
@@ -32501,7 +32501,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1108" t="n">
-        <v>6.84936141967773</v>
+        <v>6.84936285018921</v>
       </c>
       <c r="H1108" t="n">
         <v>837524</v>
@@ -32588,7 +32588,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1111" t="n">
-        <v>6.82439565658569</v>
+        <v>6.82439517974854</v>
       </c>
       <c r="H1111" t="n">
         <v>536368</v>
@@ -32675,7 +32675,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G1114" t="n">
-        <v>6.73701000213623</v>
+        <v>6.73700952529907</v>
       </c>
       <c r="H1114" t="n">
         <v>403288</v>
@@ -32704,7 +32704,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1115" t="n">
-        <v>6.67459201812744</v>
+        <v>6.6745924949646</v>
       </c>
       <c r="H1115" t="n">
         <v>401776</v>
@@ -32733,7 +32733,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G1116" t="n">
-        <v>6.32921123504639</v>
+        <v>6.32921075820923</v>
       </c>
       <c r="H1116" t="n">
         <v>799601</v>
@@ -32762,7 +32762,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1117" t="n">
-        <v>6.12531089782715</v>
+        <v>6.12531185150146</v>
       </c>
       <c r="H1117" t="n">
         <v>977744</v>
@@ -32936,7 +32936,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G1123" t="n">
-        <v>6.08369874954224</v>
+        <v>6.08369827270508</v>
       </c>
       <c r="H1123" t="n">
         <v>743614</v>
@@ -33023,7 +33023,7 @@
         <v>7.29500007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>6.07121562957764</v>
+        <v>6.07121467590332</v>
       </c>
       <c r="H1126" t="n">
         <v>253688</v>
@@ -33081,7 +33081,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G1128" t="n">
-        <v>5.84234809875488</v>
+        <v>5.84234762191772</v>
       </c>
       <c r="H1128" t="n">
         <v>475336</v>
@@ -33313,7 +33313,7 @@
         <v>6.5</v>
       </c>
       <c r="G1136" t="n">
-        <v>5.40958213806152</v>
+        <v>5.40958166122437</v>
       </c>
       <c r="H1136" t="n">
         <v>595985</v>
@@ -33371,7 +33371,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1138" t="n">
-        <v>5.36796951293945</v>
+        <v>5.36796998977661</v>
       </c>
       <c r="H1138" t="n">
         <v>495632</v>
@@ -33429,7 +33429,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G1140" t="n">
-        <v>5.19319820404053</v>
+        <v>5.19319868087769</v>
       </c>
       <c r="H1140" t="n">
         <v>547876</v>
@@ -33458,7 +33458,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.97265434265137</v>
+        <v>4.97265386581421</v>
       </c>
       <c r="H1141" t="n">
         <v>823758</v>
@@ -33487,7 +33487,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.96849203109741</v>
+        <v>4.96849250793457</v>
       </c>
       <c r="H1142" t="n">
         <v>956681</v>
@@ -33516,7 +33516,7 @@
         <v>5.91499996185303</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.92271995544434</v>
+        <v>4.92271900177002</v>
       </c>
       <c r="H1143" t="n">
         <v>1044953</v>
@@ -33545,7 +33545,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1144" t="n">
-        <v>5.19735956192017</v>
+        <v>5.19736003875732</v>
       </c>
       <c r="H1144" t="n">
         <v>1595315</v>
@@ -33603,7 +33603,7 @@
         <v>6.40999984741211</v>
       </c>
       <c r="G1146" t="n">
-        <v>5.33467960357666</v>
+        <v>5.33468008041382</v>
       </c>
       <c r="H1146" t="n">
         <v>1034459</v>
@@ -33632,7 +33632,7 @@
         <v>6.625</v>
       </c>
       <c r="G1147" t="n">
-        <v>5.51361274719238</v>
+        <v>5.51361179351807</v>
       </c>
       <c r="H1147" t="n">
         <v>639431</v>
@@ -33661,7 +33661,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1148" t="n">
-        <v>5.65925455093384</v>
+        <v>5.659255027771</v>
       </c>
       <c r="H1148" t="n">
         <v>592371</v>
@@ -33719,7 +33719,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G1150" t="n">
-        <v>5.73415613174438</v>
+        <v>5.73415660858154</v>
       </c>
       <c r="H1150" t="n">
         <v>534994</v>
@@ -33748,7 +33748,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G1151" t="n">
-        <v>6.81607294082642</v>
+        <v>6.8160719871521</v>
       </c>
       <c r="H1151" t="n">
         <v>3683546</v>
@@ -33777,7 +33777,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1152" t="n">
-        <v>6.62049531936646</v>
+        <v>6.62049579620361</v>
       </c>
       <c r="H1152" t="n">
         <v>1532496</v>
@@ -33864,7 +33864,7 @@
         <v>8.3149995803833</v>
       </c>
       <c r="G1155" t="n">
-        <v>6.92010259628296</v>
+        <v>6.92010354995728</v>
       </c>
       <c r="H1155" t="n">
         <v>988621</v>
@@ -33893,7 +33893,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1156" t="n">
-        <v>8.07276153564453</v>
+        <v>8.07276058197021</v>
       </c>
       <c r="H1156" t="n">
         <v>2995188</v>
@@ -33951,7 +33951,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1158" t="n">
-        <v>7.73986339569092</v>
+        <v>7.73986387252808</v>
       </c>
       <c r="H1158" t="n">
         <v>1672437</v>
@@ -34009,7 +34009,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1160" t="n">
-        <v>7.36535358428955</v>
+        <v>7.36535453796387</v>
       </c>
       <c r="H1160" t="n">
         <v>441310</v>
@@ -34038,7 +34038,7 @@
         <v>8.79500007629395</v>
       </c>
       <c r="G1161" t="n">
-        <v>7.319580078125</v>
+        <v>7.31958103179932</v>
       </c>
       <c r="H1161" t="n">
         <v>790804</v>
@@ -34067,7 +34067,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G1162" t="n">
-        <v>7.59005880355835</v>
+        <v>7.59005832672119</v>
       </c>
       <c r="H1162" t="n">
         <v>853925</v>
@@ -34096,7 +34096,7 @@
         <v>9.09500026702881</v>
       </c>
       <c r="G1163" t="n">
-        <v>7.56925344467163</v>
+        <v>7.56925392150879</v>
       </c>
       <c r="H1163" t="n">
         <v>1015132</v>
@@ -34125,7 +34125,7 @@
         <v>9</v>
       </c>
       <c r="G1164" t="n">
-        <v>7.49019002914429</v>
+        <v>7.49019050598145</v>
       </c>
       <c r="H1164" t="n">
         <v>489336</v>
@@ -34154,7 +34154,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>7.42361068725586</v>
+        <v>7.42360973358154</v>
       </c>
       <c r="H1165" t="n">
         <v>800168</v>
@@ -34183,7 +34183,7 @@
         <v>8.99499988555908</v>
       </c>
       <c r="G1166" t="n">
-        <v>7.48602867126465</v>
+        <v>7.48602724075317</v>
       </c>
       <c r="H1166" t="n">
         <v>803082</v>
@@ -34299,7 +34299,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1170" t="n">
-        <v>7.75650787353516</v>
+        <v>7.75650691986084</v>
       </c>
       <c r="H1170" t="n">
         <v>605586</v>
@@ -34328,7 +34328,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1171" t="n">
-        <v>7.73154067993164</v>
+        <v>7.73154020309448</v>
       </c>
       <c r="H1171" t="n">
         <v>325427</v>
@@ -34415,7 +34415,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G1174" t="n">
-        <v>7.73986339569092</v>
+        <v>7.73986387252808</v>
       </c>
       <c r="H1174" t="n">
         <v>479342</v>
@@ -34444,7 +34444,7 @@
         <v>9.05500030517578</v>
       </c>
       <c r="G1175" t="n">
-        <v>7.53596258163452</v>
+        <v>7.53596353530884</v>
       </c>
       <c r="H1175" t="n">
         <v>542278</v>
@@ -34473,7 +34473,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1176" t="n">
-        <v>7.66079998016357</v>
+        <v>7.66079950332642</v>
       </c>
       <c r="H1176" t="n">
         <v>510238</v>
@@ -34502,7 +34502,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1177" t="n">
-        <v>7.59838247299194</v>
+        <v>7.59838151931763</v>
       </c>
       <c r="H1177" t="n">
         <v>632086</v>
@@ -34560,7 +34560,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G1179" t="n">
-        <v>7.67328405380249</v>
+        <v>7.67328310012817</v>
       </c>
       <c r="H1179" t="n">
         <v>490383</v>
@@ -34589,7 +34589,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1180" t="n">
-        <v>7.68992757797241</v>
+        <v>7.68992853164673</v>
       </c>
       <c r="H1180" t="n">
         <v>442789</v>
@@ -34618,7 +34618,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1181" t="n">
-        <v>7.65663814544678</v>
+        <v>7.65663909912109</v>
       </c>
       <c r="H1181" t="n">
         <v>953015</v>
@@ -34647,7 +34647,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1182" t="n">
-        <v>7.49851369857788</v>
+        <v>7.49851322174072</v>
       </c>
       <c r="H1182" t="n">
         <v>1258663</v>
@@ -34676,7 +34676,7 @@
         <v>9</v>
       </c>
       <c r="G1183" t="n">
-        <v>7.49019002914429</v>
+        <v>7.49019050598145</v>
       </c>
       <c r="H1183" t="n">
         <v>1179598</v>
@@ -34705,7 +34705,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G1184" t="n">
-        <v>7.73154067993164</v>
+        <v>7.73154020309448</v>
       </c>
       <c r="H1184" t="n">
         <v>772533</v>
@@ -34763,7 +34763,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1186" t="n">
-        <v>7.68992757797241</v>
+        <v>7.68992853164673</v>
       </c>
       <c r="H1186" t="n">
         <v>276809</v>
@@ -34792,7 +34792,7 @@
         <v>9.23499965667725</v>
       </c>
       <c r="G1187" t="n">
-        <v>7.68576717376709</v>
+        <v>7.68576765060425</v>
       </c>
       <c r="H1187" t="n">
         <v>484415</v>
@@ -34821,7 +34821,7 @@
         <v>9.27000045776367</v>
       </c>
       <c r="G1188" t="n">
-        <v>7.71489715576172</v>
+        <v>7.7148962020874</v>
       </c>
       <c r="H1188" t="n">
         <v>459399</v>
@@ -34850,7 +34850,7 @@
         <v>9.06999969482422</v>
       </c>
       <c r="G1189" t="n">
-        <v>7.54844665527344</v>
+        <v>7.54844617843628</v>
       </c>
       <c r="H1189" t="n">
         <v>1148276</v>
@@ -34908,7 +34908,7 @@
         <v>9</v>
       </c>
       <c r="G1191" t="n">
-        <v>7.49019002914429</v>
+        <v>7.49019050598145</v>
       </c>
       <c r="H1191" t="n">
         <v>979210</v>
@@ -34937,7 +34937,7 @@
         <v>9</v>
       </c>
       <c r="G1192" t="n">
-        <v>7.49019002914429</v>
+        <v>7.49019050598145</v>
       </c>
       <c r="H1192" t="n">
         <v>606851</v>
@@ -34966,7 +34966,7 @@
         <v>8.82499980926514</v>
       </c>
       <c r="G1193" t="n">
-        <v>7.34454774856567</v>
+        <v>7.34454822540283</v>
       </c>
       <c r="H1193" t="n">
         <v>516791</v>
@@ -34995,7 +34995,7 @@
         <v>8.95499992370605</v>
       </c>
       <c r="G1194" t="n">
-        <v>7.45273923873901</v>
+        <v>7.45273876190186</v>
       </c>
       <c r="H1194" t="n">
         <v>528921</v>
@@ -35053,7 +35053,7 @@
         <v>8.74499988555908</v>
       </c>
       <c r="G1196" t="n">
-        <v>7.27796792984009</v>
+        <v>7.27796745300293</v>
       </c>
       <c r="H1196" t="n">
         <v>395935</v>
@@ -35082,7 +35082,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1197" t="n">
-        <v>7.15729331970215</v>
+        <v>7.15729379653931</v>
       </c>
       <c r="H1197" t="n">
         <v>630045</v>
@@ -35169,7 +35169,7 @@
         <v>8.63500022888184</v>
       </c>
       <c r="G1200" t="n">
-        <v>7.18642139434814</v>
+        <v>7.18642044067383</v>
       </c>
       <c r="H1200" t="n">
         <v>498515</v>
@@ -35198,7 +35198,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G1201" t="n">
-        <v>7.06158447265625</v>
+        <v>7.06158494949341</v>
       </c>
       <c r="H1201" t="n">
         <v>352249</v>
@@ -35256,7 +35256,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G1203" t="n">
-        <v>7.06158447265625</v>
+        <v>7.06158494949341</v>
       </c>
       <c r="H1203" t="n">
         <v>528178</v>
@@ -35285,7 +35285,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G1204" t="n">
-        <v>6.93674755096436</v>
+        <v>6.93674802780151</v>
       </c>
       <c r="H1204" t="n">
         <v>725848</v>
@@ -35314,7 +35314,7 @@
         <v>8.47500038146973</v>
       </c>
       <c r="G1205" t="n">
-        <v>7.05326271057129</v>
+        <v>7.05326318740845</v>
       </c>
       <c r="H1205" t="n">
         <v>542476</v>
@@ -35401,7 +35401,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1208" t="n">
-        <v>7.50683546066284</v>
+        <v>7.5068359375</v>
       </c>
       <c r="H1208" t="n">
         <v>418361</v>
@@ -35430,7 +35430,7 @@
         <v>9.14500045776367</v>
       </c>
       <c r="G1209" t="n">
-        <v>7.61086559295654</v>
+        <v>7.61086511611938</v>
       </c>
       <c r="H1209" t="n">
         <v>895468</v>
@@ -35459,7 +35459,7 @@
         <v>9.13000011444092</v>
       </c>
       <c r="G1210" t="n">
-        <v>7.59838247299194</v>
+        <v>7.59838151931763</v>
       </c>
       <c r="H1210" t="n">
         <v>629602</v>
@@ -35488,7 +35488,7 @@
         <v>8.89500045776367</v>
       </c>
       <c r="G1211" t="n">
-        <v>7.40280485153198</v>
+        <v>7.40280437469482</v>
       </c>
       <c r="H1211" t="n">
         <v>851592</v>
@@ -35517,7 +35517,7 @@
         <v>9.20499992370605</v>
       </c>
       <c r="G1212" t="n">
-        <v>7.66079998016357</v>
+        <v>7.66079950332642</v>
       </c>
       <c r="H1212" t="n">
         <v>1722239</v>
@@ -35546,7 +35546,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G1213" t="n">
-        <v>7.71905708312988</v>
+        <v>7.71905612945557</v>
       </c>
       <c r="H1213" t="n">
         <v>532913</v>
@@ -35575,7 +35575,7 @@
         <v>9.69499969482422</v>
       </c>
       <c r="G1214" t="n">
-        <v>8.06859874725342</v>
+        <v>8.0685977935791</v>
       </c>
       <c r="H1214" t="n">
         <v>1665763</v>
@@ -35691,7 +35691,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1218" t="n">
-        <v>8.07276153564453</v>
+        <v>8.07276058197021</v>
       </c>
       <c r="H1218" t="n">
         <v>586734</v>
@@ -35720,7 +35720,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1219" t="n">
-        <v>8.03947067260742</v>
+        <v>8.03947162628174</v>
       </c>
       <c r="H1219" t="n">
         <v>499371</v>
@@ -35749,7 +35749,7 @@
         <v>9.6850004196167</v>
       </c>
       <c r="G1220" t="n">
-        <v>8.06027698516846</v>
+        <v>8.06027793884277</v>
       </c>
       <c r="H1220" t="n">
         <v>569534</v>
@@ -35778,7 +35778,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G1221" t="n">
-        <v>8.16014575958252</v>
+        <v>8.1601448059082</v>
       </c>
       <c r="H1221" t="n">
         <v>388414</v>
@@ -35807,7 +35807,7 @@
         <v>9.60999965667725</v>
       </c>
       <c r="G1222" t="n">
-        <v>7.99785757064819</v>
+        <v>7.99785852432251</v>
       </c>
       <c r="H1222" t="n">
         <v>310234</v>
@@ -35836,7 +35836,7 @@
         <v>9.39000034332275</v>
       </c>
       <c r="G1223" t="n">
-        <v>7.81476497650146</v>
+        <v>7.81476545333862</v>
       </c>
       <c r="H1223" t="n">
         <v>611461</v>
@@ -35865,7 +35865,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1224" t="n">
-        <v>7.82308673858643</v>
+        <v>7.82308721542358</v>
       </c>
       <c r="H1224" t="n">
         <v>762128</v>
@@ -35894,7 +35894,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G1225" t="n">
-        <v>7.65247821807861</v>
+        <v>7.65247678756714</v>
       </c>
       <c r="H1225" t="n">
         <v>434472</v>
@@ -36039,7 +36039,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G1230" t="n">
-        <v>8.16014575958252</v>
+        <v>8.1601448059082</v>
       </c>
       <c r="H1230" t="n">
         <v>974912</v>
@@ -36068,7 +36068,7 @@
         <v>9.67500019073486</v>
       </c>
       <c r="G1231" t="n">
-        <v>8.05195426940918</v>
+        <v>8.0519552230835</v>
       </c>
       <c r="H1231" t="n">
         <v>773827</v>
@@ -36097,7 +36097,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G1232" t="n">
-        <v>8.17678928375244</v>
+        <v>8.17679119110107</v>
       </c>
       <c r="H1232" t="n">
         <v>450014</v>
@@ -36155,7 +36155,7 @@
         <v>10.0100002288818</v>
       </c>
       <c r="G1234" t="n">
-        <v>8.33075523376465</v>
+        <v>8.33075618743896</v>
       </c>
       <c r="H1234" t="n">
         <v>856533</v>
@@ -36213,7 +36213,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G1236" t="n">
-        <v>8.48055839538574</v>
+        <v>8.48055934906006</v>
       </c>
       <c r="H1236" t="n">
         <v>489386</v>
@@ -36242,7 +36242,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G1237" t="n">
-        <v>8.48055839538574</v>
+        <v>8.48055934906006</v>
       </c>
       <c r="H1237" t="n">
         <v>372012</v>
@@ -36300,7 +36300,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1239" t="n">
-        <v>8.38901233673096</v>
+        <v>8.38901329040527</v>
       </c>
       <c r="H1239" t="n">
         <v>265905</v>
@@ -36329,7 +36329,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1240" t="n">
-        <v>8.45559310913086</v>
+        <v>8.45559215545654</v>
       </c>
       <c r="H1240" t="n">
         <v>311321</v>
@@ -36358,7 +36358,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1241" t="n">
-        <v>8.45559310913086</v>
+        <v>8.45559215545654</v>
       </c>
       <c r="H1241" t="n">
         <v>283776</v>
@@ -36387,7 +36387,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1242" t="n">
-        <v>8.07276153564453</v>
+        <v>8.07276058197021</v>
       </c>
       <c r="H1242" t="n">
         <v>1068110</v>
@@ -36503,7 +36503,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G1246" t="n">
-        <v>8.16430759429932</v>
+        <v>8.16430854797363</v>
       </c>
       <c r="H1246" t="n">
         <v>514279</v>
@@ -36532,7 +36532,7 @@
         <v>9.80500030517578</v>
       </c>
       <c r="G1247" t="n">
-        <v>8.16014575958252</v>
+        <v>8.1601448059082</v>
       </c>
       <c r="H1247" t="n">
         <v>254659</v>
@@ -36561,7 +36561,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G1248" t="n">
-        <v>8.36404609680176</v>
+        <v>8.36404705047607</v>
       </c>
       <c r="H1248" t="n">
         <v>275611</v>
@@ -36619,7 +36619,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G1250" t="n">
-        <v>8.380690574646</v>
+        <v>8.38068962097168</v>
       </c>
       <c r="H1250" t="n">
         <v>384901</v>
@@ -36648,7 +36648,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1251" t="n">
-        <v>8.78016662597656</v>
+        <v>8.7801685333252</v>
       </c>
       <c r="H1251" t="n">
         <v>902306</v>
@@ -36677,7 +36677,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G1252" t="n">
-        <v>8.63036441802979</v>
+        <v>8.63036251068115</v>
       </c>
       <c r="H1252" t="n">
         <v>442178</v>
@@ -36706,7 +36706,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G1253" t="n">
-        <v>8.28082275390625</v>
+        <v>8.28082180023193</v>
       </c>
       <c r="H1253" t="n">
         <v>771614</v>
@@ -36735,7 +36735,7 @@
         <v>10.25</v>
       </c>
       <c r="G1254" t="n">
-        <v>8.53049373626709</v>
+        <v>8.53049468994141</v>
       </c>
       <c r="H1254" t="n">
         <v>408301</v>
@@ -36764,7 +36764,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1255" t="n">
-        <v>8.93829250335693</v>
+        <v>8.93829345703125</v>
       </c>
       <c r="H1255" t="n">
         <v>835569</v>
@@ -36822,7 +36822,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>8.82177925109863</v>
+        <v>8.82178020477295</v>
       </c>
       <c r="H1257" t="n">
         <v>448328</v>
@@ -36880,7 +36880,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1259" t="n">
-        <v>9.38770484924316</v>
+        <v>9.38770389556885</v>
       </c>
       <c r="H1259" t="n">
         <v>839790</v>
@@ -36909,7 +36909,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1260" t="n">
-        <v>9.42931842803955</v>
+        <v>9.42931747436523</v>
       </c>
       <c r="H1260" t="n">
         <v>889434</v>
@@ -36967,7 +36967,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G1262" t="n">
-        <v>8.88003730773926</v>
+        <v>8.88003635406494</v>
       </c>
       <c r="H1262" t="n">
         <v>703842</v>
@@ -36996,7 +36996,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1263" t="n">
-        <v>9.05480861663818</v>
+        <v>9.05480766296387</v>
       </c>
       <c r="H1263" t="n">
         <v>971844</v>
@@ -37025,7 +37025,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1264" t="n">
-        <v>8.88836002349854</v>
+        <v>8.8883581161499</v>
       </c>
       <c r="H1264" t="n">
         <v>446999</v>
@@ -37083,7 +37083,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1266" t="n">
-        <v>9.53750896453857</v>
+        <v>9.53750801086426</v>
       </c>
       <c r="H1266" t="n">
         <v>1435751</v>
@@ -37141,7 +37141,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1268" t="n">
-        <v>9.22957801818848</v>
+        <v>9.22957897186279</v>
       </c>
       <c r="H1268" t="n">
         <v>767210</v>
@@ -37199,7 +37199,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G1270" t="n">
-        <v>9.3128023147583</v>
+        <v>9.31280326843262</v>
       </c>
       <c r="H1270" t="n">
         <v>549253</v>
@@ -37286,7 +37286,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1273" t="n">
-        <v>9.38770484924316</v>
+        <v>9.38770389556885</v>
       </c>
       <c r="H1273" t="n">
         <v>840905</v>
@@ -37315,7 +37315,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1274" t="n">
-        <v>9.86208534240723</v>
+        <v>9.86208343505859</v>
       </c>
       <c r="H1274" t="n">
         <v>1790399</v>
@@ -37344,7 +37344,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1275" t="n">
-        <v>9.61241054534912</v>
+        <v>9.61241149902344</v>
       </c>
       <c r="H1275" t="n">
         <v>1418925</v>
@@ -37373,7 +37373,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1276" t="n">
-        <v>9.39602756500244</v>
+        <v>9.39602661132812</v>
       </c>
       <c r="H1276" t="n">
         <v>714093</v>
@@ -37460,7 +37460,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G1279" t="n">
-        <v>9.35441398620605</v>
+        <v>9.35441493988037</v>
       </c>
       <c r="H1279" t="n">
         <v>540716</v>
@@ -37576,7 +37576,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G1283" t="n">
-        <v>8.68029880523682</v>
+        <v>8.6802978515625</v>
       </c>
       <c r="H1283" t="n">
         <v>2354826</v>
@@ -37663,7 +37663,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G1286" t="n">
-        <v>8.81542015075684</v>
+        <v>8.81541919708252</v>
       </c>
       <c r="H1286" t="n">
         <v>1797174</v>
@@ -37750,7 +37750,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G1289" t="n">
-        <v>8.84942436218262</v>
+        <v>8.8494234085083</v>
       </c>
       <c r="H1289" t="n">
         <v>567341</v>
@@ -37779,7 +37779,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G1290" t="n">
-        <v>8.80691814422607</v>
+        <v>8.80691909790039</v>
       </c>
       <c r="H1290" t="n">
         <v>486717</v>
@@ -37866,7 +37866,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1293" t="n">
-        <v>9.07894802093506</v>
+        <v>9.07894706726074</v>
       </c>
       <c r="H1293" t="n">
         <v>995379</v>
@@ -37924,7 +37924,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1295" t="n">
-        <v>9.26596641540527</v>
+        <v>9.26596736907959</v>
       </c>
       <c r="H1295" t="n">
         <v>798691</v>
@@ -38040,7 +38040,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>9.30846977233887</v>
+        <v>9.30847072601318</v>
       </c>
       <c r="H1299" t="n">
         <v>542574</v>
@@ -38156,7 +38156,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G1303" t="n">
-        <v>8.9514331817627</v>
+        <v>8.95143413543701</v>
       </c>
       <c r="H1303" t="n">
         <v>345148</v>
@@ -38214,7 +38214,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1305" t="n">
-        <v>8.85792541503906</v>
+        <v>8.85792446136475</v>
       </c>
       <c r="H1305" t="n">
         <v>350212</v>
@@ -38359,7 +38359,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G1310" t="n">
-        <v>9.10445022583008</v>
+        <v>9.10444927215576</v>
       </c>
       <c r="H1310" t="n">
         <v>488302</v>
@@ -38446,7 +38446,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1313" t="n">
-        <v>9.07894802093506</v>
+        <v>9.07894706726074</v>
       </c>
       <c r="H1313" t="n">
         <v>364245</v>
@@ -38504,7 +38504,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1315" t="n">
-        <v>9.16395568847656</v>
+        <v>9.16395664215088</v>
       </c>
       <c r="H1315" t="n">
         <v>199145</v>
@@ -38533,7 +38533,7 @@
         <v>10.75</v>
       </c>
       <c r="G1316" t="n">
-        <v>9.13845348358154</v>
+        <v>9.13845443725586</v>
       </c>
       <c r="H1316" t="n">
         <v>342194</v>
@@ -38649,7 +38649,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1320" t="n">
-        <v>8.96843528747559</v>
+        <v>8.9684362411499</v>
       </c>
       <c r="H1320" t="n">
         <v>166956</v>
@@ -38765,7 +38765,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1324" t="n">
-        <v>8.85792541503906</v>
+        <v>8.85792446136475</v>
       </c>
       <c r="H1324" t="n">
         <v>412228</v>
@@ -38939,7 +38939,7 @@
         <v>10.75</v>
       </c>
       <c r="G1330" t="n">
-        <v>9.13845348358154</v>
+        <v>9.13845443725586</v>
       </c>
       <c r="H1330" t="n">
         <v>220260</v>
@@ -38997,7 +38997,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1332" t="n">
-        <v>9.26596641540527</v>
+        <v>9.26596736907959</v>
       </c>
       <c r="H1332" t="n">
         <v>470450</v>
@@ -39055,7 +39055,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1334" t="n">
-        <v>9.24896621704102</v>
+        <v>9.2489652633667</v>
       </c>
       <c r="H1334" t="n">
         <v>286658</v>
@@ -39084,7 +39084,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G1335" t="n">
-        <v>9.00243949890137</v>
+        <v>9.00243854522705</v>
       </c>
       <c r="H1335" t="n">
         <v>667252</v>
@@ -39113,7 +39113,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1336" t="n">
-        <v>8.85792541503906</v>
+        <v>8.85792446136475</v>
       </c>
       <c r="H1336" t="n">
         <v>924305</v>
@@ -39142,7 +39142,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G1337" t="n">
-        <v>8.83242225646973</v>
+        <v>8.83242321014404</v>
       </c>
       <c r="H1337" t="n">
         <v>691598</v>
@@ -39258,7 +39258,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G1341" t="n">
-        <v>9.00243949890137</v>
+        <v>9.00243854522705</v>
       </c>
       <c r="H1341" t="n">
         <v>392991</v>
@@ -39316,7 +39316,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1343" t="n">
-        <v>9.0109395980835</v>
+        <v>9.01094055175781</v>
       </c>
       <c r="H1343" t="n">
         <v>249416</v>
@@ -39490,7 +39490,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G1349" t="n">
-        <v>8.56039333343506</v>
+        <v>8.56039237976074</v>
       </c>
       <c r="H1349" t="n">
         <v>442552</v>
@@ -39519,7 +39519,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G1350" t="n">
-        <v>8.61989879608154</v>
+        <v>8.61989974975586</v>
       </c>
       <c r="H1350" t="n">
         <v>270709</v>
@@ -39577,7 +39577,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G1352" t="n">
-        <v>8.84942436218262</v>
+        <v>8.8494234085083</v>
       </c>
       <c r="H1352" t="n">
         <v>442643</v>
@@ -39896,7 +39896,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1363" t="n">
-        <v>8.56889343261719</v>
+        <v>8.5688943862915</v>
       </c>
       <c r="H1363" t="n">
         <v>627311</v>
@@ -40070,7 +40070,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1369" t="n">
-        <v>8.11834621429443</v>
+        <v>8.11834716796875</v>
       </c>
       <c r="H1369" t="n">
         <v>1098341</v>
@@ -40099,7 +40099,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G1370" t="n">
-        <v>8.05034065246582</v>
+        <v>8.0503396987915</v>
       </c>
       <c r="H1370" t="n">
         <v>636232</v>
@@ -40157,7 +40157,7 @@
         <v>9.57499980926514</v>
       </c>
       <c r="G1372" t="n">
-        <v>8.13959980010986</v>
+        <v>8.13959884643555</v>
       </c>
       <c r="H1372" t="n">
         <v>769115</v>
@@ -40215,7 +40215,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1374" t="n">
-        <v>8.58589649200439</v>
+        <v>8.58589553833008</v>
       </c>
       <c r="H1374" t="n">
         <v>521686</v>
@@ -40273,7 +40273,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1376" t="n">
-        <v>8.56889343261719</v>
+        <v>8.5688943862915</v>
       </c>
       <c r="H1376" t="n">
         <v>474906</v>
@@ -40389,7 +40389,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G1380" t="n">
-        <v>8.2118558883667</v>
+        <v>8.21185684204102</v>
       </c>
       <c r="H1380" t="n">
         <v>488394</v>
@@ -40534,7 +40534,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1385" t="n">
-        <v>8.51788806915283</v>
+        <v>8.51788902282715</v>
       </c>
       <c r="H1385" t="n">
         <v>297568</v>
@@ -40563,7 +40563,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G1386" t="n">
-        <v>8.47538471221924</v>
+        <v>8.47538566589355</v>
       </c>
       <c r="H1386" t="n">
         <v>184022</v>
@@ -40592,7 +40592,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G1387" t="n">
-        <v>8.45838356018066</v>
+        <v>8.45838260650635</v>
       </c>
       <c r="H1387" t="n">
         <v>280731</v>
@@ -40621,7 +40621,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G1388" t="n">
-        <v>8.45838356018066</v>
+        <v>8.45838260650635</v>
       </c>
       <c r="H1388" t="n">
         <v>398507</v>
@@ -40679,7 +40679,7 @@
         <v>9.82499980926514</v>
       </c>
       <c r="G1390" t="n">
-        <v>8.3521203994751</v>
+        <v>8.35212230682373</v>
       </c>
       <c r="H1390" t="n">
         <v>515954</v>
@@ -40766,7 +40766,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G1393" t="n">
-        <v>8.66240310668945</v>
+        <v>8.66240406036377</v>
       </c>
       <c r="H1393" t="n">
         <v>749405</v>
@@ -40824,7 +40824,7 @@
         <v>10.0699996948242</v>
       </c>
       <c r="G1395" t="n">
-        <v>8.56039333343506</v>
+        <v>8.56039237976074</v>
       </c>
       <c r="H1395" t="n">
         <v>312011</v>
@@ -40911,7 +40911,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1398" t="n">
-        <v>7.78681182861328</v>
+        <v>7.7868127822876</v>
       </c>
       <c r="H1398" t="n">
         <v>2757234</v>
@@ -41056,7 +41056,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G1403" t="n">
-        <v>7.85481882095337</v>
+        <v>7.85481977462769</v>
       </c>
       <c r="H1403" t="n">
         <v>1236899</v>
@@ -41085,7 +41085,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1404" t="n">
-        <v>7.8208155632019</v>
+        <v>7.82081651687622</v>
       </c>
       <c r="H1404" t="n">
         <v>1054283</v>
@@ -41114,7 +41114,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1405" t="n">
-        <v>7.77831077575684</v>
+        <v>7.77831172943115</v>
       </c>
       <c r="H1405" t="n">
         <v>360056</v>
@@ -41201,7 +41201,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G1408" t="n">
-        <v>7.78681182861328</v>
+        <v>7.7868127822876</v>
       </c>
       <c r="H1408" t="n">
         <v>311531</v>
@@ -41230,7 +41230,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G1409" t="n">
-        <v>7.816565990448</v>
+        <v>7.81656503677368</v>
       </c>
       <c r="H1409" t="n">
         <v>192120</v>
@@ -41288,7 +41288,7 @@
         <v>9.19499969482422</v>
       </c>
       <c r="G1411" t="n">
-        <v>7.816565990448</v>
+        <v>7.81656503677368</v>
       </c>
       <c r="H1411" t="n">
         <v>254159</v>
@@ -41346,7 +41346,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G1413" t="n">
-        <v>7.51478385925293</v>
+        <v>7.51478481292725</v>
       </c>
       <c r="H1413" t="n">
         <v>1078150</v>
@@ -41375,7 +41375,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1414" t="n">
-        <v>7.39577198028564</v>
+        <v>7.39577102661133</v>
       </c>
       <c r="H1414" t="n">
         <v>1019261</v>
@@ -41433,7 +41433,7 @@
         <v>8.66499996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>7.36601829528809</v>
+        <v>7.36601877212524</v>
       </c>
       <c r="H1416" t="n">
         <v>316835</v>
@@ -41520,7 +41520,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1419" t="n">
-        <v>6.97072744369507</v>
+        <v>6.97072696685791</v>
       </c>
       <c r="H1419" t="n">
         <v>1127425</v>
@@ -41636,7 +41636,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G1423" t="n">
-        <v>6.98347854614258</v>
+        <v>6.98347902297974</v>
       </c>
       <c r="H1423" t="n">
         <v>384442</v>
@@ -41665,7 +41665,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1424" t="n">
-        <v>6.97072744369507</v>
+        <v>6.97072696685791</v>
       </c>
       <c r="H1424" t="n">
         <v>403050</v>
@@ -41694,7 +41694,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G1425" t="n">
-        <v>7.20875120162964</v>
+        <v>7.20875215530396</v>
       </c>
       <c r="H1425" t="n">
         <v>803371</v>
@@ -41839,7 +41839,7 @@
         <v>8.26500034332275</v>
       </c>
       <c r="G1430" t="n">
-        <v>7.02598333358765</v>
+        <v>7.0259838104248</v>
       </c>
       <c r="H1430" t="n">
         <v>442378</v>
@@ -41926,7 +41926,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G1433" t="n">
-        <v>7.07273721694946</v>
+        <v>7.07273817062378</v>
       </c>
       <c r="H1433" t="n">
         <v>997832</v>
@@ -42042,7 +42042,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1437" t="n">
-        <v>7.13224506378174</v>
+        <v>7.13224458694458</v>
       </c>
       <c r="H1437" t="n">
         <v>213525</v>
@@ -42100,7 +42100,7 @@
         <v>8.55500030517578</v>
       </c>
       <c r="G1439" t="n">
-        <v>7.27250957489014</v>
+        <v>7.27250862121582</v>
       </c>
       <c r="H1439" t="n">
         <v>208384</v>
@@ -42129,7 +42129,7 @@
         <v>8.61499977111816</v>
       </c>
       <c r="G1440" t="n">
-        <v>7.32351398468018</v>
+        <v>7.32351350784302</v>
       </c>
       <c r="H1440" t="n">
         <v>153130</v>
@@ -42187,7 +42187,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G1442" t="n">
-        <v>7.18749952316284</v>
+        <v>7.18750047683716</v>
       </c>
       <c r="H1442" t="n">
         <v>197685</v>
@@ -42245,7 +42245,7 @@
         <v>8.5</v>
       </c>
       <c r="G1444" t="n">
-        <v>7.22575426101685</v>
+        <v>7.22575378417969</v>
       </c>
       <c r="H1444" t="n">
         <v>465240</v>
@@ -42274,7 +42274,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1445" t="n">
-        <v>7.23425531387329</v>
+        <v>7.23425483703613</v>
       </c>
       <c r="H1445" t="n">
         <v>241449</v>
@@ -42303,7 +42303,7 @@
         <v>8.48499965667725</v>
       </c>
       <c r="G1446" t="n">
-        <v>7.21300220489502</v>
+        <v>7.21300315856934</v>
       </c>
       <c r="H1446" t="n">
         <v>493806</v>
@@ -42332,7 +42332,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G1447" t="n">
-        <v>7.13224506378174</v>
+        <v>7.13224458694458</v>
       </c>
       <c r="H1447" t="n">
         <v>351332</v>
@@ -42419,7 +42419,7 @@
         <v>8.25</v>
       </c>
       <c r="G1450" t="n">
-        <v>7.01323223114014</v>
+        <v>7.01323175430298</v>
       </c>
       <c r="H1450" t="n">
         <v>513491</v>
@@ -42593,7 +42593,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1456" t="n">
-        <v>6.7582049369812</v>
+        <v>6.75820541381836</v>
       </c>
       <c r="H1456" t="n">
         <v>369743</v>
@@ -42709,7 +42709,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1460" t="n">
-        <v>6.31190872192383</v>
+        <v>6.31190919876099</v>
       </c>
       <c r="H1460" t="n">
         <v>536445</v>
@@ -43057,7 +43057,7 @@
         <v>7.44500017166138</v>
       </c>
       <c r="G1472" t="n">
-        <v>6.32891035079956</v>
+        <v>6.32891082763672</v>
       </c>
       <c r="H1472" t="n">
         <v>218304</v>
@@ -43144,7 +43144,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G1475" t="n">
-        <v>6.63919258117676</v>
+        <v>6.63919305801392</v>
       </c>
       <c r="H1475" t="n">
         <v>1769037</v>
@@ -43202,7 +43202,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G1477" t="n">
-        <v>6.37991571426392</v>
+        <v>6.37991523742676</v>
       </c>
       <c r="H1477" t="n">
         <v>249208</v>
@@ -43260,7 +43260,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G1479" t="n">
-        <v>6.10363626480103</v>
+        <v>6.10363674163818</v>
       </c>
       <c r="H1479" t="n">
         <v>1000004</v>
@@ -43318,7 +43318,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1481" t="n">
-        <v>5.78060293197632</v>
+        <v>5.78060340881348</v>
       </c>
       <c r="H1481" t="n">
         <v>992024</v>
@@ -43347,7 +43347,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1482" t="n">
-        <v>6.09088516235352</v>
+        <v>6.09088563919067</v>
       </c>
       <c r="H1482" t="n">
         <v>606132</v>
@@ -43405,7 +43405,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G1484" t="n">
-        <v>5.94212007522583</v>
+        <v>5.94211959838867</v>
       </c>
       <c r="H1484" t="n">
         <v>540742</v>
@@ -43463,7 +43463,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G1486" t="n">
-        <v>5.60633516311646</v>
+        <v>5.6063346862793</v>
       </c>
       <c r="H1486" t="n">
         <v>683726</v>
@@ -43492,7 +43492,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G1487" t="n">
-        <v>5.50857496261597</v>
+        <v>5.50857543945312</v>
       </c>
       <c r="H1487" t="n">
         <v>878851</v>
@@ -43521,7 +43521,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G1488" t="n">
-        <v>5.36405992507935</v>
+        <v>5.36405944824219</v>
       </c>
       <c r="H1488" t="n">
         <v>1119617</v>
@@ -43637,7 +43637,7 @@
         <v>6.41499996185303</v>
       </c>
       <c r="G1492" t="n">
-        <v>5.45331859588623</v>
+        <v>5.45331811904907</v>
       </c>
       <c r="H1492" t="n">
         <v>413498</v>
@@ -43666,7 +43666,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G1493" t="n">
-        <v>5.53407764434814</v>
+        <v>5.5340781211853</v>
       </c>
       <c r="H1493" t="n">
         <v>334896</v>
@@ -43724,7 +43724,7 @@
         <v>6.80999994277954</v>
       </c>
       <c r="G1495" t="n">
-        <v>5.78910398483276</v>
+        <v>5.78910350799561</v>
       </c>
       <c r="H1495" t="n">
         <v>973159</v>
@@ -43753,7 +43753,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1496" t="n">
-        <v>5.72959756851196</v>
+        <v>5.72959804534912</v>
       </c>
       <c r="H1496" t="n">
         <v>596360</v>
@@ -43840,7 +43840,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G1499" t="n">
-        <v>5.7465991973877</v>
+        <v>5.74659967422485</v>
       </c>
       <c r="H1499" t="n">
         <v>292225</v>
@@ -43869,7 +43869,7 @@
         <v>6.625</v>
       </c>
       <c r="G1500" t="n">
-        <v>5.63183784484863</v>
+        <v>5.63183736801147</v>
       </c>
       <c r="H1500" t="n">
         <v>824737</v>
@@ -43927,7 +43927,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G1502" t="n">
-        <v>5.97612333297729</v>
+        <v>5.97612380981445</v>
       </c>
       <c r="H1502" t="n">
         <v>782481</v>
@@ -43985,7 +43985,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G1504" t="n">
-        <v>6.25665283203125</v>
+        <v>6.25665330886841</v>
       </c>
       <c r="H1504" t="n">
         <v>863991</v>
@@ -44101,7 +44101,7 @@
         <v>7.36999988555908</v>
       </c>
       <c r="G1508" t="n">
-        <v>6.2651538848877</v>
+        <v>6.26515340805054</v>
       </c>
       <c r="H1508" t="n">
         <v>541230</v>
@@ -44159,7 +44159,7 @@
         <v>6.92999982833862</v>
       </c>
       <c r="G1510" t="n">
-        <v>5.89111423492432</v>
+        <v>5.89111471176147</v>
       </c>
       <c r="H1510" t="n">
         <v>714679</v>
@@ -44217,7 +44217,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1512" t="n">
-        <v>6.04413080215454</v>
+        <v>6.04413032531738</v>
       </c>
       <c r="H1512" t="n">
         <v>511651</v>
@@ -44304,7 +44304,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1515" t="n">
-        <v>6.0356297492981</v>
+        <v>6.03562927246094</v>
       </c>
       <c r="H1515" t="n">
         <v>308123</v>
@@ -44333,7 +44333,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1516" t="n">
-        <v>6.09088516235352</v>
+        <v>6.09088563919067</v>
       </c>
       <c r="H1516" t="n">
         <v>462962</v>
@@ -44478,7 +44478,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1521" t="n">
-        <v>6.0356297492981</v>
+        <v>6.03562927246094</v>
       </c>
       <c r="H1521" t="n">
         <v>355951</v>
@@ -44565,7 +44565,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G1524" t="n">
-        <v>6.0653829574585</v>
+        <v>6.06538343429565</v>
       </c>
       <c r="H1524" t="n">
         <v>290140</v>
@@ -44623,7 +44623,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G1526" t="n">
-        <v>6.18864583969116</v>
+        <v>6.188645362854</v>
       </c>
       <c r="H1526" t="n">
         <v>287358</v>
@@ -44739,7 +44739,7 @@
         <v>7.21500015258789</v>
       </c>
       <c r="G1530" t="n">
-        <v>6.13339042663574</v>
+        <v>6.13338994979858</v>
       </c>
       <c r="H1530" t="n">
         <v>398036</v>
@@ -44797,7 +44797,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1532" t="n">
-        <v>6.01012754440308</v>
+        <v>6.01012706756592</v>
       </c>
       <c r="H1532" t="n">
         <v>312688</v>
@@ -44826,7 +44826,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G1533" t="n">
-        <v>6.01012754440308</v>
+        <v>6.01012706756592</v>
       </c>
       <c r="H1533" t="n">
         <v>593640</v>
@@ -44855,7 +44855,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1534" t="n">
-        <v>6.36716413497925</v>
+        <v>6.36716365814209</v>
       </c>
       <c r="H1534" t="n">
         <v>634465</v>
@@ -44971,7 +44971,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G1538" t="n">
-        <v>6.40116786956787</v>
+        <v>6.40116834640503</v>
       </c>
       <c r="H1538" t="n">
         <v>291825</v>
@@ -45000,7 +45000,7 @@
         <v>7.32999992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>6.23115015029907</v>
+        <v>6.23115062713623</v>
       </c>
       <c r="H1539" t="n">
         <v>562940</v>
@@ -45029,7 +45029,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G1540" t="n">
-        <v>5.99737501144409</v>
+        <v>5.99737548828125</v>
       </c>
       <c r="H1540" t="n">
         <v>387132</v>
@@ -45058,7 +45058,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G1541" t="n">
-        <v>6.16698980331421</v>
+        <v>6.16699028015137</v>
       </c>
       <c r="H1541" t="n">
         <v>388808</v>
@@ -45116,7 +45116,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1543" t="n">
-        <v>6.0191216468811</v>
+        <v>6.01912117004395</v>
       </c>
       <c r="H1543" t="n">
         <v>424736</v>
@@ -45377,7 +45377,7 @@
         <v>7.16499996185303</v>
       </c>
       <c r="G1552" t="n">
-        <v>6.23222589492798</v>
+        <v>6.23222637176514</v>
       </c>
       <c r="H1552" t="n">
         <v>178147</v>
@@ -45406,7 +45406,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G1553" t="n">
-        <v>6.30181074142456</v>
+        <v>6.30181121826172</v>
       </c>
       <c r="H1553" t="n">
         <v>167323</v>
@@ -45812,7 +45812,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G1567" t="n">
-        <v>5.68859148025513</v>
+        <v>5.68859100341797</v>
       </c>
       <c r="H1567" t="n">
         <v>222803</v>
@@ -45841,7 +45841,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G1568" t="n">
-        <v>5.50593042373657</v>
+        <v>5.50592994689941</v>
       </c>
       <c r="H1568" t="n">
         <v>112737</v>
@@ -45957,7 +45957,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1572" t="n">
-        <v>5.43199634552002</v>
+        <v>5.43199586868286</v>
       </c>
       <c r="H1572" t="n">
         <v>204408</v>
@@ -45986,7 +45986,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G1573" t="n">
-        <v>5.56681776046753</v>
+        <v>5.56681728363037</v>
       </c>
       <c r="H1573" t="n">
         <v>354717</v>
@@ -46015,7 +46015,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>5.61900663375854</v>
+        <v>5.61900615692139</v>
       </c>
       <c r="H1574" t="n">
         <v>371778</v>
@@ -46073,7 +46073,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G1576" t="n">
-        <v>5.67554426193237</v>
+        <v>5.67554378509521</v>
       </c>
       <c r="H1576" t="n">
         <v>451590</v>
@@ -46160,7 +46160,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G1579" t="n">
-        <v>5.31022214889526</v>
+        <v>5.31022167205811</v>
       </c>
       <c r="H1579" t="n">
         <v>623818</v>
@@ -46421,7 +46421,7 @@
         <v>6.59499979019165</v>
       </c>
       <c r="G1588" t="n">
-        <v>5.73643159866333</v>
+        <v>5.73643112182617</v>
       </c>
       <c r="H1588" t="n">
         <v>206960</v>
@@ -46450,7 +46450,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1589" t="n">
-        <v>5.79731845855713</v>
+        <v>5.79731798171997</v>
       </c>
       <c r="H1589" t="n">
         <v>273499</v>
@@ -46508,7 +46508,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1591" t="n">
-        <v>6.05391359329224</v>
+        <v>6.05391407012939</v>
       </c>
       <c r="H1591" t="n">
         <v>211882</v>
@@ -46537,7 +46537,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G1592" t="n">
-        <v>5.8625545501709</v>
+        <v>5.86255407333374</v>
       </c>
       <c r="H1592" t="n">
         <v>445033</v>
@@ -46595,7 +46595,7 @@
         <v>6.86499977111816</v>
       </c>
       <c r="G1594" t="n">
-        <v>5.97128105163574</v>
+        <v>5.97128057479858</v>
       </c>
       <c r="H1594" t="n">
         <v>356759</v>
@@ -46624,7 +46624,7 @@
         <v>6.66499996185303</v>
       </c>
       <c r="G1595" t="n">
-        <v>5.79731845855713</v>
+        <v>5.79731798171997</v>
       </c>
       <c r="H1595" t="n">
         <v>385377</v>
@@ -46653,7 +46653,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G1596" t="n">
-        <v>5.84950733184814</v>
+        <v>5.84950685501099</v>
       </c>
       <c r="H1596" t="n">
         <v>327728</v>
@@ -46711,7 +46711,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G1598" t="n">
-        <v>6.03651762008667</v>
+        <v>6.03651714324951</v>
       </c>
       <c r="H1598" t="n">
         <v>216562</v>
@@ -46740,7 +46740,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G1599" t="n">
-        <v>6.0191216468811</v>
+        <v>6.01912117004395</v>
       </c>
       <c r="H1599" t="n">
         <v>170090</v>
@@ -46769,7 +46769,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G1600" t="n">
-        <v>6.07131004333496</v>
+        <v>6.07131052017212</v>
       </c>
       <c r="H1600" t="n">
         <v>168765</v>
@@ -46885,7 +46885,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1604" t="n">
-        <v>6.05391359329224</v>
+        <v>6.05391407012939</v>
       </c>
       <c r="H1604" t="n">
         <v>195134</v>
@@ -46972,7 +46972,7 @@
         <v>6.80499982833862</v>
       </c>
       <c r="G1607" t="n">
-        <v>5.91909217834473</v>
+        <v>5.91909170150757</v>
       </c>
       <c r="H1607" t="n">
         <v>217266</v>
@@ -47088,7 +47088,7 @@
         <v>6.79500007629395</v>
       </c>
       <c r="G1611" t="n">
-        <v>5.9103946685791</v>
+        <v>5.91039419174194</v>
       </c>
       <c r="H1611" t="n">
         <v>230024</v>
@@ -47204,7 +47204,7 @@
         <v>6.33500003814697</v>
       </c>
       <c r="G1615" t="n">
-        <v>5.5102801322937</v>
+        <v>5.51027965545654</v>
       </c>
       <c r="H1615" t="n">
         <v>340807</v>
@@ -47233,7 +47233,7 @@
         <v>6.40500020980835</v>
       </c>
       <c r="G1616" t="n">
-        <v>5.5711669921875</v>
+        <v>5.57116651535034</v>
       </c>
       <c r="H1616" t="n">
         <v>154650</v>
@@ -47262,7 +47262,7 @@
         <v>6.47499990463257</v>
       </c>
       <c r="G1617" t="n">
-        <v>5.6320538520813</v>
+        <v>5.63205337524414</v>
       </c>
       <c r="H1617" t="n">
         <v>106494</v>
@@ -47291,7 +47291,7 @@
         <v>6.52500009536743</v>
       </c>
       <c r="G1618" t="n">
-        <v>5.67554426193237</v>
+        <v>5.67554378509521</v>
       </c>
       <c r="H1618" t="n">
         <v>193557</v>
@@ -47523,7 +47523,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1626" t="n">
-        <v>5.38415622711182</v>
+        <v>5.38415575027466</v>
       </c>
       <c r="H1626" t="n">
         <v>253046</v>
@@ -47581,7 +47581,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G1628" t="n">
-        <v>5.38415622711182</v>
+        <v>5.38415575027466</v>
       </c>
       <c r="H1628" t="n">
         <v>273775</v>
@@ -47639,7 +47639,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G1630" t="n">
-        <v>5.31022214889526</v>
+        <v>5.31022167205811</v>
       </c>
       <c r="H1630" t="n">
         <v>211039</v>
@@ -47726,7 +47726,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1633" t="n">
-        <v>5.49288320541382</v>
+        <v>5.49288272857666</v>
       </c>
       <c r="H1633" t="n">
         <v>256530</v>
@@ -47871,7 +47871,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G1638" t="n">
-        <v>5.61900663375854</v>
+        <v>5.61900615692139</v>
       </c>
       <c r="H1638" t="n">
         <v>271876</v>
@@ -47900,7 +47900,7 @@
         <v>6.38500022888184</v>
       </c>
       <c r="G1639" t="n">
-        <v>5.55377054214478</v>
+        <v>5.55377006530762</v>
       </c>
       <c r="H1639" t="n">
         <v>229483</v>
@@ -47929,7 +47929,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1640" t="n">
-        <v>5.43199634552002</v>
+        <v>5.43199586868286</v>
       </c>
       <c r="H1640" t="n">
         <v>392174</v>
@@ -47958,7 +47958,7 @@
         <v>6.31500005722046</v>
       </c>
       <c r="G1641" t="n">
-        <v>5.49288320541382</v>
+        <v>5.49288272857666</v>
       </c>
       <c r="H1641" t="n">
         <v>354096</v>
@@ -48074,7 +48074,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G1645" t="n">
-        <v>5.62770414352417</v>
+        <v>5.62770366668701</v>
       </c>
       <c r="H1645" t="n">
         <v>173514</v>
@@ -48190,7 +48190,7 @@
         <v>6.74499988555908</v>
       </c>
       <c r="G1649" t="n">
-        <v>5.86690378189087</v>
+        <v>5.86690330505371</v>
       </c>
       <c r="H1649" t="n">
         <v>304886</v>
@@ -48335,7 +48335,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G1654" t="n">
-        <v>6.06261157989502</v>
+        <v>6.06261205673218</v>
       </c>
       <c r="H1654" t="n">
         <v>236220</v>
@@ -48364,7 +48364,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G1655" t="n">
-        <v>6.05391359329224</v>
+        <v>6.05391407012939</v>
       </c>
       <c r="H1655" t="n">
         <v>145304</v>
@@ -48393,7 +48393,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G1656" t="n">
-        <v>5.97563076019287</v>
+        <v>5.97563028335571</v>
       </c>
       <c r="H1656" t="n">
         <v>155925</v>
@@ -48422,7 +48422,7 @@
         <v>6.72499990463257</v>
       </c>
       <c r="G1657" t="n">
-        <v>5.84950733184814</v>
+        <v>5.84950685501099</v>
       </c>
       <c r="H1657" t="n">
         <v>540420</v>
@@ -48509,7 +48509,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G1660" t="n">
-        <v>6.11045169830322</v>
+        <v>6.11045217514038</v>
       </c>
       <c r="H1660" t="n">
         <v>593820</v>
@@ -48538,7 +48538,7 @@
         <v>7.02500009536743</v>
       </c>
       <c r="G1661" t="n">
-        <v>6.11045169830322</v>
+        <v>6.11045217514038</v>
       </c>
       <c r="H1661" t="n">
         <v>293085</v>
@@ -48567,7 +48567,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G1662" t="n">
-        <v>6.18438577651978</v>
+        <v>6.18438625335693</v>
       </c>
       <c r="H1662" t="n">
         <v>404302</v>
@@ -48770,7 +48770,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1669" t="n">
-        <v>6.24092435836792</v>
+        <v>6.24092483520508</v>
       </c>
       <c r="H1669" t="n">
         <v>242065</v>
@@ -48828,7 +48828,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G1671" t="n">
-        <v>6.16698980331421</v>
+        <v>6.16699028015137</v>
       </c>
       <c r="H1671" t="n">
         <v>105288</v>
@@ -48857,7 +48857,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G1672" t="n">
-        <v>6.30181074142456</v>
+        <v>6.30181121826172</v>
       </c>
       <c r="H1672" t="n">
         <v>224652</v>
@@ -49002,7 +49002,7 @@
         <v>7.375</v>
       </c>
       <c r="G1677" t="n">
-        <v>6.41488695144653</v>
+        <v>6.41488742828369</v>
       </c>
       <c r="H1677" t="n">
         <v>318095</v>
@@ -49031,7 +49031,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G1678" t="n">
-        <v>6.48882102966309</v>
+        <v>6.48882150650024</v>
       </c>
       <c r="H1678" t="n">
         <v>147514</v>
@@ -49118,7 +49118,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G1681" t="n">
-        <v>6.53666114807129</v>
+        <v>6.53666162490845</v>
       </c>
       <c r="H1681" t="n">
         <v>356104</v>
@@ -49234,7 +49234,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G1685" t="n">
-        <v>6.38009452819824</v>
+        <v>6.3800950050354</v>
       </c>
       <c r="H1685" t="n">
         <v>205651</v>
@@ -49263,7 +49263,7 @@
         <v>7.5</v>
       </c>
       <c r="G1686" t="n">
-        <v>6.52361392974854</v>
+        <v>6.52361440658569</v>
       </c>
       <c r="H1686" t="n">
         <v>272875</v>
@@ -49292,7 +49292,7 @@
         <v>7.48999977111816</v>
       </c>
       <c r="G1687" t="n">
-        <v>6.51491594314575</v>
+        <v>6.51491546630859</v>
       </c>
       <c r="H1687" t="n">
         <v>184886</v>
@@ -49437,7 +49437,7 @@
         <v>7.33500003814697</v>
       </c>
       <c r="G1692" t="n">
-        <v>6.38009452819824</v>
+        <v>6.3800950050354</v>
       </c>
       <c r="H1692" t="n">
         <v>156192</v>
@@ -49466,7 +49466,7 @@
         <v>7.17500019073486</v>
       </c>
       <c r="G1693" t="n">
-        <v>6.24092435836792</v>
+        <v>6.24092483520508</v>
       </c>
       <c r="H1693" t="n">
         <v>213681</v>
@@ -49495,7 +49495,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G1694" t="n">
-        <v>6.28876352310181</v>
+        <v>6.28876399993896</v>
       </c>
       <c r="H1694" t="n">
         <v>95514</v>
@@ -49582,7 +49582,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G1697" t="n">
-        <v>6.35399961471558</v>
+        <v>6.35400009155273</v>
       </c>
       <c r="H1697" t="n">
         <v>97943</v>
@@ -49640,7 +49640,7 @@
         <v>7.2350001335144</v>
       </c>
       <c r="G1699" t="n">
-        <v>6.29311323165894</v>
+        <v>6.29311370849609</v>
       </c>
       <c r="H1699" t="n">
         <v>91680</v>
@@ -49843,7 +49843,7 @@
         <v>7.96500015258789</v>
       </c>
       <c r="G1706" t="n">
-        <v>6.92807865142822</v>
+        <v>6.92807817459106</v>
       </c>
       <c r="H1706" t="n">
         <v>423143</v>
@@ -49959,7 +49959,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G1710" t="n">
-        <v>7.19772100448608</v>
+        <v>7.19772052764893</v>
       </c>
       <c r="H1710" t="n">
         <v>730813</v>
@@ -49988,7 +49988,7 @@
         <v>8.625</v>
       </c>
       <c r="G1711" t="n">
-        <v>7.50215578079224</v>
+        <v>7.50215673446655</v>
       </c>
       <c r="H1711" t="n">
         <v>1273529</v>
@@ -50046,7 +50046,7 @@
         <v>8.82999992370605</v>
       </c>
       <c r="G1713" t="n">
-        <v>7.68046855926514</v>
+        <v>7.68046760559082</v>
       </c>
       <c r="H1713" t="n">
         <v>543773</v>
@@ -50278,7 +50278,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G1721" t="n">
-        <v>7.17162656784058</v>
+        <v>7.17162609100342</v>
       </c>
       <c r="H1721" t="n">
         <v>318551</v>
@@ -50336,7 +50336,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1723" t="n">
-        <v>7.35863637924194</v>
+        <v>7.3586368560791</v>
       </c>
       <c r="H1723" t="n">
         <v>442517</v>
@@ -50394,7 +50394,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G1725" t="n">
-        <v>7.21511697769165</v>
+        <v>7.21511650085449</v>
       </c>
       <c r="H1725" t="n">
         <v>180285</v>
@@ -50597,7 +50597,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1732" t="n">
-        <v>7.21946668624878</v>
+        <v>7.21946620941162</v>
       </c>
       <c r="H1732" t="n">
         <v>362705</v>
@@ -50742,7 +50742,7 @@
         <v>8.23499965667725</v>
       </c>
       <c r="G1737" t="n">
-        <v>7.16292810440063</v>
+        <v>7.16292762756348</v>
       </c>
       <c r="H1737" t="n">
         <v>262644</v>
@@ -50800,7 +50800,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G1739" t="n">
-        <v>7.28035354614258</v>
+        <v>7.28035306930542</v>
       </c>
       <c r="H1739" t="n">
         <v>385555</v>
@@ -51061,7 +51061,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1748" t="n">
-        <v>6.82804918289185</v>
+        <v>6.828049659729</v>
       </c>
       <c r="H1748" t="n">
         <v>390212</v>
@@ -51119,7 +51119,7 @@
         <v>7.90500020980835</v>
       </c>
       <c r="G1750" t="n">
-        <v>6.87588930130005</v>
+        <v>6.87588977813721</v>
       </c>
       <c r="H1750" t="n">
         <v>361584</v>
@@ -51438,7 +51438,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1761" t="n">
-        <v>6.82804918289185</v>
+        <v>6.828049659729</v>
       </c>
       <c r="H1761" t="n">
         <v>587784</v>
@@ -51612,7 +51612,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G1767" t="n">
-        <v>6.98026704788208</v>
+        <v>6.98026657104492</v>
       </c>
       <c r="H1767" t="n">
         <v>454744</v>
@@ -51728,7 +51728,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1771" t="n">
-        <v>7.2281641960144</v>
+        <v>7.22816467285156</v>
       </c>
       <c r="H1771" t="n">
         <v>279940</v>
@@ -51815,7 +51815,7 @@
         <v>8.26500034332275</v>
       </c>
       <c r="G1774" t="n">
-        <v>7.1890230178833</v>
+        <v>7.18902349472046</v>
       </c>
       <c r="H1774" t="n">
         <v>213174</v>
@@ -51844,7 +51844,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G1775" t="n">
-        <v>7.25425863265991</v>
+        <v>7.25425910949707</v>
       </c>
       <c r="H1775" t="n">
         <v>172962</v>
@@ -51873,7 +51873,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G1776" t="n">
-        <v>7.27165508270264</v>
+        <v>7.27165460586548</v>
       </c>
       <c r="H1776" t="n">
         <v>308540</v>
@@ -51902,7 +51902,7 @@
         <v>8.35499954223633</v>
       </c>
       <c r="G1777" t="n">
-        <v>7.26730632781982</v>
+        <v>7.26730537414551</v>
       </c>
       <c r="H1777" t="n">
         <v>132772</v>
@@ -51931,7 +51931,7 @@
         <v>8.3100004196167</v>
       </c>
       <c r="G1778" t="n">
-        <v>7.2281641960144</v>
+        <v>7.22816467285156</v>
       </c>
       <c r="H1778" t="n">
         <v>115709</v>
@@ -51960,7 +51960,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G1779" t="n">
-        <v>7.14988136291504</v>
+        <v>7.14988088607788</v>
       </c>
       <c r="H1779" t="n">
         <v>182182</v>
@@ -52018,7 +52018,7 @@
         <v>8.26500034332275</v>
       </c>
       <c r="G1781" t="n">
-        <v>7.1890230178833</v>
+        <v>7.18902349472046</v>
       </c>
       <c r="H1781" t="n">
         <v>227840</v>
@@ -52047,7 +52047,7 @@
         <v>8.23499965667725</v>
       </c>
       <c r="G1782" t="n">
-        <v>7.16292810440063</v>
+        <v>7.16292762756348</v>
       </c>
       <c r="H1782" t="n">
         <v>348606</v>
@@ -52105,7 +52105,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G1784" t="n">
-        <v>7.35863637924194</v>
+        <v>7.3586368560791</v>
       </c>
       <c r="H1784" t="n">
         <v>404423</v>
@@ -52192,7 +52192,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1787" t="n">
-        <v>7.34124088287354</v>
+        <v>7.34123992919922</v>
       </c>
       <c r="H1787" t="n">
         <v>270407</v>
@@ -52279,7 +52279,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G1790" t="n">
-        <v>7.34124088287354</v>
+        <v>7.34123992919922</v>
       </c>
       <c r="H1790" t="n">
         <v>522045</v>
@@ -77573,6 +77573,35 @@
         <v>183172</v>
       </c>
       <c r="I2662" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2663">
+      <c r="A2663" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2663" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2663" t="n">
+        <v>12.6899995803833</v>
+      </c>
+      <c r="D2663" t="n">
+        <v>12.8800001144409</v>
+      </c>
+      <c r="E2663" t="n">
+        <v>12.6499996185303</v>
+      </c>
+      <c r="F2663" t="n">
+        <v>12.6499996185303</v>
+      </c>
+      <c r="G2663" t="n">
+        <v>12.6499996185303</v>
+      </c>
+      <c r="H2663" t="n">
+        <v>313902</v>
+      </c>
+      <c r="I2663" t="s">
         <v>9</v>
       </c>
     </row>
